--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -483,7 +483,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B5" t="str">
         <v>Route 103</v>
@@ -503,7 +503,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B6" t="str">
         <v>Route 103</v>
@@ -523,7 +523,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B7" t="str">
         <v>Route 103</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B8" t="str">
         <v>Route 103</v>
@@ -563,7 +563,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B9" t="str">
         <v>Route 103</v>
@@ -583,7 +583,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B10" t="str">
         <v>Route 102</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B11" t="str">
         <v>Route 102</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B12" t="str">
         <v>Route 102</v>
@@ -643,7 +643,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B13" t="str">
         <v>Route 102</v>
@@ -663,7 +663,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B14" t="str">
         <v>Route 102</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B15" t="str">
         <v>Route 102</v>
@@ -703,7 +703,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B16" t="str">
         <v>Route 104</v>
@@ -723,7 +723,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B17" t="str">
         <v>Route 104</v>
@@ -743,7 +743,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B18" t="str">
         <v>Route 104</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B19" t="str">
         <v>Route 104</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B20" t="str">
         <v>Route 104</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B21" t="str">
         <v>Petalburg Woods</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B22" t="str">
         <v>Petalburg Woods</v>
@@ -843,7 +843,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B23" t="str">
         <v>Petalburg Woods</v>
@@ -863,7 +863,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B24" t="str">
         <v>Petalburg Woods</v>
@@ -883,7 +883,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B25" t="str">
         <v>Petalburg Woods</v>
@@ -903,7 +903,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B26" t="str">
         <v>Petalburg Woods</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B27" t="str">
         <v>Route 116</v>
@@ -943,7 +943,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B28" t="str">
         <v>Route 116</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B29" t="str">
         <v>Route 116</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B30" t="str">
         <v>Route 116</v>
@@ -1003,7 +1003,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B31" t="str">
         <v>Route 116</v>
@@ -1023,7 +1023,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B32" t="str">
         <v>Granite Cave</v>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B33" t="str">
         <v>Granite Cave</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B34" t="str">
         <v>Granite Cave</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B35" t="str">
         <v>Granite Cave</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B36" t="str">
         <v>Granite Cave</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B37" t="str">
         <v>Granite Cave</v>
@@ -1143,7 +1143,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B38" t="str">
         <v>Granite Cave</v>
@@ -1163,7 +1163,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B39" t="str">
         <v>Granite Cave</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B40" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B41" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B42" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1243,7 +1243,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B43" t="str">
         <v>Tiny Fishing Spot</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B44" t="str">
         <v>Route 107</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B45" t="str">
         <v>Route 107</v>
@@ -1303,7 +1303,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B46" t="str">
         <v>Route 107</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B47" t="str">
         <v>Route 110</v>
@@ -1343,7 +1343,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B48" t="str">
         <v>Route 110</v>
@@ -1363,7 +1363,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B49" t="str">
         <v>Route 110</v>
@@ -1383,7 +1383,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B50" t="str">
         <v>Route 110</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B51" t="str">
         <v>Route 110</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B52" t="str">
         <v>Route 110</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B53" t="str">
         <v>Route 110</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B54" t="str">
         <v>Route 117</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B55" t="str">
         <v>Route 117</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B56" t="str">
         <v>Route 117</v>
@@ -1523,7 +1523,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B57" t="str">
         <v>Route 117</v>
@@ -1543,7 +1543,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B58" t="str">
         <v>Route 117</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B59" t="str">
         <v>Route 117</v>
@@ -1583,7 +1583,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B60" t="str">
         <v>Route 117</v>
@@ -1603,7 +1603,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B61" t="str">
         <v>Route 111</v>
@@ -1623,7 +1623,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B62" t="str">
         <v>Route 111</v>
@@ -1643,7 +1643,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B63" t="str">
         <v>Route 111</v>
@@ -1663,7 +1663,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B64" t="str">
         <v>Route 111</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B65" t="str">
         <v>Route 111</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B66" t="str">
         <v>Fiery Path</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B67" t="str">
         <v>Fiery Path</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B68" t="str">
         <v>Fiery Path</v>
@@ -1763,7 +1763,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B69" t="str">
         <v>Fiery Path</v>
@@ -1783,7 +1783,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B70" t="str">
         <v>Fiery Path</v>
@@ -1803,7 +1803,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B71" t="str">
         <v>Fiery Path</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B72" t="str">
         <v>Jagged Pass</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B73" t="str">
         <v>Jagged Pass</v>
@@ -1863,7 +1863,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B74" t="str">
         <v>Jagged Pass</v>
@@ -1883,7 +1883,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B75" t="str">
         <v>Route 113</v>
@@ -1903,7 +1903,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B76" t="str">
         <v>Route 113</v>
@@ -1923,7 +1923,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B77" t="str">
         <v>Route 113</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B78" t="str">
         <v>Route 114</v>
@@ -1963,7 +1963,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B79" t="str">
         <v>Route 114</v>
@@ -1983,7 +1983,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B80" t="str">
         <v>Route 114</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B81" t="str">
         <v>Route 114</v>
@@ -2023,7 +2023,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B82" t="str">
         <v>Route 114</v>
@@ -2043,7 +2043,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B83" t="str">
         <v>Route 114</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B84" t="str">
         <v>Route 114</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B85" t="str">
         <v>Meteor Falls</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B86" t="str">
         <v>Meteor Falls</v>
@@ -2123,7 +2123,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B87" t="str">
         <v>Meteor Falls</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B88" t="str">
         <v>Meteor Falls</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B89" t="str">
         <v>Meteor Falls</v>
@@ -2183,7 +2183,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B90" t="str">
         <v>Route 115</v>
@@ -2203,7 +2203,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B91" t="str">
         <v>Route 115</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B92" t="str">
         <v>Route 115</v>
@@ -2243,7 +2243,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B93" t="str">
         <v>Route 115</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B94" t="str">
         <v>Route 115</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B95" t="str">
         <v>Route 118</v>
@@ -2303,7 +2303,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B96" t="str">
         <v>Route 118</v>
@@ -2323,7 +2323,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B97" t="str">
         <v>Route 118</v>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B98" t="str">
         <v>Route 118</v>
@@ -2363,7 +2363,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B99" t="str">
         <v>Route 118</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B100" t="str">
         <v>Route 118</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B101" t="str">
         <v>Small Fishing Spot</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B102" t="str">
         <v>Small Fishing Spot</v>
@@ -2443,7 +2443,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B103" t="str">
         <v>Small Fishing Spot</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B104" t="str">
         <v>Small Fishing Spot</v>
@@ -2483,7 +2483,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B105" t="str">
         <v>Small Fishing Spot</v>
@@ -2503,7 +2503,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B106" t="str">
         <v>Small Fishing Spot</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B107" t="str">
         <v>Route 119</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B108" t="str">
         <v>Route 119</v>
@@ -2563,7 +2563,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B109" t="str">
         <v>Route 119</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B110" t="str">
         <v>Route 119</v>
@@ -2603,7 +2603,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B111" t="str">
         <v>Route 119</v>
@@ -2623,7 +2623,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B112" t="str">
         <v>Route 119</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B113" t="str">
         <v>Route 120</v>
@@ -2663,7 +2663,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B114" t="str">
         <v>Route 120</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B115" t="str">
         <v>Route 120</v>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B116" t="str">
         <v>Route 120</v>
@@ -2723,7 +2723,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B117" t="str">
         <v>Route 120</v>
@@ -2743,7 +2743,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B118" t="str">
         <v>Route 120</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B119" t="str">
         <v>Route 120</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B120" t="str">
         <v>Route 121</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B121" t="str">
         <v>Route 121</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B122" t="str">
         <v>Route 121</v>
@@ -2843,7 +2843,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B123" t="str">
         <v>Route 121</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B124" t="str">
         <v>Route 121</v>
@@ -2883,7 +2883,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B125" t="str">
         <v>Route 121</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B126" t="str">
         <v>Safari Zone East</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B127" t="str">
         <v>Safari Zone East</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B128" t="str">
         <v>Safari Zone East</v>
@@ -2963,7 +2963,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B129" t="str">
         <v>Safari Zone East</v>
@@ -2983,7 +2983,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B130" t="str">
         <v>Safari Zone East</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B131" t="str">
         <v>Safari Zone East</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B132" t="str">
         <v>Safari Zone East</v>
@@ -3043,7 +3043,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B133" t="str">
         <v>Safari Zone East</v>
@@ -3063,7 +3063,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B134" t="str">
         <v>Safari Zone East</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B135" t="str">
         <v>Safari Zone West</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B136" t="str">
         <v>Safari Zone West</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B137" t="str">
         <v>Safari Zone West</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B138" t="str">
         <v>Safari Zone West</v>
@@ -3163,7 +3163,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B139" t="str">
         <v>Safari Zone West</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B140" t="str">
         <v>Safari Zone West</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B141" t="str">
         <v>Safari Zone West</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B142" t="str">
         <v>Safari Zone West</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B143" t="str">
         <v>Safari Zone West</v>
@@ -3263,7 +3263,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B144" t="str">
         <v>Safari Zone West</v>
@@ -3283,7 +3283,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B145" t="str">
         <v>Safari Zone North</v>
@@ -3303,7 +3303,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B146" t="str">
         <v>Safari Zone North</v>
@@ -3323,7 +3323,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B147" t="str">
         <v>Safari Zone North</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B148" t="str">
         <v>Safari Zone North</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B149" t="str">
         <v>Safari Zone North</v>
@@ -3383,7 +3383,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B150" t="str">
         <v>Safari Zone North</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B151" t="str">
         <v>Safari Zone North</v>
@@ -3423,7 +3423,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B152" t="str">
         <v>Safari Zone North</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B153" t="str">
         <v>Mount Pyre</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B154" t="str">
         <v>Mount Pyre</v>
@@ -3483,7 +3483,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B155" t="str">
         <v>Mount Pyre</v>
@@ -3503,7 +3503,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B156" t="str">
         <v>Mount Pyre</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B157" t="str">
         <v>Mount Pyre</v>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B158" t="str">
         <v>Route 123</v>
@@ -3563,7 +3563,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B159" t="str">
         <v>Route 123</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B160" t="str">
         <v>Route 123</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B161" t="str">
         <v>Route 123</v>
@@ -3623,7 +3623,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B162" t="str">
         <v>Route 123</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B163" t="str">
         <v>Big Fishing Spot</v>
@@ -3663,7 +3663,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B164" t="str">
         <v>Big Fishing Spot</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B165" t="str">
         <v>Big Fishing Spot</v>
@@ -3703,7 +3703,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B166" t="str">
         <v>Big Fishing Spot</v>
@@ -3723,7 +3723,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B167" t="str">
         <v>Big Fishing Spot</v>
@@ -3743,7 +3743,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B168" t="str">
         <v>Big Fishing Spot</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B169" t="str">
         <v>Big Fishing Spot</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B170" t="str">
         <v>Underwater Fishing Spot</v>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B171" t="str">
         <v>Underwater Fishing Spot</v>
@@ -3823,7 +3823,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B172" t="str">
         <v>Underwater Fishing Spot</v>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B173" t="str">
         <v>Shoal Cave</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B174" t="str">
         <v>Shoal Cave</v>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B175" t="str">
         <v>Shoal Cave</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B176" t="str">
         <v>Shoal Cave</v>
@@ -3923,7 +3923,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="B177" t="str">
         <v>Mirage Island</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B178" t="str">
         <v>Victory Road</v>
@@ -3963,7 +3963,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B179" t="str">
         <v>Victory Road</v>
@@ -3983,7 +3983,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B180" t="str">
         <v>Victory Road</v>
@@ -4003,7 +4003,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B181" t="str">
         <v>Victory Road</v>
@@ -4023,7 +4023,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B182" t="str">
         <v>Victory Road</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B183" t="str">
         <v>Victory Road</v>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B184" t="str">
         <v>Sky Pillar</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B185" t="str">
         <v>Sky Pillar</v>
@@ -4103,7 +4103,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B186" t="str">
         <v>Sky Pillar</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B187" t="str">
         <v>Sky Pillar</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B188" t="str">
         <v>Sky Pillar</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B189" t="str">
         <v>Nebula Fissure</v>
@@ -4183,7 +4183,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B190" t="str">
         <v>Nebula Fissure</v>
@@ -4203,7 +4203,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B191" t="str">
         <v>Nebula Fissure</v>
@@ -4223,7 +4223,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B192" t="str">
         <v>Nebula Fissure</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B193" t="str">
         <v>Trick House</v>
@@ -4263,7 +4263,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B194" t="str">
         <v>Trick House</v>
@@ -4283,7 +4283,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B195" t="str">
         <v>Trick House</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B196" t="str">
         <v>Trick House</v>
@@ -4323,7 +4323,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B197" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B198" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -4363,7 +4363,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B199" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -4383,7 +4383,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B200" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -4403,7 +4403,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B201" t="str">
         <v>Abandoned Ship</v>
@@ -4423,7 +4423,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B202" t="str">
         <v>Abandoned Ship</v>
@@ -4443,7 +4443,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B203" t="str">
         <v>Abandoned Ship</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B204" t="str">
         <v>Abandoned Ship</v>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B205" t="str">
         <v>Enemy Hideout</v>
@@ -4503,7 +4503,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B206" t="str">
         <v>Enemy Hideout</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B207" t="str">
         <v>Enemy Hideout</v>
@@ -4543,7 +4543,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B208" t="str">
         <v>Enemy Hideout</v>
@@ -4563,7 +4563,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B209" t="str">
         <v>Sealed Chamber</v>
@@ -4583,7 +4583,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B210" t="str">
         <v>Sealed Chamber</v>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B211" t="str">
         <v>Sealed Chamber</v>
@@ -4623,7 +4623,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B212" t="str">
         <v>Ancient Ruins</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B213" t="str">
         <v>Ancient Ruins</v>
@@ -4663,7 +4663,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B214" t="str">
         <v>Ancient Ruins</v>
@@ -4683,7 +4683,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B215" t="str">
         <v>Mauville Game Corner</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B216" t="str">
         <v>Mauville Game Corner</v>
@@ -4723,7 +4723,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B217" t="str">
         <v>Mauville Game Corner</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B218" t="str">
         <v>Mauville Game Corner</v>
@@ -4763,7 +4763,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B219" t="str">
         <v>Starter Sanctuary</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B220" t="str">
         <v>Starter Sanctuary</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B221" t="str">
         <v>Starter Sanctuary</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B222" t="str">
         <v>Daycare Special Spot</v>
@@ -4843,7 +4843,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B223" t="str">
         <v>Daycare Special Spot</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B224" t="str">
         <v>Daycare Special Spot</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B225" t="str">
         <v>Daycare Special Spot</v>
@@ -4903,7 +4903,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B226" t="str">
         <v>Battle Frontier Facility</v>
@@ -4923,7 +4923,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B227" t="str">
         <v>Battle Frontier Facility</v>
@@ -4943,7 +4943,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B228" t="str">
         <v>Battle Frontier Facility</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B229" t="str">
         <v>Battle Frontier Facility</v>
@@ -4983,7 +4983,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B230" t="str">
         <v>Weather Climax Cave</v>
@@ -5003,7 +5003,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B231" t="str">
         <v>Weather Climax Cave</v>
@@ -5023,7 +5023,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B232" t="str">
         <v>Weather Climax Cave</v>
@@ -5043,7 +5043,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B233" t="str">
         <v>Roaming Hoenn Skies</v>
@@ -5063,7 +5063,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B234" t="str">
         <v>Roaming Hoenn Skies</v>
@@ -5090,10 +5090,627 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C56"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Challenge Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Requisite</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Reward</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Challenge 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Catch 2 Poochyena</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Unlocks: Route 103</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Challenge 2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Catch 1 Wingull</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Unlocks: Route 102</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Catch 1 Lotad, Catch 1 Seedot</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Unlocks: Route 104</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Catch 2 Taillow</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Unlocks: Petalburg Woods</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Challenge 5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Catch 1 Shroomish, Catch 1 Slakoth</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Unlocks: Route 116; Gift: 1 Bug Stone</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Challenge 6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Catch 2 Whismur</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Unlocks: Rustboro Gym</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Earn Stone Badge</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Unlocks: Granite Cave</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Catch 1 Makuhita, Catch 1 Aron</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Unlocks: Tiny Fishing Spot; Gift: 1 Rock Stone</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="B10" t="str">
+        <v/>
+      </c>
+      <c r="C10" t="str">
+        <v>Unlocks: Dewford Gym</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Earn Knuckle Badge</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Unlocks: Route 107</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Challenge 11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Defeat 50 on Route 107</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Unlocks: Mauville Gym</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Earn Dynamo Badge</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Unlocks: Route 110</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Catch 2 Electrike, Catch 1 Plusle, Catch 1 Minun</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Unlocks: Route 117</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Challenge 14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Catch 1 Illumise, Catch 1 Volbeat</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Unlocks: Route 111</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Challenge 15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Catch 1 Trapinch, Catch 1 Cacnea</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Unlocks: Lavaridge Gym</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Earn Heat Badge</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Unlocks: Fiery Path</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Challenge 17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Catch 2 Numel, Catch 1 Torkoal</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Unlocks: Jagged Pass; Gift: 1 Fire Stone</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Defeat 100 on Jagged Pass</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Unlocks: Route 113</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Challenge 19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Catch 5 Spinda</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Unlocks: Route 114</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Catch 1 Zangoose, Catch 1 Seviper</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Unlocks: Meteor Falls</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Catch 1 Bagon, Catch 1 Solrock, Catch 1 Lunatone</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Unlocks: Route 115; Gift: 1 Dragon Stone</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Catch 2 Swablu</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Unlocks: Petalburg Gym</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Earn Balance Badge</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Unlocks: Route 118</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Catch 1 Manectric, Catch 1 Kecleon</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Unlocks: Small Fishing Spot</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Catch 1 Carvanha, Catch 1 Barboach</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Unlocks: Route 119</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Catch 2 Tropius</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Unlocks: Route 120</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Catch 1 Absol</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Unlocks: Route 121</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Catch 2 Shuppet, Catch 2 Duskull</v>
+      </c>
+      <c r="C29" t="str">
+        <v>Unlocks: Safari Zone East, Safari Zone West, Safari Zone North</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Defeat 150 on Safari Zone East</v>
+      </c>
+      <c r="C30" t="str">
+        <v>Unlocks: Mount Pyre</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Catch 1 Chimecho</v>
+      </c>
+      <c r="C31" t="str">
+        <v>Unlocks: Route 123; Gift: 2 Ghost Stone</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Defeat 150 on Route 123</v>
+      </c>
+      <c r="C32" t="str">
+        <v>Unlocks: Fortree Gym</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Earn Feather Badge</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Unlocks: Mossdeep Gym</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Earn Mind Badge</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Unlocks: Big Fishing Spot</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Catch 1 Feebas, Catch 2 Wailmer</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Unlocks: Underwater Fishing Spot; Gift: 2 Water Stone</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Catch 1 Relicanth, Catch 2 Clamperl</v>
+      </c>
+      <c r="C36" t="str">
+        <v>Unlocks: Sootopolis Gym</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Earn Rain Badge</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Unlocks: Shoal Cave</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Catch 2 Spheal, Catch 1 Snorunt</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Unlocks: Mirage Island; Gift: 1 Ice Stone</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Catch 1 Wynaut</v>
+      </c>
+      <c r="C39" t="str">
+        <v>Unlocks: Sky Pillar</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Catch 1 Altaria, Catch 1 Claydol</v>
+      </c>
+      <c r="C40" t="str">
+        <v>Unlocks: Victory Road</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Defeat 200 on Victory Road</v>
+      </c>
+      <c r="C41" t="str">
+        <v>Unlocks: Hoenn Pokemon League</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Defeat Hoenn Champion</v>
+      </c>
+      <c r="C42" t="str">
+        <v>Unlocks: Roaming Hoenn Skies, Mauville Game Corner, Trick House; Gifts: 2 Masterball</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Catch 8 Common (Slakoth/Abra)</v>
+      </c>
+      <c r="C43" t="str">
+        <v>Unlocks: Starter Sanctuary; Gift: 3 Fire Stone</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Catch 1 Treecko, Catch 1 Torchic, Catch 1 Mudkip</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Unlocks: Daycare Special Spot; Gift: 3 Leaf Stone</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Catch 1 Wynaut, Catch 1 Azurill</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Unlocks: Battle Frontier Facility; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Defeat 50 on Battle Frontier Facility</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Unlocks: Weather Climax Cave; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Catch 1 Kyogre, Catch 1 Groudon, Catch 1 Rayquaza</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 2 Masterball</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Extra Challenge B 1</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Defeat 20 on Trick House</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Unlocks: Rustboro Fossil Lab; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Extra Challenge B 2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Catch 1 Lileep, Catch 1 Anorith</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Unlocks: Abandoned Ship; Gift: 1 Root Fossil</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Extra Challenge B 3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Catch 1 Tentacruel</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Unlocks: Enemy Hideout; Gift: 1 Deep Sea Scale</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Catch 1 Weezing; Defeat 25 on Enemy Hideout</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Unlocks: Sealed Chamber; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Extra Challenge B 5</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Defeat 1 Relicanth</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Unlocks: Ancient Ruins; Gift: 2 Masterball</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Extra Challenge B 6</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Catch 1 Regirock, Catch 1 Regice, Catch 1 Registeel</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Extra Challenge (Roaming)</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Defeat 1 Latias, Defeat 1 Latios</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 1 Masterball</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Complete challenges: Extra Challenge A 5, Extra Challenge B 6, Extra Challenge (Roaming)</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Unlocks: Nebula Fissure</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Nebula Fissure Challenge</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Defeat 1 Deoxys</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Gift: 1 Masterball</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F253"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -435,7 +435,7 @@
         <v>Poochyena</v>
       </c>
       <c r="E2" t="str">
-        <v>1-1</v>
+        <v>1-4</v>
       </c>
       <c r="F2" t="str">
         <v>45.00%</v>
@@ -455,7 +455,7 @@
         <v>Zigzagoon</v>
       </c>
       <c r="E3" t="str">
-        <v>1-1</v>
+        <v>1-4</v>
       </c>
       <c r="F3" t="str">
         <v>45.00%</v>
@@ -475,7 +475,7 @@
         <v>Wurmple</v>
       </c>
       <c r="E4" t="str">
-        <v>1-1</v>
+        <v>1-4</v>
       </c>
       <c r="F4" t="str">
         <v>10.00%</v>
@@ -495,7 +495,7 @@
         <v>Poochyena</v>
       </c>
       <c r="E5" t="str">
-        <v>1-1</v>
+        <v>2-5</v>
       </c>
       <c r="F5" t="str">
         <v>30.00%</v>
@@ -515,7 +515,7 @@
         <v>Zigzagoon</v>
       </c>
       <c r="E6" t="str">
-        <v>1-1</v>
+        <v>2-5</v>
       </c>
       <c r="F6" t="str">
         <v>25.00%</v>
@@ -535,7 +535,7 @@
         <v>Wingull</v>
       </c>
       <c r="E7" t="str">
-        <v>1-1</v>
+        <v>2-5</v>
       </c>
       <c r="F7" t="str">
         <v>25.00%</v>
@@ -555,7 +555,7 @@
         <v>Tentacool</v>
       </c>
       <c r="E8" t="str">
-        <v>1-1</v>
+        <v>2-5</v>
       </c>
       <c r="F8" t="str">
         <v>10.00%</v>
@@ -575,7 +575,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E9" t="str">
-        <v>1-1</v>
+        <v>2-5</v>
       </c>
       <c r="F9" t="str">
         <v>10.00%</v>
@@ -595,7 +595,7 @@
         <v>Wurmple</v>
       </c>
       <c r="E10" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F10" t="str">
         <v>25.00%</v>
@@ -615,7 +615,7 @@
         <v>Lotad</v>
       </c>
       <c r="E11" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F11" t="str">
         <v>25.00%</v>
@@ -635,7 +635,7 @@
         <v>Seedot</v>
       </c>
       <c r="E12" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F12" t="str">
         <v>20.00%</v>
@@ -655,7 +655,7 @@
         <v>Marill</v>
       </c>
       <c r="E13" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F13" t="str">
         <v>15.00%</v>
@@ -675,7 +675,7 @@
         <v>Ralts</v>
       </c>
       <c r="E14" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F14" t="str">
         <v>10.00%</v>
@@ -695,7 +695,7 @@
         <v>Surskit</v>
       </c>
       <c r="E15" t="str">
-        <v>1-1</v>
+        <v>4-7</v>
       </c>
       <c r="F15" t="str">
         <v>5.00%</v>
@@ -715,7 +715,7 @@
         <v>Poochyena</v>
       </c>
       <c r="E16" t="str">
-        <v>1-1</v>
+        <v>5-8</v>
       </c>
       <c r="F16" t="str">
         <v>25.00%</v>
@@ -735,7 +735,7 @@
         <v>Wurmple</v>
       </c>
       <c r="E17" t="str">
-        <v>1-1</v>
+        <v>5-8</v>
       </c>
       <c r="F17" t="str">
         <v>25.00%</v>
@@ -755,7 +755,7 @@
         <v>Taillow</v>
       </c>
       <c r="E18" t="str">
-        <v>1-1</v>
+        <v>5-8</v>
       </c>
       <c r="F18" t="str">
         <v>20.00%</v>
@@ -775,7 +775,7 @@
         <v>Wingull</v>
       </c>
       <c r="E19" t="str">
-        <v>1-1</v>
+        <v>5-8</v>
       </c>
       <c r="F19" t="str">
         <v>20.00%</v>
@@ -795,7 +795,7 @@
         <v>Pelipper</v>
       </c>
       <c r="E20" t="str">
-        <v>1-1</v>
+        <v>5-8</v>
       </c>
       <c r="F20" t="str">
         <v>10.00%</v>
@@ -815,7 +815,7 @@
         <v>Wurmple</v>
       </c>
       <c r="E21" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F21" t="str">
         <v>30.00%</v>
@@ -835,7 +835,7 @@
         <v>Silcoon</v>
       </c>
       <c r="E22" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F22" t="str">
         <v>20.00%</v>
@@ -855,7 +855,7 @@
         <v>Cascoon</v>
       </c>
       <c r="E23" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F23" t="str">
         <v>20.00%</v>
@@ -875,7 +875,7 @@
         <v>Taillow</v>
       </c>
       <c r="E24" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F24" t="str">
         <v>15.00%</v>
@@ -895,7 +895,7 @@
         <v>Shroomish</v>
       </c>
       <c r="E25" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F25" t="str">
         <v>10.00%</v>
@@ -915,7 +915,7 @@
         <v>Slakoth</v>
       </c>
       <c r="E26" t="str">
-        <v>1-1</v>
+        <v>7-10</v>
       </c>
       <c r="F26" t="str">
         <v>5.00%</v>
@@ -935,10 +935,10 @@
         <v>Poochyena</v>
       </c>
       <c r="E27" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F27" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="28">
@@ -955,10 +955,10 @@
         <v>Taillow</v>
       </c>
       <c r="E28" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F28" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="29">
@@ -975,10 +975,10 @@
         <v>Whismur</v>
       </c>
       <c r="E29" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F29" t="str">
-        <v>20.00%</v>
+        <v>19.00%</v>
       </c>
     </row>
     <row r="30">
@@ -995,10 +995,10 @@
         <v>Nincada</v>
       </c>
       <c r="E30" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F30" t="str">
-        <v>20.00%</v>
+        <v>19.00%</v>
       </c>
     </row>
     <row r="31">
@@ -1015,30 +1015,30 @@
         <v>Skitty</v>
       </c>
       <c r="E31" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F31" t="str">
-        <v>10.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Challenge 7</v>
+        <v>Challenge 5</v>
       </c>
       <c r="B32" t="str">
-        <v>Granite Cave</v>
+        <v>Route 116</v>
       </c>
       <c r="C32" t="str">
         <v/>
       </c>
       <c r="D32" t="str">
-        <v>Zubat</v>
+        <v>Shedinja</v>
       </c>
       <c r="E32" t="str">
-        <v>1-1</v>
+        <v>9-12</v>
       </c>
       <c r="F32" t="str">
-        <v>19.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="33">
@@ -1052,13 +1052,13 @@
         <v/>
       </c>
       <c r="D33" t="str">
-        <v>Makuhita</v>
+        <v>Zubat</v>
       </c>
       <c r="E33" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F33" t="str">
-        <v>15.00%</v>
+        <v>18.05%</v>
       </c>
     </row>
     <row r="34">
@@ -1072,13 +1072,13 @@
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>Geodude</v>
+        <v>Makuhita</v>
       </c>
       <c r="E34" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F34" t="str">
-        <v>15.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="35">
@@ -1092,13 +1092,13 @@
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>Aron</v>
+        <v>Geodude</v>
       </c>
       <c r="E35" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F35" t="str">
-        <v>15.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="36">
@@ -1112,13 +1112,13 @@
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>Abra</v>
+        <v>Aron</v>
       </c>
       <c r="E36" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F36" t="str">
-        <v>15.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="37">
@@ -1132,13 +1132,13 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>Sableye</v>
+        <v>Abra</v>
       </c>
       <c r="E37" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F37" t="str">
-        <v>8.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="38">
@@ -1152,13 +1152,13 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>Mawile</v>
+        <v>Sableye</v>
       </c>
       <c r="E38" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F38" t="str">
-        <v>8.00%</v>
+        <v>7.60%</v>
       </c>
     </row>
     <row r="39">
@@ -1172,53 +1172,53 @@
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>Nosepass</v>
+        <v>Mawile</v>
       </c>
       <c r="E39" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F39" t="str">
-        <v>5.00%</v>
+        <v>7.60%</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Challenge 8</v>
+        <v>Challenge 7</v>
       </c>
       <c r="B40" t="str">
-        <v>Tiny Fishing Spot</v>
+        <v>Granite Cave</v>
       </c>
       <c r="C40" t="str">
         <v/>
       </c>
       <c r="D40" t="str">
-        <v>Magikarp</v>
+        <v>Nosepass</v>
       </c>
       <c r="E40" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F40" t="str">
-        <v>50.00%</v>
+        <v>4.75%</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Challenge 8</v>
+        <v>Challenge 7</v>
       </c>
       <c r="B41" t="str">
-        <v>Tiny Fishing Spot</v>
+        <v>Granite Cave</v>
       </c>
       <c r="C41" t="str">
         <v/>
       </c>
       <c r="D41" t="str">
-        <v>Goldeen</v>
+        <v>Kadabra</v>
       </c>
       <c r="E41" t="str">
-        <v>1-1</v>
+        <v>12-15</v>
       </c>
       <c r="F41" t="str">
-        <v>20.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="42">
@@ -1232,13 +1232,13 @@
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>Tentacool</v>
+        <v>Magikarp</v>
       </c>
       <c r="E42" t="str">
-        <v>1-1</v>
+        <v>14-17</v>
       </c>
       <c r="F42" t="str">
-        <v>20.00%</v>
+        <v>45.00%</v>
       </c>
     </row>
     <row r="43">
@@ -1252,21 +1252,21 @@
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>Surskit</v>
+        <v>Goldeen</v>
       </c>
       <c r="E43" t="str">
-        <v>1-1</v>
+        <v>14-17</v>
       </c>
       <c r="F43" t="str">
-        <v>10.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 8</v>
       </c>
       <c r="B44" t="str">
-        <v>Route 107</v>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="C44" t="str">
         <v/>
@@ -1275,47 +1275,47 @@
         <v>Tentacool</v>
       </c>
       <c r="E44" t="str">
-        <v>1-1</v>
+        <v>14-17</v>
       </c>
       <c r="F44" t="str">
-        <v>50.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 8</v>
       </c>
       <c r="B45" t="str">
-        <v>Route 107</v>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="C45" t="str">
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>Wingull</v>
+        <v>Surskit</v>
       </c>
       <c r="E45" t="str">
-        <v>1-1</v>
+        <v>14-17</v>
       </c>
       <c r="F45" t="str">
-        <v>40.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Challenge 10</v>
+        <v>Challenge 8</v>
       </c>
       <c r="B46" t="str">
-        <v>Route 107</v>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="C46" t="str">
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>Pelipper</v>
+        <v>Staryu</v>
       </c>
       <c r="E46" t="str">
-        <v>1-1</v>
+        <v>14-17</v>
       </c>
       <c r="F46" t="str">
         <v>10.00%</v>
@@ -1323,62 +1323,62 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B47" t="str">
-        <v>Route 110</v>
+        <v>Route 107</v>
       </c>
       <c r="C47" t="str">
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>Electrike</v>
+        <v>Tentacool</v>
       </c>
       <c r="E47" t="str">
-        <v>1-1</v>
+        <v>17-20</v>
       </c>
       <c r="F47" t="str">
-        <v>25.00%</v>
+        <v>50.00%</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B48" t="str">
-        <v>Route 110</v>
+        <v>Route 107</v>
       </c>
       <c r="C48" t="str">
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>Gulpin</v>
+        <v>Wingull</v>
       </c>
       <c r="E48" t="str">
-        <v>1-1</v>
+        <v>17-20</v>
       </c>
       <c r="F48" t="str">
-        <v>15.00%</v>
+        <v>40.00%</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Challenge 12</v>
+        <v>Challenge 10</v>
       </c>
       <c r="B49" t="str">
-        <v>Route 110</v>
+        <v>Route 107</v>
       </c>
       <c r="C49" t="str">
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>Minun</v>
+        <v>Pelipper</v>
       </c>
       <c r="E49" t="str">
-        <v>1-1</v>
+        <v>17-20</v>
       </c>
       <c r="F49" t="str">
-        <v>15.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="50">
@@ -1392,13 +1392,13 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>Plusle</v>
+        <v>Electrike</v>
       </c>
       <c r="E50" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F50" t="str">
-        <v>15.00%</v>
+        <v>22.50%</v>
       </c>
     </row>
     <row r="51">
@@ -1412,13 +1412,13 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>Wingull</v>
+        <v>Gulpin</v>
       </c>
       <c r="E51" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F51" t="str">
-        <v>15.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="52">
@@ -1432,13 +1432,13 @@
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>Oddish</v>
+        <v>Minun</v>
       </c>
       <c r="E52" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F52" t="str">
-        <v>10.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="53">
@@ -1452,93 +1452,93 @@
         <v/>
       </c>
       <c r="D53" t="str">
-        <v>Pelipper</v>
+        <v>Plusle</v>
       </c>
       <c r="E53" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F53" t="str">
-        <v>5.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B54" t="str">
-        <v>Route 117</v>
+        <v>Route 110</v>
       </c>
       <c r="C54" t="str">
         <v/>
       </c>
       <c r="D54" t="str">
-        <v>Oddish</v>
+        <v>Wingull</v>
       </c>
       <c r="E54" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F54" t="str">
-        <v>20.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B55" t="str">
-        <v>Route 117</v>
+        <v>Route 110</v>
       </c>
       <c r="C55" t="str">
         <v/>
       </c>
       <c r="D55" t="str">
-        <v>Marill</v>
+        <v>Oddish</v>
       </c>
       <c r="E55" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F55" t="str">
-        <v>15.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B56" t="str">
-        <v>Route 117</v>
+        <v>Route 110</v>
       </c>
       <c r="C56" t="str">
         <v/>
       </c>
       <c r="D56" t="str">
-        <v>Illumise</v>
+        <v>Pelipper</v>
       </c>
       <c r="E56" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F56" t="str">
-        <v>15.00%</v>
+        <v>4.50%</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Challenge 13</v>
+        <v>Challenge 12</v>
       </c>
       <c r="B57" t="str">
-        <v>Route 117</v>
+        <v>Route 110</v>
       </c>
       <c r="C57" t="str">
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>Volbeat</v>
+        <v>Magnemite</v>
       </c>
       <c r="E57" t="str">
-        <v>1-1</v>
+        <v>20-23</v>
       </c>
       <c r="F57" t="str">
-        <v>15.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="58">
@@ -1552,13 +1552,13 @@
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>Roselia</v>
+        <v>Oddish</v>
       </c>
       <c r="E58" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F58" t="str">
-        <v>15.00%</v>
+        <v>19.00%</v>
       </c>
     </row>
     <row r="59">
@@ -1572,13 +1572,13 @@
         <v/>
       </c>
       <c r="D59" t="str">
-        <v>Seedot</v>
+        <v>Marill</v>
       </c>
       <c r="E59" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F59" t="str">
-        <v>10.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="60">
@@ -1592,230 +1592,230 @@
         <v/>
       </c>
       <c r="D60" t="str">
-        <v>Surskit</v>
+        <v>Illumise</v>
       </c>
       <c r="E60" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F60" t="str">
-        <v>10.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B61" t="str">
-        <v>Route 111</v>
+        <v>Route 117</v>
       </c>
       <c r="C61" t="str">
         <v/>
       </c>
       <c r="D61" t="str">
-        <v>Sandshrew</v>
+        <v>Volbeat</v>
       </c>
       <c r="E61" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F61" t="str">
-        <v>25.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B62" t="str">
-        <v>Route 111</v>
+        <v>Route 117</v>
       </c>
       <c r="C62" t="str">
         <v/>
       </c>
       <c r="D62" t="str">
-        <v>Trapinch</v>
+        <v>Roselia</v>
       </c>
       <c r="E62" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F62" t="str">
-        <v>25.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B63" t="str">
-        <v>Route 111</v>
+        <v>Route 117</v>
       </c>
       <c r="C63" t="str">
         <v/>
       </c>
       <c r="D63" t="str">
-        <v>Geodude</v>
+        <v>Seedot</v>
       </c>
       <c r="E63" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F63" t="str">
-        <v>25.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B64" t="str">
-        <v>Route 111</v>
+        <v>Route 117</v>
       </c>
       <c r="C64" t="str">
         <v/>
       </c>
       <c r="D64" t="str">
-        <v>Cacnea</v>
+        <v>Surskit</v>
       </c>
       <c r="E64" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F64" t="str">
-        <v>15.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Challenge 14</v>
+        <v>Challenge 13</v>
       </c>
       <c r="B65" t="str">
-        <v>Route 111</v>
+        <v>Route 117</v>
       </c>
       <c r="C65" t="str">
         <v/>
       </c>
       <c r="D65" t="str">
-        <v>Baltoy</v>
+        <v>Kirlia</v>
       </c>
       <c r="E65" t="str">
-        <v>1-1</v>
+        <v>22-25</v>
       </c>
       <c r="F65" t="str">
-        <v>10.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B66" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C66" t="str">
         <v/>
       </c>
       <c r="D66" t="str">
-        <v>Numel</v>
+        <v>Sandshrew</v>
       </c>
       <c r="E66" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F66" t="str">
-        <v>30.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B67" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C67" t="str">
         <v/>
       </c>
       <c r="D67" t="str">
-        <v>Machop</v>
+        <v>Trapinch</v>
       </c>
       <c r="E67" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F67" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B68" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C68" t="str">
         <v/>
       </c>
       <c r="D68" t="str">
-        <v>Slugma</v>
+        <v>Geodude</v>
       </c>
       <c r="E68" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F68" t="str">
-        <v>15.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B69" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C69" t="str">
         <v/>
       </c>
       <c r="D69" t="str">
-        <v>Torkoal</v>
+        <v>Cacnea</v>
       </c>
       <c r="E69" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F69" t="str">
-        <v>15.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B70" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C70" t="str">
         <v/>
       </c>
       <c r="D70" t="str">
-        <v>Koffing</v>
+        <v>Baltoy</v>
       </c>
       <c r="E70" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F70" t="str">
-        <v>10.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Challenge 16</v>
+        <v>Challenge 14</v>
       </c>
       <c r="B71" t="str">
-        <v>Fiery Path</v>
+        <v>Route 111</v>
       </c>
       <c r="C71" t="str">
         <v/>
       </c>
       <c r="D71" t="str">
-        <v>Grimer</v>
+        <v>Flygon</v>
       </c>
       <c r="E71" t="str">
-        <v>1-1</v>
+        <v>23-27</v>
       </c>
       <c r="F71" t="str">
         <v>5.00%</v>
@@ -1823,319 +1823,319 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B72" t="str">
-        <v>Jagged Pass</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C72" t="str">
         <v/>
       </c>
       <c r="D72" t="str">
-        <v>Machop</v>
+        <v>Numel</v>
       </c>
       <c r="E72" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F72" t="str">
-        <v>45.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B73" t="str">
-        <v>Jagged Pass</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C73" t="str">
         <v/>
       </c>
       <c r="D73" t="str">
-        <v>Numel</v>
+        <v>Machop</v>
       </c>
       <c r="E73" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F73" t="str">
-        <v>45.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Challenge 17</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B74" t="str">
-        <v>Jagged Pass</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C74" t="str">
         <v/>
       </c>
       <c r="D74" t="str">
-        <v>Spoink</v>
+        <v>Slugma</v>
       </c>
       <c r="E74" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F74" t="str">
-        <v>10.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B75" t="str">
-        <v>Route 113</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C75" t="str">
         <v/>
       </c>
       <c r="D75" t="str">
-        <v>Spinda</v>
+        <v>Torkoal</v>
       </c>
       <c r="E75" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F75" t="str">
-        <v>70.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B76" t="str">
-        <v>Route 113</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C76" t="str">
         <v/>
       </c>
       <c r="D76" t="str">
-        <v>Skarmory</v>
+        <v>Koffing</v>
       </c>
       <c r="E76" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F76" t="str">
-        <v>15.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Challenge 18</v>
+        <v>Challenge 16</v>
       </c>
       <c r="B77" t="str">
-        <v>Route 113</v>
+        <v>Fiery Path</v>
       </c>
       <c r="C77" t="str">
         <v/>
       </c>
       <c r="D77" t="str">
-        <v>Sandshrew</v>
+        <v>Grimer</v>
       </c>
       <c r="E77" t="str">
-        <v>1-1</v>
+        <v>27-30</v>
       </c>
       <c r="F77" t="str">
-        <v>15.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B78" t="str">
-        <v>Route 114</v>
+        <v>Jagged Pass</v>
       </c>
       <c r="C78" t="str">
         <v/>
       </c>
       <c r="D78" t="str">
-        <v>Swablu</v>
+        <v>Machop</v>
       </c>
       <c r="E78" t="str">
-        <v>1-1</v>
+        <v>28-32</v>
       </c>
       <c r="F78" t="str">
-        <v>25.00%</v>
+        <v>42.75%</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B79" t="str">
-        <v>Route 114</v>
+        <v>Jagged Pass</v>
       </c>
       <c r="C79" t="str">
         <v/>
       </c>
       <c r="D79" t="str">
-        <v>Geodude</v>
+        <v>Numel</v>
       </c>
       <c r="E79" t="str">
-        <v>1-1</v>
+        <v>28-32</v>
       </c>
       <c r="F79" t="str">
-        <v>20.00%</v>
+        <v>42.75%</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B80" t="str">
-        <v>Route 114</v>
+        <v>Jagged Pass</v>
       </c>
       <c r="C80" t="str">
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>Lombre</v>
+        <v>Spoink</v>
       </c>
       <c r="E80" t="str">
-        <v>1-1</v>
+        <v>28-32</v>
       </c>
       <c r="F80" t="str">
-        <v>15.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 17</v>
       </c>
       <c r="B81" t="str">
-        <v>Route 114</v>
+        <v>Jagged Pass</v>
       </c>
       <c r="C81" t="str">
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>Nuzleaf</v>
+        <v>Machoke</v>
       </c>
       <c r="E81" t="str">
-        <v>1-1</v>
+        <v>28-32</v>
       </c>
       <c r="F81" t="str">
-        <v>15.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B82" t="str">
-        <v>Route 114</v>
+        <v>Route 113</v>
       </c>
       <c r="C82" t="str">
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>Seviper</v>
+        <v>Spinda</v>
       </c>
       <c r="E82" t="str">
-        <v>1-1</v>
+        <v>30-33</v>
       </c>
       <c r="F82" t="str">
-        <v>10.00%</v>
+        <v>70.00%</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B83" t="str">
-        <v>Route 114</v>
+        <v>Route 113</v>
       </c>
       <c r="C83" t="str">
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>Zangoose</v>
+        <v>Skarmory</v>
       </c>
       <c r="E83" t="str">
-        <v>1-1</v>
+        <v>30-33</v>
       </c>
       <c r="F83" t="str">
-        <v>10.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Challenge 19</v>
+        <v>Challenge 18</v>
       </c>
       <c r="B84" t="str">
-        <v>Route 114</v>
+        <v>Route 113</v>
       </c>
       <c r="C84" t="str">
         <v/>
       </c>
       <c r="D84" t="str">
-        <v>Surskit</v>
+        <v>Sandshrew</v>
       </c>
       <c r="E84" t="str">
-        <v>1-1</v>
+        <v>30-33</v>
       </c>
       <c r="F84" t="str">
-        <v>5.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B85" t="str">
-        <v>Meteor Falls</v>
+        <v>Route 114</v>
       </c>
       <c r="C85" t="str">
         <v/>
       </c>
       <c r="D85" t="str">
-        <v>Zubat</v>
+        <v>Swablu</v>
       </c>
       <c r="E85" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F85" t="str">
-        <v>35.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B86" t="str">
-        <v>Meteor Falls</v>
+        <v>Route 114</v>
       </c>
       <c r="C86" t="str">
         <v/>
       </c>
       <c r="D86" t="str">
-        <v>Golbat</v>
+        <v>Geodude</v>
       </c>
       <c r="E86" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F86" t="str">
-        <v>25.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B87" t="str">
-        <v>Meteor Falls</v>
+        <v>Route 114</v>
       </c>
       <c r="C87" t="str">
         <v/>
       </c>
       <c r="D87" t="str">
-        <v>Solrock</v>
+        <v>Lombre</v>
       </c>
       <c r="E87" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F87" t="str">
         <v>15.00%</v>
@@ -2143,19 +2143,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B88" t="str">
-        <v>Meteor Falls</v>
+        <v>Route 114</v>
       </c>
       <c r="C88" t="str">
         <v/>
       </c>
       <c r="D88" t="str">
-        <v>Lunatone</v>
+        <v>Nuzleaf</v>
       </c>
       <c r="E88" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F88" t="str">
         <v>15.00%</v>
@@ -2163,19 +2163,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Challenge 20</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B89" t="str">
-        <v>Meteor Falls</v>
+        <v>Route 114</v>
       </c>
       <c r="C89" t="str">
         <v/>
       </c>
       <c r="D89" t="str">
-        <v>Bagon</v>
+        <v>Seviper</v>
       </c>
       <c r="E89" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F89" t="str">
         <v>10.00%</v>
@@ -2183,239 +2183,239 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Challenge 21</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B90" t="str">
-        <v>Route 115</v>
+        <v>Route 114</v>
       </c>
       <c r="C90" t="str">
         <v/>
       </c>
       <c r="D90" t="str">
-        <v>Swablu</v>
+        <v>Zangoose</v>
       </c>
       <c r="E90" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F90" t="str">
-        <v>30.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Challenge 21</v>
+        <v>Challenge 19</v>
       </c>
       <c r="B91" t="str">
-        <v>Route 115</v>
+        <v>Route 114</v>
       </c>
       <c r="C91" t="str">
         <v/>
       </c>
       <c r="D91" t="str">
-        <v>Taillow</v>
+        <v>Surskit</v>
       </c>
       <c r="E91" t="str">
-        <v>1-1</v>
+        <v>31-35</v>
       </c>
       <c r="F91" t="str">
-        <v>25.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Challenge 21</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B92" t="str">
-        <v>Route 115</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C92" t="str">
         <v/>
       </c>
       <c r="D92" t="str">
-        <v>Wingull</v>
+        <v>Zubat</v>
       </c>
       <c r="E92" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F92" t="str">
-        <v>25.00%</v>
+        <v>33.25%</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Challenge 21</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B93" t="str">
-        <v>Route 115</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C93" t="str">
         <v/>
       </c>
       <c r="D93" t="str">
-        <v>Jigglypuff</v>
+        <v>Golbat</v>
       </c>
       <c r="E93" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F93" t="str">
-        <v>10.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Challenge 21</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B94" t="str">
-        <v>Route 115</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C94" t="str">
         <v/>
       </c>
       <c r="D94" t="str">
-        <v>Pelipper</v>
+        <v>Solrock</v>
       </c>
       <c r="E94" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F94" t="str">
-        <v>10.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B95" t="str">
-        <v>Route 118</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C95" t="str">
         <v/>
       </c>
       <c r="D95" t="str">
-        <v>Electrike</v>
+        <v>Lunatone</v>
       </c>
       <c r="E95" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F95" t="str">
-        <v>25.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B96" t="str">
-        <v>Route 118</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C96" t="str">
         <v/>
       </c>
       <c r="D96" t="str">
-        <v>Linoone</v>
+        <v>Bagon</v>
       </c>
       <c r="E96" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F96" t="str">
-        <v>20.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 20</v>
       </c>
       <c r="B97" t="str">
-        <v>Route 118</v>
+        <v>Meteor Falls</v>
       </c>
       <c r="C97" t="str">
         <v/>
       </c>
       <c r="D97" t="str">
-        <v>Wingull</v>
+        <v>Beldum</v>
       </c>
       <c r="E97" t="str">
-        <v>1-1</v>
+        <v>33-37</v>
       </c>
       <c r="F97" t="str">
-        <v>20.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 21</v>
       </c>
       <c r="B98" t="str">
-        <v>Route 118</v>
+        <v>Route 115</v>
       </c>
       <c r="C98" t="str">
         <v/>
       </c>
       <c r="D98" t="str">
-        <v>Manectric</v>
+        <v>Swablu</v>
       </c>
       <c r="E98" t="str">
-        <v>1-1</v>
+        <v>35-38</v>
       </c>
       <c r="F98" t="str">
-        <v>15.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 21</v>
       </c>
       <c r="B99" t="str">
-        <v>Route 118</v>
+        <v>Route 115</v>
       </c>
       <c r="C99" t="str">
         <v/>
       </c>
       <c r="D99" t="str">
-        <v>Kecleon</v>
+        <v>Taillow</v>
       </c>
       <c r="E99" t="str">
-        <v>1-1</v>
+        <v>35-38</v>
       </c>
       <c r="F99" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Challenge 23</v>
+        <v>Challenge 21</v>
       </c>
       <c r="B100" t="str">
-        <v>Route 118</v>
+        <v>Route 115</v>
       </c>
       <c r="C100" t="str">
         <v/>
       </c>
       <c r="D100" t="str">
-        <v>Pelipper</v>
+        <v>Wingull</v>
       </c>
       <c r="E100" t="str">
-        <v>1-1</v>
+        <v>35-38</v>
       </c>
       <c r="F100" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 21</v>
       </c>
       <c r="B101" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 115</v>
       </c>
       <c r="C101" t="str">
         <v/>
       </c>
       <c r="D101" t="str">
-        <v>Carvanha</v>
+        <v>Jigglypuff</v>
       </c>
       <c r="E101" t="str">
-        <v>1-1</v>
+        <v>35-38</v>
       </c>
       <c r="F101" t="str">
         <v>10.00%</v>
@@ -2423,79 +2423,79 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 21</v>
       </c>
       <c r="B102" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 115</v>
       </c>
       <c r="C102" t="str">
         <v/>
       </c>
       <c r="D102" t="str">
-        <v>Barboach</v>
+        <v>Pelipper</v>
       </c>
       <c r="E102" t="str">
-        <v>1-1</v>
+        <v>35-38</v>
       </c>
       <c r="F102" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B103" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 118</v>
       </c>
       <c r="C103" t="str">
         <v/>
       </c>
       <c r="D103" t="str">
-        <v>Corphish</v>
+        <v>Electrike</v>
       </c>
       <c r="E103" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F103" t="str">
-        <v>20.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B104" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 118</v>
       </c>
       <c r="C104" t="str">
         <v/>
       </c>
       <c r="D104" t="str">
-        <v>Wailmer</v>
+        <v>Linoone</v>
       </c>
       <c r="E104" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F104" t="str">
-        <v>10.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B105" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 118</v>
       </c>
       <c r="C105" t="str">
         <v/>
       </c>
       <c r="D105" t="str">
-        <v>Goldeen</v>
+        <v>Wingull</v>
       </c>
       <c r="E105" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F105" t="str">
         <v>20.00%</v>
@@ -2503,559 +2503,559 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Challenge 24</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B106" t="str">
-        <v>Small Fishing Spot</v>
+        <v>Route 118</v>
       </c>
       <c r="C106" t="str">
         <v/>
       </c>
       <c r="D106" t="str">
-        <v>Tentacool</v>
+        <v>Manectric</v>
       </c>
       <c r="E106" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F106" t="str">
-        <v>20.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B107" t="str">
-        <v>Route 119</v>
+        <v>Route 118</v>
       </c>
       <c r="C107" t="str">
         <v/>
       </c>
       <c r="D107" t="str">
-        <v>Linoone</v>
+        <v>Kecleon</v>
       </c>
       <c r="E107" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F107" t="str">
-        <v>30.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 23</v>
       </c>
       <c r="B108" t="str">
-        <v>Route 119</v>
+        <v>Route 118</v>
       </c>
       <c r="C108" t="str">
         <v/>
       </c>
       <c r="D108" t="str">
-        <v>Oddish</v>
+        <v>Pelipper</v>
       </c>
       <c r="E108" t="str">
-        <v>1-1</v>
+        <v>38-41</v>
       </c>
       <c r="F108" t="str">
-        <v>30.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B109" t="str">
-        <v>Route 119</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C109" t="str">
         <v/>
       </c>
       <c r="D109" t="str">
-        <v>Tropius</v>
+        <v>Carvanha</v>
       </c>
       <c r="E109" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F109" t="str">
-        <v>15.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B110" t="str">
-        <v>Route 119</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C110" t="str">
         <v/>
       </c>
       <c r="D110" t="str">
-        <v>Wingull</v>
+        <v>Barboach</v>
       </c>
       <c r="E110" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F110" t="str">
-        <v>10.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B111" t="str">
-        <v>Route 119</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C111" t="str">
         <v/>
       </c>
       <c r="D111" t="str">
-        <v>Kecleon</v>
+        <v>Corphish</v>
       </c>
       <c r="E111" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F111" t="str">
-        <v>10.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Challenge 25</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B112" t="str">
-        <v>Route 119</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C112" t="str">
         <v/>
       </c>
       <c r="D112" t="str">
-        <v>Pelipper</v>
+        <v>Wailmer</v>
       </c>
       <c r="E112" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F112" t="str">
-        <v>5.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B113" t="str">
-        <v>Route 120</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C113" t="str">
         <v/>
       </c>
       <c r="D113" t="str">
-        <v>Linoone</v>
+        <v>Goldeen</v>
       </c>
       <c r="E113" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F113" t="str">
-        <v>25.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B114" t="str">
-        <v>Route 120</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C114" t="str">
         <v/>
       </c>
       <c r="D114" t="str">
-        <v>Mightyena</v>
+        <v>Tentacool</v>
       </c>
       <c r="E114" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F114" t="str">
-        <v>20.00%</v>
+        <v>18.00%</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 24</v>
       </c>
       <c r="B115" t="str">
-        <v>Route 120</v>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="C115" t="str">
         <v/>
       </c>
       <c r="D115" t="str">
-        <v>Oddish</v>
+        <v>Luvdisc</v>
       </c>
       <c r="E115" t="str">
-        <v>1-1</v>
+        <v>40-43</v>
       </c>
       <c r="F115" t="str">
-        <v>15.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B116" t="str">
-        <v>Route 120</v>
+        <v>Route 119</v>
       </c>
       <c r="C116" t="str">
         <v/>
       </c>
       <c r="D116" t="str">
-        <v>Marill</v>
+        <v>Linoone</v>
       </c>
       <c r="E116" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F116" t="str">
-        <v>15.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B117" t="str">
-        <v>Route 120</v>
+        <v>Route 119</v>
       </c>
       <c r="C117" t="str">
         <v/>
       </c>
       <c r="D117" t="str">
-        <v>Absol</v>
+        <v>Oddish</v>
       </c>
       <c r="E117" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F117" t="str">
-        <v>10.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B118" t="str">
-        <v>Route 120</v>
+        <v>Route 119</v>
       </c>
       <c r="C118" t="str">
         <v/>
       </c>
       <c r="D118" t="str">
-        <v>Kecleon</v>
+        <v>Tropius</v>
       </c>
       <c r="E118" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F118" t="str">
-        <v>10.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Challenge 26</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B119" t="str">
-        <v>Route 120</v>
+        <v>Route 119</v>
       </c>
       <c r="C119" t="str">
         <v/>
       </c>
       <c r="D119" t="str">
-        <v>Surskit</v>
+        <v>Wingull</v>
       </c>
       <c r="E119" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F119" t="str">
-        <v>5.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B120" t="str">
-        <v>Route 121</v>
+        <v>Route 119</v>
       </c>
       <c r="C120" t="str">
         <v/>
       </c>
       <c r="D120" t="str">
-        <v>Poochyena</v>
+        <v>Kecleon</v>
       </c>
       <c r="E120" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F120" t="str">
-        <v>20.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 25</v>
       </c>
       <c r="B121" t="str">
-        <v>Route 121</v>
+        <v>Route 119</v>
       </c>
       <c r="C121" t="str">
         <v/>
       </c>
       <c r="D121" t="str">
-        <v>Mightyena</v>
+        <v>Pelipper</v>
       </c>
       <c r="E121" t="str">
-        <v>1-1</v>
+        <v>41-45</v>
       </c>
       <c r="F121" t="str">
-        <v>25.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B122" t="str">
-        <v>Route 121</v>
+        <v>Route 120</v>
       </c>
       <c r="C122" t="str">
         <v/>
       </c>
       <c r="D122" t="str">
-        <v>Shuppet</v>
+        <v>Linoone</v>
       </c>
       <c r="E122" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F122" t="str">
-        <v>20.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B123" t="str">
-        <v>Route 121</v>
+        <v>Route 120</v>
       </c>
       <c r="C123" t="str">
         <v/>
       </c>
       <c r="D123" t="str">
-        <v>Duskull</v>
+        <v>Mightyena</v>
       </c>
       <c r="E123" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F123" t="str">
-        <v>15.00%</v>
+        <v>19.00%</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B124" t="str">
-        <v>Route 121</v>
+        <v>Route 120</v>
       </c>
       <c r="C124" t="str">
         <v/>
       </c>
       <c r="D124" t="str">
-        <v>Gloom</v>
+        <v>Oddish</v>
       </c>
       <c r="E124" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F124" t="str">
-        <v>10.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Challenge 27</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B125" t="str">
-        <v>Route 121</v>
+        <v>Route 120</v>
       </c>
       <c r="C125" t="str">
         <v/>
       </c>
       <c r="D125" t="str">
-        <v>Kecleon</v>
+        <v>Marill</v>
       </c>
       <c r="E125" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F125" t="str">
-        <v>10.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B126" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 120</v>
       </c>
       <c r="C126" t="str">
         <v/>
       </c>
       <c r="D126" t="str">
-        <v>Pikachu</v>
+        <v>Absol</v>
       </c>
       <c r="E126" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F126" t="str">
-        <v>15.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B127" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 120</v>
       </c>
       <c r="C127" t="str">
         <v/>
       </c>
       <c r="D127" t="str">
-        <v>Natu</v>
+        <v>Kecleon</v>
       </c>
       <c r="E127" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F127" t="str">
-        <v>15.00%</v>
+        <v>9.50%</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B128" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 120</v>
       </c>
       <c r="C128" t="str">
         <v/>
       </c>
       <c r="D128" t="str">
-        <v>Pinsir</v>
+        <v>Surskit</v>
       </c>
       <c r="E128" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F128" t="str">
-        <v>8.00%</v>
+        <v>4.75%</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 26</v>
       </c>
       <c r="B129" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 120</v>
       </c>
       <c r="C129" t="str">
         <v/>
       </c>
       <c r="D129" t="str">
-        <v>Phanpy</v>
+        <v>Masquerain</v>
       </c>
       <c r="E129" t="str">
-        <v>1-1</v>
+        <v>43-46</v>
       </c>
       <c r="F129" t="str">
-        <v>7.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B130" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 121</v>
       </c>
       <c r="C130" t="str">
         <v/>
       </c>
       <c r="D130" t="str">
-        <v>Geodude</v>
+        <v>Poochyena</v>
       </c>
       <c r="E130" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F130" t="str">
-        <v>11.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B131" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 121</v>
       </c>
       <c r="C131" t="str">
         <v/>
       </c>
       <c r="D131" t="str">
-        <v>Aipom</v>
+        <v>Mightyena</v>
       </c>
       <c r="E131" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F131" t="str">
-        <v>10.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B132" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 121</v>
       </c>
       <c r="C132" t="str">
         <v/>
       </c>
       <c r="D132" t="str">
-        <v>Houndour</v>
+        <v>Shuppet</v>
       </c>
       <c r="E132" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F132" t="str">
-        <v>9.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B133" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 121</v>
       </c>
       <c r="C133" t="str">
         <v/>
       </c>
       <c r="D133" t="str">
-        <v>Sunkern</v>
+        <v>Duskull</v>
       </c>
       <c r="E133" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F133" t="str">
         <v>15.00%</v>
@@ -3063,19 +3063,19 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B134" t="str">
-        <v>Safari Zone East</v>
+        <v>Route 121</v>
       </c>
       <c r="C134" t="str">
         <v/>
       </c>
       <c r="D134" t="str">
-        <v>Shuckle</v>
+        <v>Gloom</v>
       </c>
       <c r="E134" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F134" t="str">
         <v>10.00%</v>
@@ -3083,22 +3083,22 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Challenge 28</v>
+        <v>Challenge 27</v>
       </c>
       <c r="B135" t="str">
-        <v>Safari Zone West</v>
+        <v>Route 121</v>
       </c>
       <c r="C135" t="str">
         <v/>
       </c>
       <c r="D135" t="str">
-        <v>Doduo</v>
+        <v>Kecleon</v>
       </c>
       <c r="E135" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F135" t="str">
-        <v>12.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="136">
@@ -3106,19 +3106,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B136" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C136" t="str">
         <v/>
       </c>
       <c r="D136" t="str">
-        <v>Rhyhorn</v>
+        <v>Pikachu</v>
       </c>
       <c r="E136" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F136" t="str">
-        <v>8.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="137">
@@ -3126,19 +3126,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B137" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C137" t="str">
         <v/>
       </c>
       <c r="D137" t="str">
-        <v>Girafarig</v>
+        <v>Natu</v>
       </c>
       <c r="E137" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F137" t="str">
-        <v>8.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="138">
@@ -3146,19 +3146,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B138" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C138" t="str">
         <v/>
       </c>
       <c r="D138" t="str">
-        <v>Psyduck</v>
+        <v>Pinsir</v>
       </c>
       <c r="E138" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F138" t="str">
-        <v>12.00%</v>
+        <v>8.00%</v>
       </c>
     </row>
     <row r="139">
@@ -3166,19 +3166,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B139" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C139" t="str">
         <v/>
       </c>
       <c r="D139" t="str">
-        <v>Xatu</v>
+        <v>Phanpy</v>
       </c>
       <c r="E139" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F139" t="str">
-        <v>12.00%</v>
+        <v>7.00%</v>
       </c>
     </row>
     <row r="140">
@@ -3186,19 +3186,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B140" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C140" t="str">
         <v/>
       </c>
       <c r="D140" t="str">
-        <v>Teddiursa</v>
+        <v>Geodude</v>
       </c>
       <c r="E140" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F140" t="str">
-        <v>8.00%</v>
+        <v>11.00%</v>
       </c>
     </row>
     <row r="141">
@@ -3206,16 +3206,16 @@
         <v>Challenge 28</v>
       </c>
       <c r="B141" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C141" t="str">
         <v/>
       </c>
       <c r="D141" t="str">
-        <v>Stantler</v>
+        <v>Aipom</v>
       </c>
       <c r="E141" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F141" t="str">
         <v>10.00%</v>
@@ -3226,19 +3226,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B142" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C142" t="str">
         <v/>
       </c>
       <c r="D142" t="str">
-        <v>Wooper</v>
+        <v>Houndour</v>
       </c>
       <c r="E142" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F142" t="str">
-        <v>10.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="143">
@@ -3246,19 +3246,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B143" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C143" t="str">
         <v/>
       </c>
       <c r="D143" t="str">
-        <v>Ledyba</v>
+        <v>Sunkern</v>
       </c>
       <c r="E143" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F143" t="str">
-        <v>11.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="144">
@@ -3266,19 +3266,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B144" t="str">
-        <v>Safari Zone West</v>
+        <v>Safari Zone East</v>
       </c>
       <c r="C144" t="str">
         <v/>
       </c>
       <c r="D144" t="str">
-        <v>Gloom</v>
+        <v>Shuckle</v>
       </c>
       <c r="E144" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F144" t="str">
-        <v>9.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="145">
@@ -3286,19 +3286,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B145" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C145" t="str">
         <v/>
       </c>
       <c r="D145" t="str">
-        <v>Heracross</v>
+        <v>Doduo</v>
       </c>
       <c r="E145" t="str">
         <v>1-1</v>
       </c>
       <c r="F145" t="str">
-        <v>16.00%</v>
+        <v>12.00%</v>
       </c>
     </row>
     <row r="146">
@@ -3306,19 +3306,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B146" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C146" t="str">
         <v/>
       </c>
       <c r="D146" t="str">
-        <v>Wobbuffet</v>
+        <v>Rhyhorn</v>
       </c>
       <c r="E146" t="str">
         <v>1-1</v>
       </c>
       <c r="F146" t="str">
-        <v>16.00%</v>
+        <v>8.00%</v>
       </c>
     </row>
     <row r="147">
@@ -3326,19 +3326,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B147" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C147" t="str">
         <v/>
       </c>
       <c r="D147" t="str">
-        <v>Golduck</v>
+        <v>Girafarig</v>
       </c>
       <c r="E147" t="str">
         <v>1-1</v>
       </c>
       <c r="F147" t="str">
-        <v>12.00%</v>
+        <v>8.00%</v>
       </c>
     </row>
     <row r="148">
@@ -3346,13 +3346,13 @@
         <v>Challenge 28</v>
       </c>
       <c r="B148" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C148" t="str">
         <v/>
       </c>
       <c r="D148" t="str">
-        <v>Mareep</v>
+        <v>Psyduck</v>
       </c>
       <c r="E148" t="str">
         <v>1-1</v>
@@ -3366,19 +3366,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B149" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C149" t="str">
         <v/>
       </c>
       <c r="D149" t="str">
-        <v>Gligar</v>
+        <v>Xatu</v>
       </c>
       <c r="E149" t="str">
         <v>1-1</v>
       </c>
       <c r="F149" t="str">
-        <v>13.00%</v>
+        <v>12.00%</v>
       </c>
     </row>
     <row r="150">
@@ -3386,19 +3386,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B150" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C150" t="str">
         <v/>
       </c>
       <c r="D150" t="str">
-        <v>Pineco</v>
+        <v>Teddiursa</v>
       </c>
       <c r="E150" t="str">
         <v>1-1</v>
       </c>
       <c r="F150" t="str">
-        <v>9.00%</v>
+        <v>8.00%</v>
       </c>
     </row>
     <row r="151">
@@ -3406,19 +3406,19 @@
         <v>Challenge 28</v>
       </c>
       <c r="B151" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C151" t="str">
         <v/>
       </c>
       <c r="D151" t="str">
-        <v>Quagsire</v>
+        <v>Stantler</v>
       </c>
       <c r="E151" t="str">
         <v>1-1</v>
       </c>
       <c r="F151" t="str">
-        <v>13.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="152">
@@ -3426,296 +3426,296 @@
         <v>Challenge 28</v>
       </c>
       <c r="B152" t="str">
-        <v>Safari Zone North</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C152" t="str">
         <v/>
       </c>
       <c r="D152" t="str">
-        <v>Spinarak</v>
+        <v>Wooper</v>
       </c>
       <c r="E152" t="str">
         <v>1-1</v>
       </c>
       <c r="F152" t="str">
-        <v>9.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B153" t="str">
-        <v>Mount Pyre</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C153" t="str">
         <v/>
       </c>
       <c r="D153" t="str">
-        <v>Shuppet</v>
+        <v>Ledyba</v>
       </c>
       <c r="E153" t="str">
         <v>1-1</v>
       </c>
       <c r="F153" t="str">
-        <v>30.00%</v>
+        <v>11.00%</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B154" t="str">
-        <v>Mount Pyre</v>
+        <v>Safari Zone West</v>
       </c>
       <c r="C154" t="str">
         <v/>
       </c>
       <c r="D154" t="str">
-        <v>Duskull</v>
+        <v>Gloom</v>
       </c>
       <c r="E154" t="str">
         <v>1-1</v>
       </c>
       <c r="F154" t="str">
-        <v>25.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B155" t="str">
-        <v>Mount Pyre</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C155" t="str">
         <v/>
       </c>
       <c r="D155" t="str">
-        <v>Vulpix</v>
+        <v>Heracross</v>
       </c>
       <c r="E155" t="str">
         <v>1-1</v>
       </c>
       <c r="F155" t="str">
-        <v>20.00%</v>
+        <v>16.00%</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B156" t="str">
-        <v>Mount Pyre</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C156" t="str">
         <v/>
       </c>
       <c r="D156" t="str">
-        <v>Meditite</v>
+        <v>Wobbuffet</v>
       </c>
       <c r="E156" t="str">
         <v>1-1</v>
       </c>
       <c r="F156" t="str">
-        <v>15.00%</v>
+        <v>16.00%</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Challenge 29</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B157" t="str">
-        <v>Mount Pyre</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C157" t="str">
         <v/>
       </c>
       <c r="D157" t="str">
-        <v>Chimecho</v>
+        <v>Golduck</v>
       </c>
       <c r="E157" t="str">
         <v>1-1</v>
       </c>
       <c r="F157" t="str">
-        <v>10.00%</v>
+        <v>12.00%</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B158" t="str">
-        <v>Route 123</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C158" t="str">
         <v/>
       </c>
       <c r="D158" t="str">
-        <v>Mightyena</v>
+        <v>Mareep</v>
       </c>
       <c r="E158" t="str">
         <v>1-1</v>
       </c>
       <c r="F158" t="str">
-        <v>30.00%</v>
+        <v>12.00%</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B159" t="str">
-        <v>Route 123</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C159" t="str">
         <v/>
       </c>
       <c r="D159" t="str">
-        <v>Shuppet</v>
+        <v>Gligar</v>
       </c>
       <c r="E159" t="str">
         <v>1-1</v>
       </c>
       <c r="F159" t="str">
-        <v>25.00%</v>
+        <v>13.00%</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B160" t="str">
-        <v>Route 123</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C160" t="str">
         <v/>
       </c>
       <c r="D160" t="str">
-        <v>Duskull</v>
+        <v>Pineco</v>
       </c>
       <c r="E160" t="str">
         <v>1-1</v>
       </c>
       <c r="F160" t="str">
-        <v>20.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B161" t="str">
-        <v>Route 123</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C161" t="str">
         <v/>
       </c>
       <c r="D161" t="str">
-        <v>Gloom</v>
+        <v>Quagsire</v>
       </c>
       <c r="E161" t="str">
         <v>1-1</v>
       </c>
       <c r="F161" t="str">
-        <v>15.00%</v>
+        <v>13.00%</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Challenge 30</v>
+        <v>Challenge 28</v>
       </c>
       <c r="B162" t="str">
-        <v>Route 123</v>
+        <v>Safari Zone North</v>
       </c>
       <c r="C162" t="str">
         <v/>
       </c>
       <c r="D162" t="str">
-        <v>Kecleon</v>
+        <v>Spinarak</v>
       </c>
       <c r="E162" t="str">
         <v>1-1</v>
       </c>
       <c r="F162" t="str">
-        <v>10.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B163" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Mount Pyre</v>
       </c>
       <c r="C163" t="str">
         <v/>
       </c>
       <c r="D163" t="str">
-        <v>Wailmer</v>
+        <v>Shuppet</v>
       </c>
       <c r="E163" t="str">
-        <v>1-1</v>
+        <v>48-51</v>
       </c>
       <c r="F163" t="str">
-        <v>22.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B164" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Mount Pyre</v>
       </c>
       <c r="C164" t="str">
         <v/>
       </c>
       <c r="D164" t="str">
-        <v>Sharpedo</v>
+        <v>Duskull</v>
       </c>
       <c r="E164" t="str">
-        <v>1-1</v>
+        <v>48-51</v>
       </c>
       <c r="F164" t="str">
-        <v>22.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B165" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Mount Pyre</v>
       </c>
       <c r="C165" t="str">
         <v/>
       </c>
       <c r="D165" t="str">
-        <v>Seaking</v>
+        <v>Vulpix</v>
       </c>
       <c r="E165" t="str">
-        <v>1-1</v>
+        <v>48-51</v>
       </c>
       <c r="F165" t="str">
-        <v>15.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B166" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Mount Pyre</v>
       </c>
       <c r="C166" t="str">
         <v/>
       </c>
       <c r="D166" t="str">
-        <v>Whiscash</v>
+        <v>Meditite</v>
       </c>
       <c r="E166" t="str">
-        <v>1-1</v>
+        <v>48-51</v>
       </c>
       <c r="F166" t="str">
         <v>15.00%</v>
@@ -3723,19 +3723,19 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 29</v>
       </c>
       <c r="B167" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Mount Pyre</v>
       </c>
       <c r="C167" t="str">
         <v/>
       </c>
       <c r="D167" t="str">
-        <v>Corsola</v>
+        <v>Chimecho</v>
       </c>
       <c r="E167" t="str">
-        <v>1-1</v>
+        <v>48-51</v>
       </c>
       <c r="F167" t="str">
         <v>10.00%</v>
@@ -3743,99 +3743,99 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B168" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 123</v>
       </c>
       <c r="C168" t="str">
         <v/>
       </c>
       <c r="D168" t="str">
-        <v>Tentacruel</v>
+        <v>Mightyena</v>
       </c>
       <c r="E168" t="str">
-        <v>1-1</v>
+        <v>49-53</v>
       </c>
       <c r="F168" t="str">
-        <v>8.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Challenge 33</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B169" t="str">
-        <v>Big Fishing Spot</v>
+        <v>Route 123</v>
       </c>
       <c r="C169" t="str">
         <v/>
       </c>
       <c r="D169" t="str">
-        <v>Feebas</v>
+        <v>Shuppet</v>
       </c>
       <c r="E169" t="str">
-        <v>1-1</v>
+        <v>49-53</v>
       </c>
       <c r="F169" t="str">
-        <v>8.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B170" t="str">
-        <v>Underwater Fishing Spot</v>
+        <v>Route 123</v>
       </c>
       <c r="C170" t="str">
         <v/>
       </c>
       <c r="D170" t="str">
-        <v>Clamperl</v>
+        <v>Duskull</v>
       </c>
       <c r="E170" t="str">
-        <v>1-1</v>
+        <v>49-53</v>
       </c>
       <c r="F170" t="str">
-        <v>65.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B171" t="str">
-        <v>Underwater Fishing Spot</v>
+        <v>Route 123</v>
       </c>
       <c r="C171" t="str">
         <v/>
       </c>
       <c r="D171" t="str">
-        <v>Chinchou</v>
+        <v>Gloom</v>
       </c>
       <c r="E171" t="str">
-        <v>1-1</v>
+        <v>49-53</v>
       </c>
       <c r="F171" t="str">
-        <v>25.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Challenge 34</v>
+        <v>Challenge 30</v>
       </c>
       <c r="B172" t="str">
-        <v>Underwater Fishing Spot</v>
+        <v>Route 123</v>
       </c>
       <c r="C172" t="str">
         <v/>
       </c>
       <c r="D172" t="str">
-        <v>Relicanth</v>
+        <v>Kecleon</v>
       </c>
       <c r="E172" t="str">
-        <v>1-1</v>
+        <v>49-53</v>
       </c>
       <c r="F172" t="str">
         <v>10.00%</v>
@@ -3843,619 +3843,619 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B173" t="str">
-        <v>Shoal Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C173" t="str">
         <v/>
       </c>
       <c r="D173" t="str">
-        <v>Spheal</v>
+        <v>Wailmer</v>
       </c>
       <c r="E173" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F173" t="str">
-        <v>45.00%</v>
+        <v>19.80%</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B174" t="str">
-        <v>Shoal Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C174" t="str">
         <v/>
       </c>
       <c r="D174" t="str">
-        <v>Zubat</v>
+        <v>Sharpedo</v>
       </c>
       <c r="E174" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F174" t="str">
-        <v>30.00%</v>
+        <v>19.80%</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B175" t="str">
-        <v>Shoal Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C175" t="str">
         <v/>
       </c>
       <c r="D175" t="str">
-        <v>Golbat</v>
+        <v>Seaking</v>
       </c>
       <c r="E175" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F175" t="str">
-        <v>15.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Challenge 36</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B176" t="str">
-        <v>Shoal Cave</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C176" t="str">
         <v/>
       </c>
       <c r="D176" t="str">
-        <v>Snorunt</v>
+        <v>Whiscash</v>
       </c>
       <c r="E176" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F176" t="str">
-        <v>10.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Challenge 37</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B177" t="str">
-        <v>Mirage Island</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C177" t="str">
         <v/>
       </c>
       <c r="D177" t="str">
-        <v>Wynaut</v>
+        <v>Corsola</v>
       </c>
       <c r="E177" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F177" t="str">
-        <v>100.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B178" t="str">
-        <v>Victory Road</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C178" t="str">
         <v/>
       </c>
       <c r="D178" t="str">
-        <v>Golbat</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E178" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F178" t="str">
-        <v>25.00%</v>
+        <v>7.20%</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B179" t="str">
-        <v>Victory Road</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C179" t="str">
         <v/>
       </c>
       <c r="D179" t="str">
-        <v>Hariyama</v>
+        <v>Feebas</v>
       </c>
       <c r="E179" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F179" t="str">
-        <v>25.00%</v>
+        <v>7.20%</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 33</v>
       </c>
       <c r="B180" t="str">
-        <v>Victory Road</v>
+        <v>Big Fishing Spot</v>
       </c>
       <c r="C180" t="str">
         <v/>
       </c>
       <c r="D180" t="str">
-        <v>Lairon</v>
+        <v>Horsea</v>
       </c>
       <c r="E180" t="str">
-        <v>1-1</v>
+        <v>54-58</v>
       </c>
       <c r="F180" t="str">
-        <v>16.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B181" t="str">
-        <v>Victory Road</v>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="C181" t="str">
         <v/>
       </c>
       <c r="D181" t="str">
-        <v>Medicham</v>
+        <v>Clamperl</v>
       </c>
       <c r="E181" t="str">
-        <v>1-1</v>
+        <v>56-60</v>
       </c>
       <c r="F181" t="str">
-        <v>16.00%</v>
+        <v>58.50%</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B182" t="str">
-        <v>Victory Road</v>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="C182" t="str">
         <v/>
       </c>
       <c r="D182" t="str">
-        <v>Loudred</v>
+        <v>Chinchou</v>
       </c>
       <c r="E182" t="str">
-        <v>1-1</v>
+        <v>56-60</v>
       </c>
       <c r="F182" t="str">
-        <v>12.00%</v>
+        <v>22.50%</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Challenge 42</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B183" t="str">
-        <v>Victory Road</v>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="C183" t="str">
         <v/>
       </c>
       <c r="D183" t="str">
-        <v>Graveler</v>
+        <v>Relicanth</v>
       </c>
       <c r="E183" t="str">
-        <v>1-1</v>
+        <v>56-60</v>
       </c>
       <c r="F183" t="str">
-        <v>6.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 34</v>
       </c>
       <c r="B184" t="str">
-        <v>Sky Pillar</v>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="C184" t="str">
         <v/>
       </c>
       <c r="D184" t="str">
-        <v>Golbat</v>
+        <v>Seadra</v>
       </c>
       <c r="E184" t="str">
-        <v>1-1</v>
+        <v>56-60</v>
       </c>
       <c r="F184" t="str">
-        <v>30.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B185" t="str">
-        <v>Sky Pillar</v>
+        <v>Shoal Cave</v>
       </c>
       <c r="C185" t="str">
         <v/>
       </c>
       <c r="D185" t="str">
-        <v>Claydol</v>
+        <v>Spheal</v>
       </c>
       <c r="E185" t="str">
-        <v>1-1</v>
+        <v>59-63</v>
       </c>
       <c r="F185" t="str">
-        <v>25.00%</v>
+        <v>40.50%</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B186" t="str">
-        <v>Sky Pillar</v>
+        <v>Shoal Cave</v>
       </c>
       <c r="C186" t="str">
         <v/>
       </c>
       <c r="D186" t="str">
-        <v>Altaria</v>
+        <v>Zubat</v>
       </c>
       <c r="E186" t="str">
-        <v>1-1</v>
+        <v>59-63</v>
       </c>
       <c r="F186" t="str">
-        <v>20.00%</v>
+        <v>27.00%</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B187" t="str">
-        <v>Sky Pillar</v>
+        <v>Shoal Cave</v>
       </c>
       <c r="C187" t="str">
         <v/>
       </c>
       <c r="D187" t="str">
-        <v>Dusclops</v>
+        <v>Golbat</v>
       </c>
       <c r="E187" t="str">
-        <v>1-1</v>
+        <v>59-63</v>
       </c>
       <c r="F187" t="str">
-        <v>15.00%</v>
+        <v>13.50%</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Challenge 41</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B188" t="str">
-        <v>Sky Pillar</v>
+        <v>Shoal Cave</v>
       </c>
       <c r="C188" t="str">
         <v/>
       </c>
       <c r="D188" t="str">
-        <v>Banette</v>
+        <v>Snorunt</v>
       </c>
       <c r="E188" t="str">
-        <v>1-1</v>
+        <v>59-63</v>
       </c>
       <c r="F188" t="str">
-        <v>10.00%</v>
+        <v>9.00%</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Challenge 36</v>
       </c>
       <c r="B189" t="str">
-        <v>Nebula Fissure</v>
+        <v>Shoal Cave</v>
       </c>
       <c r="C189" t="str">
         <v/>
       </c>
       <c r="D189" t="str">
-        <v>Deoxys</v>
+        <v>Sealeo</v>
       </c>
       <c r="E189" t="str">
-        <v>1-1</v>
+        <v>59-63</v>
       </c>
       <c r="F189" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Challenge 37</v>
       </c>
       <c r="B190" t="str">
-        <v>Nebula Fissure</v>
+        <v>Mirage Island</v>
       </c>
       <c r="C190" t="str">
         <v/>
       </c>
       <c r="D190" t="str">
-        <v>Jirachi</v>
+        <v>Wynaut</v>
       </c>
       <c r="E190" t="str">
-        <v>1-1</v>
+        <v>61-65</v>
       </c>
       <c r="F190" t="str">
-        <v>25.00%</v>
+        <v>100.00%</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B191" t="str">
-        <v>Nebula Fissure</v>
+        <v>Victory Road</v>
       </c>
       <c r="C191" t="str">
         <v/>
       </c>
       <c r="D191" t="str">
-        <v>Latias</v>
+        <v>Golbat</v>
       </c>
       <c r="E191" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F191" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B192" t="str">
-        <v>Nebula Fissure</v>
+        <v>Victory Road</v>
       </c>
       <c r="C192" t="str">
         <v/>
       </c>
       <c r="D192" t="str">
-        <v>Latios</v>
+        <v>Hariyama</v>
       </c>
       <c r="E192" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F192" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B193" t="str">
-        <v>Trick House</v>
+        <v>Victory Road</v>
       </c>
       <c r="C193" t="str">
         <v/>
       </c>
       <c r="D193" t="str">
-        <v>Kecleon</v>
+        <v>Lairon</v>
       </c>
       <c r="E193" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F193" t="str">
-        <v>35.00%</v>
+        <v>15.20%</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B194" t="str">
-        <v>Trick House</v>
+        <v>Victory Road</v>
       </c>
       <c r="C194" t="str">
         <v/>
       </c>
       <c r="D194" t="str">
-        <v>Voltorb</v>
+        <v>Medicham</v>
       </c>
       <c r="E194" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F194" t="str">
-        <v>30.00%</v>
+        <v>15.20%</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B195" t="str">
-        <v>Trick House</v>
+        <v>Victory Road</v>
       </c>
       <c r="C195" t="str">
         <v/>
       </c>
       <c r="D195" t="str">
-        <v>Electrike</v>
+        <v>Loudred</v>
       </c>
       <c r="E195" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F195" t="str">
-        <v>20.00%</v>
+        <v>11.40%</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Challenge 44</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B196" t="str">
-        <v>Trick House</v>
+        <v>Victory Road</v>
       </c>
       <c r="C196" t="str">
         <v/>
       </c>
       <c r="D196" t="str">
-        <v>Electrode</v>
+        <v>Graveler</v>
       </c>
       <c r="E196" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F196" t="str">
-        <v>15.00%</v>
+        <v>5.70%</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Challenge 42</v>
       </c>
       <c r="B197" t="str">
-        <v>Rustboro Fossil Lab</v>
+        <v>Victory Road</v>
       </c>
       <c r="C197" t="str">
         <v/>
       </c>
       <c r="D197" t="str">
-        <v>Lileep</v>
+        <v>Exploud</v>
       </c>
       <c r="E197" t="str">
-        <v>1-1</v>
+        <v>64-68</v>
       </c>
       <c r="F197" t="str">
-        <v>35.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B198" t="str">
-        <v>Rustboro Fossil Lab</v>
+        <v>Sky Pillar</v>
       </c>
       <c r="C198" t="str">
         <v/>
       </c>
       <c r="D198" t="str">
-        <v>Anorith</v>
+        <v>Golbat</v>
       </c>
       <c r="E198" t="str">
-        <v>1-1</v>
+        <v>62-66</v>
       </c>
       <c r="F198" t="str">
-        <v>35.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B199" t="str">
-        <v>Rustboro Fossil Lab</v>
+        <v>Sky Pillar</v>
       </c>
       <c r="C199" t="str">
         <v/>
       </c>
       <c r="D199" t="str">
-        <v>Cradily</v>
+        <v>Claydol</v>
       </c>
       <c r="E199" t="str">
-        <v>1-1</v>
+        <v>62-66</v>
       </c>
       <c r="F199" t="str">
-        <v>15.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B200" t="str">
-        <v>Rustboro Fossil Lab</v>
+        <v>Sky Pillar</v>
       </c>
       <c r="C200" t="str">
         <v/>
       </c>
       <c r="D200" t="str">
-        <v>Armaldo</v>
+        <v>Altaria</v>
       </c>
       <c r="E200" t="str">
-        <v>1-1</v>
+        <v>62-66</v>
       </c>
       <c r="F200" t="str">
-        <v>15.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B201" t="str">
-        <v>Abandoned Ship</v>
+        <v>Sky Pillar</v>
       </c>
       <c r="C201" t="str">
         <v/>
       </c>
       <c r="D201" t="str">
-        <v>Tentacruel</v>
+        <v>Dusclops</v>
       </c>
       <c r="E201" t="str">
-        <v>1-1</v>
+        <v>62-66</v>
       </c>
       <c r="F201" t="str">
-        <v>35.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Challenge 41</v>
       </c>
       <c r="B202" t="str">
-        <v>Abandoned Ship</v>
+        <v>Sky Pillar</v>
       </c>
       <c r="C202" t="str">
         <v/>
       </c>
       <c r="D202" t="str">
-        <v>Golduck</v>
+        <v>Banette</v>
       </c>
       <c r="E202" t="str">
-        <v>1-1</v>
+        <v>62-66</v>
       </c>
       <c r="F202" t="str">
-        <v>25.00%</v>
+        <v>10.00%</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B203" t="str">
-        <v>Abandoned Ship</v>
+        <v>Nebula Fissure</v>
       </c>
       <c r="C203" t="str">
         <v/>
       </c>
       <c r="D203" t="str">
-        <v>Marill</v>
+        <v>Deoxys</v>
       </c>
       <c r="E203" t="str">
-        <v>1-1</v>
+        <v>120-120</v>
       </c>
       <c r="F203" t="str">
         <v>25.00%</v>
@@ -4463,539 +4463,539 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B204" t="str">
-        <v>Abandoned Ship</v>
+        <v>Nebula Fissure</v>
       </c>
       <c r="C204" t="str">
         <v/>
       </c>
       <c r="D204" t="str">
-        <v>Azumarill</v>
+        <v>Jirachi</v>
       </c>
       <c r="E204" t="str">
-        <v>1-1</v>
+        <v>120-120</v>
       </c>
       <c r="F204" t="str">
-        <v>15.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B205" t="str">
-        <v>Enemy Hideout</v>
+        <v>Nebula Fissure</v>
       </c>
       <c r="C205" t="str">
         <v/>
       </c>
       <c r="D205" t="str">
-        <v>Mightyena</v>
+        <v>Latias</v>
       </c>
       <c r="E205" t="str">
-        <v>1-1</v>
+        <v>110-110</v>
       </c>
       <c r="F205" t="str">
-        <v>30.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B206" t="str">
-        <v>Enemy Hideout</v>
+        <v>Nebula Fissure</v>
       </c>
       <c r="C206" t="str">
         <v/>
       </c>
       <c r="D206" t="str">
-        <v>Golbat</v>
+        <v>Latios</v>
       </c>
       <c r="E206" t="str">
-        <v>1-1</v>
+        <v>110-110</v>
       </c>
       <c r="F206" t="str">
-        <v>30.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B207" t="str">
-        <v>Enemy Hideout</v>
+        <v>Trick House</v>
       </c>
       <c r="C207" t="str">
         <v/>
       </c>
       <c r="D207" t="str">
-        <v>Koffing</v>
+        <v>Kecleon</v>
       </c>
       <c r="E207" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F207" t="str">
-        <v>20.00%</v>
+        <v>35.00%</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B208" t="str">
-        <v>Enemy Hideout</v>
+        <v>Trick House</v>
       </c>
       <c r="C208" t="str">
         <v/>
       </c>
       <c r="D208" t="str">
-        <v>Weezing</v>
+        <v>Voltorb</v>
       </c>
       <c r="E208" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F208" t="str">
-        <v>20.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B209" t="str">
-        <v>Sealed Chamber</v>
+        <v>Trick House</v>
       </c>
       <c r="C209" t="str">
         <v/>
       </c>
       <c r="D209" t="str">
-        <v>Relicanth</v>
+        <v>Electrike</v>
       </c>
       <c r="E209" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F209" t="str">
-        <v>40.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B210" t="str">
-        <v>Sealed Chamber</v>
+        <v>Trick House</v>
       </c>
       <c r="C210" t="str">
         <v/>
       </c>
       <c r="D210" t="str">
-        <v>Wailord</v>
+        <v>Electrode</v>
       </c>
       <c r="E210" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F210" t="str">
-        <v>35.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B211" t="str">
-        <v>Sealed Chamber</v>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="C211" t="str">
         <v/>
       </c>
       <c r="D211" t="str">
-        <v>Clamperl</v>
+        <v>Lileep</v>
       </c>
       <c r="E211" t="str">
-        <v>1-1</v>
+        <v>76-81</v>
       </c>
       <c r="F211" t="str">
-        <v>25.00%</v>
+        <v>35.00%</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B212" t="str">
-        <v>Ancient Ruins</v>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="C212" t="str">
         <v/>
       </c>
       <c r="D212" t="str">
-        <v>Regirock</v>
+        <v>Anorith</v>
       </c>
       <c r="E212" t="str">
-        <v>1-1</v>
+        <v>76-81</v>
       </c>
       <c r="F212" t="str">
-        <v>33.00%</v>
+        <v>35.00%</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B213" t="str">
-        <v>Ancient Ruins</v>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="C213" t="str">
         <v/>
       </c>
       <c r="D213" t="str">
-        <v>Regice</v>
+        <v>Cradily</v>
       </c>
       <c r="E213" t="str">
-        <v>1-1</v>
+        <v>76-81</v>
       </c>
       <c r="F213" t="str">
-        <v>33.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B214" t="str">
-        <v>Ancient Ruins</v>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="C214" t="str">
         <v/>
       </c>
       <c r="D214" t="str">
-        <v>Registeel</v>
+        <v>Armaldo</v>
       </c>
       <c r="E214" t="str">
-        <v>1-1</v>
+        <v>76-81</v>
       </c>
       <c r="F214" t="str">
-        <v>33.00%</v>
+        <v>15.00%</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>Challenge 44</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B215" t="str">
-        <v>Mauville Game Corner</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C215" t="str">
         <v/>
       </c>
       <c r="D215" t="str">
-        <v>Slakoth</v>
+        <v>Tentacruel</v>
       </c>
       <c r="E215" t="str">
-        <v>1-1</v>
+        <v>82-87</v>
       </c>
       <c r="F215" t="str">
-        <v>30.00%</v>
+        <v>33.25%</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>Challenge 44</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B216" t="str">
-        <v>Mauville Game Corner</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C216" t="str">
         <v/>
       </c>
       <c r="D216" t="str">
-        <v>Abra</v>
+        <v>Golduck</v>
       </c>
       <c r="E216" t="str">
-        <v>1-1</v>
+        <v>82-87</v>
       </c>
       <c r="F216" t="str">
-        <v>30.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>Challenge 44</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B217" t="str">
-        <v>Mauville Game Corner</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C217" t="str">
         <v/>
       </c>
       <c r="D217" t="str">
-        <v>Castform</v>
+        <v>Marill</v>
       </c>
       <c r="E217" t="str">
-        <v>1-1</v>
+        <v>82-87</v>
       </c>
       <c r="F217" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>Challenge 44</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B218" t="str">
-        <v>Mauville Game Corner</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C218" t="str">
         <v/>
       </c>
       <c r="D218" t="str">
-        <v>Porygon</v>
+        <v>Azumarill</v>
       </c>
       <c r="E218" t="str">
-        <v>1-1</v>
+        <v>82-87</v>
       </c>
       <c r="F218" t="str">
-        <v>15.00%</v>
+        <v>14.25%</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>Extra Challenge A 1</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B219" t="str">
-        <v>Starter Sanctuary</v>
+        <v>Abandoned Ship</v>
       </c>
       <c r="C219" t="str">
         <v/>
       </c>
       <c r="D219" t="str">
-        <v>Treecko</v>
+        <v>Gorebyss</v>
       </c>
       <c r="E219" t="str">
-        <v>1-1</v>
+        <v>82-87</v>
       </c>
       <c r="F219" t="str">
-        <v>33.34%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>Extra Challenge A 1</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B220" t="str">
-        <v>Starter Sanctuary</v>
+        <v>Enemy Hideout</v>
       </c>
       <c r="C220" t="str">
         <v/>
       </c>
       <c r="D220" t="str">
-        <v>Torchic</v>
+        <v>Mightyena</v>
       </c>
       <c r="E220" t="str">
-        <v>1-1</v>
+        <v>88-93</v>
       </c>
       <c r="F220" t="str">
-        <v>33.33%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>Extra Challenge A 1</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B221" t="str">
-        <v>Starter Sanctuary</v>
+        <v>Enemy Hideout</v>
       </c>
       <c r="C221" t="str">
         <v/>
       </c>
       <c r="D221" t="str">
-        <v>Mudkip</v>
+        <v>Golbat</v>
       </c>
       <c r="E221" t="str">
-        <v>1-1</v>
+        <v>88-93</v>
       </c>
       <c r="F221" t="str">
-        <v>33.33%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>Extra Challenge A 2</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B222" t="str">
-        <v>Daycare Special Spot</v>
+        <v>Enemy Hideout</v>
       </c>
       <c r="C222" t="str">
         <v/>
       </c>
       <c r="D222" t="str">
-        <v>Wynaut</v>
+        <v>Koffing</v>
       </c>
       <c r="E222" t="str">
-        <v>1-1</v>
+        <v>88-93</v>
       </c>
       <c r="F222" t="str">
-        <v>35.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>Extra Challenge A 2</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B223" t="str">
-        <v>Daycare Special Spot</v>
+        <v>Enemy Hideout</v>
       </c>
       <c r="C223" t="str">
         <v/>
       </c>
       <c r="D223" t="str">
-        <v>Azurill</v>
+        <v>Weezing</v>
       </c>
       <c r="E223" t="str">
-        <v>1-1</v>
+        <v>88-93</v>
       </c>
       <c r="F223" t="str">
-        <v>35.00%</v>
+        <v>20.00%</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>Extra Challenge A 2</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B224" t="str">
-        <v>Daycare Special Spot</v>
+        <v>Sealed Chamber</v>
       </c>
       <c r="C224" t="str">
         <v/>
       </c>
       <c r="D224" t="str">
-        <v>Pichu</v>
+        <v>Relicanth</v>
       </c>
       <c r="E224" t="str">
-        <v>1-1</v>
+        <v>95-100</v>
       </c>
       <c r="F224" t="str">
-        <v>15.00%</v>
+        <v>38.00%</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>Extra Challenge A 2</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B225" t="str">
-        <v>Daycare Special Spot</v>
+        <v>Sealed Chamber</v>
       </c>
       <c r="C225" t="str">
         <v/>
       </c>
       <c r="D225" t="str">
-        <v>Igglybuff</v>
+        <v>Wailord</v>
       </c>
       <c r="E225" t="str">
-        <v>1-1</v>
+        <v>95-100</v>
       </c>
       <c r="F225" t="str">
-        <v>15.00%</v>
+        <v>33.25%</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>Extra Challenge A 3</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B226" t="str">
-        <v>Battle Frontier Facility</v>
+        <v>Sealed Chamber</v>
       </c>
       <c r="C226" t="str">
         <v/>
       </c>
       <c r="D226" t="str">
-        <v>Salamence</v>
+        <v>Clamperl</v>
       </c>
       <c r="E226" t="str">
-        <v>1-1</v>
+        <v>95-100</v>
       </c>
       <c r="F226" t="str">
-        <v>25.00%</v>
+        <v>23.75%</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>Extra Challenge A 3</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B227" t="str">
-        <v>Battle Frontier Facility</v>
+        <v>Sealed Chamber</v>
       </c>
       <c r="C227" t="str">
         <v/>
       </c>
       <c r="D227" t="str">
-        <v>Metagross</v>
+        <v>Kingdra</v>
       </c>
       <c r="E227" t="str">
-        <v>1-1</v>
+        <v>95-100</v>
       </c>
       <c r="F227" t="str">
-        <v>25.00%</v>
+        <v>5.00%</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>Extra Challenge A 3</v>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B228" t="str">
-        <v>Battle Frontier Facility</v>
+        <v>Ancient Ruins</v>
       </c>
       <c r="C228" t="str">
         <v/>
       </c>
       <c r="D228" t="str">
-        <v>Milotic</v>
+        <v>Regirock</v>
       </c>
       <c r="E228" t="str">
-        <v>1-1</v>
+        <v>105-105</v>
       </c>
       <c r="F228" t="str">
-        <v>25.00%</v>
+        <v>33.00%</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>Extra Challenge A 3</v>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B229" t="str">
-        <v>Battle Frontier Facility</v>
+        <v>Ancient Ruins</v>
       </c>
       <c r="C229" t="str">
         <v/>
       </c>
       <c r="D229" t="str">
-        <v>Slaking</v>
+        <v>Regice</v>
       </c>
       <c r="E229" t="str">
-        <v>1-1</v>
+        <v>105-105</v>
       </c>
       <c r="F229" t="str">
-        <v>25.00%</v>
+        <v>33.00%</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>Extra Challenge A 4</v>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B230" t="str">
-        <v>Weather Climax Cave</v>
+        <v>Ancient Ruins</v>
       </c>
       <c r="C230" t="str">
         <v/>
       </c>
       <c r="D230" t="str">
-        <v>Kyogre</v>
+        <v>Registeel</v>
       </c>
       <c r="E230" t="str">
-        <v>1-1</v>
+        <v>105-105</v>
       </c>
       <c r="F230" t="str">
         <v>33.00%</v>
@@ -5003,42 +5003,42 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>Extra Challenge A 4</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B231" t="str">
-        <v>Weather Climax Cave</v>
+        <v>Mauville Game Corner</v>
       </c>
       <c r="C231" t="str">
         <v/>
       </c>
       <c r="D231" t="str">
-        <v>Groudon</v>
+        <v>Slakoth</v>
       </c>
       <c r="E231" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F231" t="str">
-        <v>33.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>Extra Challenge A 4</v>
+        <v>Challenge 44</v>
       </c>
       <c r="B232" t="str">
-        <v>Weather Climax Cave</v>
+        <v>Mauville Game Corner</v>
       </c>
       <c r="C232" t="str">
         <v/>
       </c>
       <c r="D232" t="str">
-        <v>Rayquaza</v>
+        <v>Abra</v>
       </c>
       <c r="E232" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F232" t="str">
-        <v>33.00%</v>
+        <v>30.00%</v>
       </c>
     </row>
     <row r="233">
@@ -5046,19 +5046,19 @@
         <v>Challenge 44</v>
       </c>
       <c r="B233" t="str">
-        <v>Roaming Hoenn Skies</v>
+        <v>Mauville Game Corner</v>
       </c>
       <c r="C233" t="str">
         <v/>
       </c>
       <c r="D233" t="str">
-        <v>Latias</v>
+        <v>Castform</v>
       </c>
       <c r="E233" t="str">
-        <v>1-1</v>
+        <v>70-75</v>
       </c>
       <c r="F233" t="str">
-        <v>50.00%</v>
+        <v>25.00%</v>
       </c>
     </row>
     <row r="234">
@@ -5066,31 +5066,411 @@
         <v>Challenge 44</v>
       </c>
       <c r="B234" t="str">
+        <v>Mauville Game Corner</v>
+      </c>
+      <c r="C234" t="str">
+        <v/>
+      </c>
+      <c r="D234" t="str">
+        <v>Porygon</v>
+      </c>
+      <c r="E234" t="str">
+        <v>70-75</v>
+      </c>
+      <c r="F234" t="str">
+        <v>15.00%</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B235" t="str">
+        <v>Starter Sanctuary</v>
+      </c>
+      <c r="C235" t="str">
+        <v/>
+      </c>
+      <c r="D235" t="str">
+        <v>Treecko</v>
+      </c>
+      <c r="E235" t="str">
+        <v>76-81</v>
+      </c>
+      <c r="F235" t="str">
+        <v>33.34%</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B236" t="str">
+        <v>Starter Sanctuary</v>
+      </c>
+      <c r="C236" t="str">
+        <v/>
+      </c>
+      <c r="D236" t="str">
+        <v>Torchic</v>
+      </c>
+      <c r="E236" t="str">
+        <v>76-81</v>
+      </c>
+      <c r="F236" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B237" t="str">
+        <v>Starter Sanctuary</v>
+      </c>
+      <c r="C237" t="str">
+        <v/>
+      </c>
+      <c r="D237" t="str">
+        <v>Mudkip</v>
+      </c>
+      <c r="E237" t="str">
+        <v>76-81</v>
+      </c>
+      <c r="F237" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B238" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C238" t="str">
+        <v/>
+      </c>
+      <c r="D238" t="str">
+        <v>Wynaut</v>
+      </c>
+      <c r="E238" t="str">
+        <v>88-93</v>
+      </c>
+      <c r="F238" t="str">
+        <v>35.00%</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B239" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C239" t="str">
+        <v/>
+      </c>
+      <c r="D239" t="str">
+        <v>Azurill</v>
+      </c>
+      <c r="E239" t="str">
+        <v>88-93</v>
+      </c>
+      <c r="F239" t="str">
+        <v>35.00%</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B240" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C240" t="str">
+        <v/>
+      </c>
+      <c r="D240" t="str">
+        <v>Pichu</v>
+      </c>
+      <c r="E240" t="str">
+        <v>88-93</v>
+      </c>
+      <c r="F240" t="str">
+        <v>15.00%</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B241" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C241" t="str">
+        <v/>
+      </c>
+      <c r="D241" t="str">
+        <v>Igglybuff</v>
+      </c>
+      <c r="E241" t="str">
+        <v>88-93</v>
+      </c>
+      <c r="F241" t="str">
+        <v>15.00%</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B242" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C242" t="str">
+        <v/>
+      </c>
+      <c r="D242" t="str">
+        <v>Salamence</v>
+      </c>
+      <c r="E242" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F242" t="str">
+        <v>25.00%</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B243" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C243" t="str">
+        <v/>
+      </c>
+      <c r="D243" t="str">
+        <v>Metagross</v>
+      </c>
+      <c r="E243" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F243" t="str">
+        <v>25.00%</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B244" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C244" t="str">
+        <v/>
+      </c>
+      <c r="D244" t="str">
+        <v>Milotic</v>
+      </c>
+      <c r="E244" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F244" t="str">
+        <v>25.00%</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B245" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C245" t="str">
+        <v/>
+      </c>
+      <c r="D245" t="str">
+        <v>Slaking</v>
+      </c>
+      <c r="E245" t="str">
+        <v>95-100</v>
+      </c>
+      <c r="F245" t="str">
+        <v>25.00%</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B246" t="str">
+        <v>Weather Climax Cave</v>
+      </c>
+      <c r="C246" t="str">
+        <v/>
+      </c>
+      <c r="D246" t="str">
+        <v>Kyogre</v>
+      </c>
+      <c r="E246" t="str">
+        <v>115-115</v>
+      </c>
+      <c r="F246" t="str">
+        <v>33.00%</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B247" t="str">
+        <v>Weather Climax Cave</v>
+      </c>
+      <c r="C247" t="str">
+        <v/>
+      </c>
+      <c r="D247" t="str">
+        <v>Groudon</v>
+      </c>
+      <c r="E247" t="str">
+        <v>115-115</v>
+      </c>
+      <c r="F247" t="str">
+        <v>33.00%</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B248" t="str">
+        <v>Weather Climax Cave</v>
+      </c>
+      <c r="C248" t="str">
+        <v/>
+      </c>
+      <c r="D248" t="str">
+        <v>Rayquaza</v>
+      </c>
+      <c r="E248" t="str">
+        <v>115-115</v>
+      </c>
+      <c r="F248" t="str">
+        <v>33.00%</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B249" t="str">
         <v>Roaming Hoenn Skies</v>
       </c>
-      <c r="C234" t="str">
-        <v/>
-      </c>
-      <c r="D234" t="str">
+      <c r="C249" t="str">
+        <v/>
+      </c>
+      <c r="D249" t="str">
+        <v>Latias</v>
+      </c>
+      <c r="E249" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F249" t="str">
+        <v>50.00%</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B250" t="str">
+        <v>Roaming Hoenn Skies</v>
+      </c>
+      <c r="C250" t="str">
+        <v/>
+      </c>
+      <c r="D250" t="str">
         <v>Latios</v>
       </c>
-      <c r="E234" t="str">
-        <v>1-1</v>
-      </c>
-      <c r="F234" t="str">
+      <c r="E250" t="str">
+        <v>110-110</v>
+      </c>
+      <c r="F250" t="str">
         <v>50.00%</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B251" t="str">
+        <v>Advanced Starter Sanctuary</v>
+      </c>
+      <c r="C251" t="str">
+        <v/>
+      </c>
+      <c r="D251" t="str">
+        <v>Grovyle</v>
+      </c>
+      <c r="E251" t="str">
+        <v>82-87</v>
+      </c>
+      <c r="F251" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B252" t="str">
+        <v>Advanced Starter Sanctuary</v>
+      </c>
+      <c r="C252" t="str">
+        <v/>
+      </c>
+      <c r="D252" t="str">
+        <v>Combusken</v>
+      </c>
+      <c r="E252" t="str">
+        <v>82-87</v>
+      </c>
+      <c r="F252" t="str">
+        <v>33.33%</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B253" t="str">
+        <v>Advanced Starter Sanctuary</v>
+      </c>
+      <c r="C253" t="str">
+        <v/>
+      </c>
+      <c r="D253" t="str">
+        <v>Marshtomp</v>
+      </c>
+      <c r="E253" t="str">
+        <v>82-87</v>
+      </c>
+      <c r="F253" t="str">
+        <v>33.34%</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F234"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F253"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5196,7 +5576,7 @@
         <v>Challenge 9</v>
       </c>
       <c r="B10" t="str">
-        <v/>
+        <v>Catch 1 Epic Magikarp</v>
       </c>
       <c r="C10" t="str">
         <v>Unlocks: Dewford Gym</v>
@@ -5562,7 +5942,7 @@
         <v>Catch 8 Common (Slakoth/Abra)</v>
       </c>
       <c r="C43" t="str">
-        <v>Unlocks: Starter Sanctuary; Gift: 3 Fire Stone</v>
+        <v>Unlocks: Starter Sanctuary; Gift: 10 Ultraball</v>
       </c>
     </row>
     <row r="44">
@@ -5573,7 +5953,7 @@
         <v>Catch 1 Treecko, Catch 1 Torchic, Catch 1 Mudkip</v>
       </c>
       <c r="C44" t="str">
-        <v>Unlocks: Daycare Special Spot; Gift: 3 Leaf Stone</v>
+        <v>Unlocks: Advanced Starter Sanctuary</v>
       </c>
     </row>
     <row r="45">
@@ -5581,10 +5961,10 @@
         <v>Extra Challenge A 3</v>
       </c>
       <c r="B45" t="str">
-        <v>Catch 1 Wynaut, Catch 1 Azurill</v>
+        <v>Catch 1 Grovyle, Catch 1 Combusken, Catch 1 Marshtomp</v>
       </c>
       <c r="C45" t="str">
-        <v>Unlocks: Battle Frontier Facility; Gift: 1 Masterball</v>
+        <v>Unlocks: Daycare Special Spot; Gift: 2 Grass Stone</v>
       </c>
     </row>
     <row r="46">
@@ -5592,10 +5972,10 @@
         <v>Extra Challenge A 4</v>
       </c>
       <c r="B46" t="str">
-        <v>Defeat 50 on Battle Frontier Facility</v>
+        <v>Catch 1 Wynaut, Catch 1 Azurill</v>
       </c>
       <c r="C46" t="str">
-        <v>Unlocks: Weather Climax Cave; Gift: 1 Masterball</v>
+        <v>Unlocks: Battle Frontier Facility; Gift: 1 Masterball</v>
       </c>
     </row>
     <row r="47">
@@ -5603,84 +5983,84 @@
         <v>Extra Challenge A 5</v>
       </c>
       <c r="B47" t="str">
-        <v>Catch 1 Kyogre, Catch 1 Groudon, Catch 1 Rayquaza</v>
+        <v>Defeat 50 on Battle Frontier Facility</v>
       </c>
       <c r="C47" t="str">
-        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 2 Masterball</v>
+        <v>Unlocks: Weather Climax Cave; Gift: 1 Masterball</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Extra Challenge B 1</v>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="B48" t="str">
-        <v>Defeat 20 on Trick House</v>
+        <v>Catch 1 Kyogre, Catch 1 Groudon, Catch 1 Rayquaza</v>
       </c>
       <c r="C48" t="str">
-        <v>Unlocks: Rustboro Fossil Lab; Gift: 1 Masterball</v>
+        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 2 Masterball</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Extra Challenge B 2</v>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B49" t="str">
-        <v>Catch 1 Lileep, Catch 1 Anorith</v>
+        <v>Defeat 20 on Trick House</v>
       </c>
       <c r="C49" t="str">
-        <v>Unlocks: Abandoned Ship; Gift: 1 Root Fossil</v>
+        <v>Unlocks: Rustboro Fossil Lab; Gift: 1 Masterball</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Extra Challenge B 3</v>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B50" t="str">
-        <v>Catch 1 Tentacruel</v>
+        <v>Catch 1 Lileep, Catch 1 Anorith</v>
       </c>
       <c r="C50" t="str">
-        <v>Unlocks: Enemy Hideout; Gift: 1 Deep Sea Scale</v>
+        <v>Unlocks: Abandoned Ship; Gift: 1 Root Fossil</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Extra Challenge B 4</v>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B51" t="str">
-        <v>Catch 1 Weezing; Defeat 25 on Enemy Hideout</v>
+        <v>Catch 1 Tentacruel</v>
       </c>
       <c r="C51" t="str">
-        <v>Unlocks: Sealed Chamber; Gift: 1 Masterball</v>
+        <v>Unlocks: Enemy Hideout; Gift: 1 Deep Sea Scale</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Extra Challenge B 5</v>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B52" t="str">
-        <v>Defeat 1 Relicanth</v>
+        <v>Catch 1 Weezing; Defeat 25 on Enemy Hideout</v>
       </c>
       <c r="C52" t="str">
-        <v>Unlocks: Ancient Ruins; Gift: 2 Masterball</v>
+        <v>Unlocks: Sealed Chamber; Gift: 1 Masterball</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Extra Challenge B 6</v>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B53" t="str">
-        <v>Catch 1 Regirock, Catch 1 Regice, Catch 1 Registeel</v>
+        <v>Defeat 1 Relicanth</v>
       </c>
       <c r="C53" t="str">
-        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 1 Masterball</v>
+        <v>Unlocks: Ancient Ruins; Gift: 2 Masterball</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Extra Challenge (Roaming)</v>
+        <v>Extra Challenge B 6</v>
       </c>
       <c r="B54" t="str">
-        <v>Defeat 1 Latias, Defeat 1 Latios</v>
+        <v>Catch 1 Regirock, Catch 1 Regice, Catch 1 Registeel</v>
       </c>
       <c r="C54" t="str">
         <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 1 Masterball</v>
@@ -5688,36 +6068,47 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Key to Nebula Fissure Challenge</v>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="B55" t="str">
-        <v>Complete challenges: Extra Challenge A 5, Extra Challenge B 6, Extra Challenge (Roaming)</v>
+        <v>Defeat 1 Latias, Defeat 1 Latios</v>
       </c>
       <c r="C55" t="str">
-        <v>Unlocks: Nebula Fissure</v>
+        <v>Unlocks: Key to Nebula Fissure Challenge; Gift: 1 Masterball</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Complete challenges: Extra Challenge A 6, Extra Challenge B 6, Extra Challenge (Roaming)</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Unlocks: Nebula Fissure</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>Nebula Fissure Challenge</v>
       </c>
-      <c r="B56" t="str">
-        <v>Defeat 1 Deoxys</v>
-      </c>
-      <c r="C56" t="str">
+      <c r="B57" t="str">
+        <v>Catch 1 Deoxys, Catch 1 Jirachi</v>
+      </c>
+      <c r="C57" t="str">
         <v>Gift: 1 Masterball</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C57"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5729,7 +6120,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Grovyle</v>
+        <v>Sceptile</v>
       </c>
       <c r="B2" t="str">
         <v>Evolve</v>
@@ -5737,15 +6128,15 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Sceptile</v>
+        <v>Blaziken</v>
       </c>
       <c r="B3" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Combusken</v>
+        <v>Swampert</v>
       </c>
       <c r="B4" t="str">
         <v>Evolve</v>
@@ -5753,15 +6144,15 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Blaziken</v>
+        <v>Beautifly</v>
       </c>
       <c r="B5" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Marshtomp</v>
+        <v>Dustox</v>
       </c>
       <c r="B6" t="str">
         <v>Evolve</v>
@@ -5769,15 +6160,15 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Swampert</v>
+        <v>Ludicolo</v>
       </c>
       <c r="B7" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Beautifly</v>
+        <v>Shiftry</v>
       </c>
       <c r="B8" t="str">
         <v>Evolve</v>
@@ -5785,7 +6176,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Dustox</v>
+        <v>Swellow</v>
       </c>
       <c r="B9" t="str">
         <v>Evolve</v>
@@ -5793,7 +6184,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Ludicolo</v>
+        <v>Gardevoir</v>
       </c>
       <c r="B10" t="str">
         <v>Evolve</v>
@@ -5801,7 +6192,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Shiftry</v>
+        <v>Breloom</v>
       </c>
       <c r="B11" t="str">
         <v>Evolve</v>
@@ -5809,7 +6200,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Swellow</v>
+        <v>Vigoroth</v>
       </c>
       <c r="B12" t="str">
         <v>Evolve</v>
@@ -5817,7 +6208,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Kirlia</v>
+        <v>Alakazam</v>
       </c>
       <c r="B13" t="str">
         <v>Evolve</v>
@@ -5825,15 +6216,15 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Gardevoir</v>
+        <v>Ninjask</v>
       </c>
       <c r="B14" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Masquerain</v>
+        <v>Gyarados</v>
       </c>
       <c r="B15" t="str">
         <v>Evolve</v>
@@ -5841,7 +6232,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Breloom</v>
+        <v>Golem</v>
       </c>
       <c r="B16" t="str">
         <v>Evolve</v>
@@ -5849,7 +6240,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Vigoroth</v>
+        <v>Delcatty</v>
       </c>
       <c r="B17" t="str">
         <v>Evolve</v>
@@ -5857,7 +6248,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Kadabra</v>
+        <v>Crobat</v>
       </c>
       <c r="B18" t="str">
         <v>Evolve</v>
@@ -5865,15 +6256,15 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Alakazam</v>
+        <v>Aggron</v>
       </c>
       <c r="B19" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Ninjask</v>
+        <v>Machamp</v>
       </c>
       <c r="B20" t="str">
         <v>Evolve</v>
@@ -5881,15 +6272,15 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Shedinja</v>
+        <v>Magneton</v>
       </c>
       <c r="B21" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Exploud</v>
+        <v>Vileplume</v>
       </c>
       <c r="B22" t="str">
         <v>Evolve</v>
@@ -5897,7 +6288,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Gyarados</v>
+        <v>Bellossom</v>
       </c>
       <c r="B23" t="str">
         <v>Evolve</v>
@@ -5905,7 +6296,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Golem</v>
+        <v>Dodrio</v>
       </c>
       <c r="B24" t="str">
         <v>Evolve</v>
@@ -5913,7 +6304,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Delcatty</v>
+        <v>Swalot</v>
       </c>
       <c r="B25" t="str">
         <v>Evolve</v>
@@ -5921,7 +6312,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Crobat</v>
+        <v>Camerupt</v>
       </c>
       <c r="B26" t="str">
         <v>Evolve</v>
@@ -5929,7 +6320,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Aggron</v>
+        <v>Magcargo</v>
       </c>
       <c r="B27" t="str">
         <v>Evolve</v>
@@ -5937,7 +6328,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Machoke</v>
+        <v>Muk</v>
       </c>
       <c r="B28" t="str">
         <v>Evolve</v>
@@ -5945,31 +6336,31 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Machamp</v>
+        <v>Grumpig</v>
       </c>
       <c r="B29" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Magnemite</v>
+        <v>Sandslash</v>
       </c>
       <c r="B30" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Magneton</v>
+        <v>Vibrava</v>
       </c>
       <c r="B31" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Vileplume</v>
+        <v>Cacturne</v>
       </c>
       <c r="B32" t="str">
         <v>Evolve</v>
@@ -5977,7 +6368,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Bellossom</v>
+        <v>Crawdaunt</v>
       </c>
       <c r="B33" t="str">
         <v>Evolve</v>
@@ -5985,7 +6376,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Dodrio</v>
+        <v>Wigglytuff</v>
       </c>
       <c r="B34" t="str">
         <v>Evolve</v>
@@ -5993,7 +6384,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Swalot</v>
+        <v>Starmie</v>
       </c>
       <c r="B35" t="str">
         <v>Evolve</v>
@@ -6001,7 +6392,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Camerupt</v>
+        <v>Ninetales</v>
       </c>
       <c r="B36" t="str">
         <v>Evolve</v>
@@ -6009,7 +6400,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Magcargo</v>
+        <v>Raichu</v>
       </c>
       <c r="B37" t="str">
         <v>Evolve</v>
@@ -6017,7 +6408,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Muk</v>
+        <v>Donphan</v>
       </c>
       <c r="B38" t="str">
         <v>Evolve</v>
@@ -6025,7 +6416,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Grumpig</v>
+        <v>Rhydon</v>
       </c>
       <c r="B39" t="str">
         <v>Evolve</v>
@@ -6033,7 +6424,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sandslash</v>
+        <v>Glalie</v>
       </c>
       <c r="B40" t="str">
         <v>Evolve</v>
@@ -6041,7 +6432,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Vibrava</v>
+        <v>Walrein</v>
       </c>
       <c r="B41" t="str">
         <v>Evolve</v>
@@ -6049,15 +6440,15 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Flygon</v>
+        <v>Huntail</v>
       </c>
       <c r="B42" t="str">
-        <v>2xEvolution</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Cacturne</v>
+        <v>Lanturn</v>
       </c>
       <c r="B43" t="str">
         <v>Evolve</v>
@@ -6065,7 +6456,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Crawdaunt</v>
+        <v>Shelgon</v>
       </c>
       <c r="B44" t="str">
         <v>Evolve</v>
@@ -6073,167 +6464,15 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Wigglytuff</v>
+        <v>Metang</v>
       </c>
       <c r="B45" t="str">
         <v>Evolve</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Staryu</v>
-      </c>
-      <c r="B46" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Starmie</v>
-      </c>
-      <c r="B47" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Ninetales</v>
-      </c>
-      <c r="B48" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Raichu</v>
-      </c>
-      <c r="B49" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Donphan</v>
-      </c>
-      <c r="B50" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Rhydon</v>
-      </c>
-      <c r="B51" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Glalie</v>
-      </c>
-      <c r="B52" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Sealeo</v>
-      </c>
-      <c r="B53" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Walrein</v>
-      </c>
-      <c r="B54" t="str">
-        <v>2xEvolution</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Huntail</v>
-      </c>
-      <c r="B55" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Gorebyss</v>
-      </c>
-      <c r="B56" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Lanturn</v>
-      </c>
-      <c r="B57" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Luvdisc</v>
-      </c>
-      <c r="B58" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Horsea</v>
-      </c>
-      <c r="B59" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Seadra</v>
-      </c>
-      <c r="B60" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Kingdra</v>
-      </c>
-      <c r="B61" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Shelgon</v>
-      </c>
-      <c r="B62" t="str">
-        <v>Evolve</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Beldum</v>
-      </c>
-      <c r="B63" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Metang</v>
-      </c>
-      <c r="B64" t="str">
-        <v>No</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -6475,4 +6476,554 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B45"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C49"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name of challenge</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Route Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Map?</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v>Route 101</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Challenge 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Route 103</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Challenge 2</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Route 102</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Challenge 3</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Route 104</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Challenge 4</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Petalburg Woods</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Challenge 5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Route 116</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Granite Cave</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Challenge 8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Tiny Fishing Spot</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Route 107</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Route 110</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Challenge 13</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Route 117</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Challenge 14</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Route 111</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Fiery Path</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Challenge 17</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Jagged Pass</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Challenge 18</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Route 113</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Challenge 19</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Route 114</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Challenge 20</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Meteor Falls</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Challenge 21</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Route 115</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Route 118</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Challenge 24</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Small Fishing Spot</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Challenge 25</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Route 119</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Challenge 26</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Route 120</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Challenge 27</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Route 121</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Safari Zone East</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Safari Zone West</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>Challenge 28</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Safari Zone North</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Challenge 29</v>
+      </c>
+      <c r="B28" t="str">
+        <v>Mount Pyre</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Challenge 30</v>
+      </c>
+      <c r="B29" t="str">
+        <v>Route 123</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B30" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>Challenge 34</v>
+      </c>
+      <c r="B31" t="str">
+        <v>Underwater Fishing Spot</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B32" t="str">
+        <v>Shoal Cave</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>Challenge 37</v>
+      </c>
+      <c r="B33" t="str">
+        <v>Mirage Island</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>Challenge 42</v>
+      </c>
+      <c r="B34" t="str">
+        <v>Victory Road</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>Challenge 41</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Sky Pillar</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B36" t="str">
+        <v>Nebula Fissure</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B37" t="str">
+        <v>Trick House</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>Extra Challenge B 1</v>
+      </c>
+      <c r="B38" t="str">
+        <v>Rustboro Fossil Lab</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>Extra Challenge B 2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>Abandoned Ship</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>Extra Challenge B 3</v>
+      </c>
+      <c r="B40" t="str">
+        <v>Enemy Hideout</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>Extra Challenge B 4</v>
+      </c>
+      <c r="B41" t="str">
+        <v>Sealed Chamber</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>Extra Challenge B 5</v>
+      </c>
+      <c r="B42" t="str">
+        <v>Ancient Ruins</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B43" t="str">
+        <v>Mauville Game Corner</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>Extra Challenge A 1</v>
+      </c>
+      <c r="B44" t="str">
+        <v>Starter Sanctuary</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>Extra Challenge A 3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Daycare Special Spot</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>Extra Challenge A 4</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Battle Frontier Facility</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>Extra Challenge A 5</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Weather Climax Cave</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Roaming Hoenn Skies</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Extra Challenge A 2</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Advanced Starter Sanctuary</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C49"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -3156,7 +3156,7 @@
         <v>Pinsir</v>
       </c>
       <c r="E138" t="str">
-        <v>46-50</v>
+        <v>51-55</v>
       </c>
       <c r="F138" t="str">
         <v>8.00%</v>
@@ -3256,7 +3256,7 @@
         <v>Sunkern</v>
       </c>
       <c r="E143" t="str">
-        <v>46-50</v>
+        <v>44-48</v>
       </c>
       <c r="F143" t="str">
         <v>15.00%</v>
@@ -3276,7 +3276,7 @@
         <v>Shuckle</v>
       </c>
       <c r="E144" t="str">
-        <v>46-50</v>
+        <v>51-55</v>
       </c>
       <c r="F144" t="str">
         <v>10.00%</v>
@@ -3296,7 +3296,7 @@
         <v>Doduo</v>
       </c>
       <c r="E145" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F145" t="str">
         <v>12.00%</v>
@@ -3316,7 +3316,7 @@
         <v>Rhyhorn</v>
       </c>
       <c r="E146" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F146" t="str">
         <v>8.00%</v>
@@ -3336,7 +3336,7 @@
         <v>Girafarig</v>
       </c>
       <c r="E147" t="str">
-        <v>1-1</v>
+        <v>50-54</v>
       </c>
       <c r="F147" t="str">
         <v>8.00%</v>
@@ -3356,7 +3356,7 @@
         <v>Psyduck</v>
       </c>
       <c r="E148" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F148" t="str">
         <v>12.00%</v>
@@ -3376,7 +3376,7 @@
         <v>Xatu</v>
       </c>
       <c r="E149" t="str">
-        <v>1-1</v>
+        <v>50-54</v>
       </c>
       <c r="F149" t="str">
         <v>12.00%</v>
@@ -3396,7 +3396,7 @@
         <v>Teddiursa</v>
       </c>
       <c r="E150" t="str">
-        <v>1-1</v>
+        <v>46-50</v>
       </c>
       <c r="F150" t="str">
         <v>8.00%</v>
@@ -3416,7 +3416,7 @@
         <v>Stantler</v>
       </c>
       <c r="E151" t="str">
-        <v>1-1</v>
+        <v>50-54</v>
       </c>
       <c r="F151" t="str">
         <v>10.00%</v>
@@ -3436,7 +3436,7 @@
         <v>Wooper</v>
       </c>
       <c r="E152" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F152" t="str">
         <v>10.00%</v>
@@ -3456,7 +3456,7 @@
         <v>Ledyba</v>
       </c>
       <c r="E153" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F153" t="str">
         <v>11.00%</v>
@@ -3476,7 +3476,7 @@
         <v>Gloom</v>
       </c>
       <c r="E154" t="str">
-        <v>1-1</v>
+        <v>48-52</v>
       </c>
       <c r="F154" t="str">
         <v>9.00%</v>
@@ -3496,7 +3496,7 @@
         <v>Heracross</v>
       </c>
       <c r="E155" t="str">
-        <v>1-1</v>
+        <v>51-55</v>
       </c>
       <c r="F155" t="str">
         <v>16.00%</v>
@@ -3516,7 +3516,7 @@
         <v>Wobbuffet</v>
       </c>
       <c r="E156" t="str">
-        <v>1-1</v>
+        <v>48-52</v>
       </c>
       <c r="F156" t="str">
         <v>16.00%</v>
@@ -3536,7 +3536,7 @@
         <v>Golduck</v>
       </c>
       <c r="E157" t="str">
-        <v>1-1</v>
+        <v>51-55</v>
       </c>
       <c r="F157" t="str">
         <v>12.00%</v>
@@ -3556,7 +3556,7 @@
         <v>Mareep</v>
       </c>
       <c r="E158" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F158" t="str">
         <v>12.00%</v>
@@ -3576,7 +3576,7 @@
         <v>Gligar</v>
       </c>
       <c r="E159" t="str">
-        <v>1-1</v>
+        <v>48-52</v>
       </c>
       <c r="F159" t="str">
         <v>13.00%</v>
@@ -3596,7 +3596,7 @@
         <v>Pineco</v>
       </c>
       <c r="E160" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F160" t="str">
         <v>9.00%</v>
@@ -3616,7 +3616,7 @@
         <v>Quagsire</v>
       </c>
       <c r="E161" t="str">
-        <v>1-1</v>
+        <v>48-52</v>
       </c>
       <c r="F161" t="str">
         <v>13.00%</v>
@@ -3636,7 +3636,7 @@
         <v>Spinarak</v>
       </c>
       <c r="E162" t="str">
-        <v>1-1</v>
+        <v>44-48</v>
       </c>
       <c r="F162" t="str">
         <v>9.00%</v>

--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -452,11 +452,14 @@
       <c r="C2" t="str">
         <v/>
       </c>
+      <c r="D2" t="str">
+        <v>Poochyena</v>
+      </c>
       <c r="E2" t="str">
-        <v>undefined-undefined</v>
+        <v>1-4</v>
       </c>
       <c r="F2" t="str">
-        <v>0.45%</v>
+        <v>45%</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -490,11 +493,14 @@
       <c r="C3" t="str">
         <v/>
       </c>
+      <c r="D3" t="str">
+        <v>Zigzagoon</v>
+      </c>
       <c r="E3" t="str">
-        <v>undefined-undefined</v>
+        <v>1-4</v>
       </c>
       <c r="F3" t="str">
-        <v>0.45%</v>
+        <v>45%</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -528,11 +534,14 @@
       <c r="C4" t="str">
         <v/>
       </c>
+      <c r="D4" t="str">
+        <v>Wurmple</v>
+      </c>
       <c r="E4" t="str">
-        <v>undefined-undefined</v>
+        <v>1-4</v>
       </c>
       <c r="F4" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -566,11 +575,14 @@
       <c r="C5" t="str">
         <v/>
       </c>
+      <c r="D5" t="str">
+        <v>Poochyena</v>
+      </c>
       <c r="E5" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F5" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -604,11 +616,14 @@
       <c r="C6" t="str">
         <v/>
       </c>
+      <c r="D6" t="str">
+        <v>Zigzagoon</v>
+      </c>
       <c r="E6" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F6" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -642,11 +657,14 @@
       <c r="C7" t="str">
         <v/>
       </c>
+      <c r="D7" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E7" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F7" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -680,11 +698,14 @@
       <c r="C8" t="str">
         <v/>
       </c>
+      <c r="D8" t="str">
+        <v>Tentacool</v>
+      </c>
       <c r="E8" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F8" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -718,11 +739,14 @@
       <c r="C9" t="str">
         <v/>
       </c>
+      <c r="D9" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E9" t="str">
-        <v>undefined-undefined</v>
+        <v>2-5</v>
       </c>
       <c r="F9" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -756,11 +780,14 @@
       <c r="C10" t="str">
         <v/>
       </c>
+      <c r="D10" t="str">
+        <v>Wurmple</v>
+      </c>
       <c r="E10" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F10" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -794,11 +821,14 @@
       <c r="C11" t="str">
         <v/>
       </c>
+      <c r="D11" t="str">
+        <v>Lotad</v>
+      </c>
       <c r="E11" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F11" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -832,11 +862,14 @@
       <c r="C12" t="str">
         <v/>
       </c>
+      <c r="D12" t="str">
+        <v>Seedot</v>
+      </c>
       <c r="E12" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F12" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -870,11 +903,14 @@
       <c r="C13" t="str">
         <v/>
       </c>
+      <c r="D13" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E13" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F13" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -908,11 +944,14 @@
       <c r="C14" t="str">
         <v/>
       </c>
+      <c r="D14" t="str">
+        <v>Ralts</v>
+      </c>
       <c r="E14" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F14" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -946,11 +985,14 @@
       <c r="C15" t="str">
         <v/>
       </c>
+      <c r="D15" t="str">
+        <v>Surskit</v>
+      </c>
       <c r="E15" t="str">
-        <v>undefined-undefined</v>
+        <v>4-7</v>
       </c>
       <c r="F15" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -984,11 +1026,14 @@
       <c r="C16" t="str">
         <v/>
       </c>
+      <c r="D16" t="str">
+        <v>Poochyena</v>
+      </c>
       <c r="E16" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F16" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -1022,11 +1067,14 @@
       <c r="C17" t="str">
         <v/>
       </c>
+      <c r="D17" t="str">
+        <v>Wurmple</v>
+      </c>
       <c r="E17" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F17" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -1060,11 +1108,14 @@
       <c r="C18" t="str">
         <v/>
       </c>
+      <c r="D18" t="str">
+        <v>Taillow</v>
+      </c>
       <c r="E18" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F18" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -1098,11 +1149,14 @@
       <c r="C19" t="str">
         <v/>
       </c>
+      <c r="D19" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E19" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F19" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -1136,11 +1190,14 @@
       <c r="C20" t="str">
         <v/>
       </c>
+      <c r="D20" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E20" t="str">
-        <v>undefined-undefined</v>
+        <v>5-8</v>
       </c>
       <c r="F20" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -1174,11 +1231,14 @@
       <c r="C21" t="str">
         <v/>
       </c>
+      <c r="D21" t="str">
+        <v>Wurmple</v>
+      </c>
       <c r="E21" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F21" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -1212,11 +1272,14 @@
       <c r="C22" t="str">
         <v/>
       </c>
+      <c r="D22" t="str">
+        <v>Silcoon</v>
+      </c>
       <c r="E22" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F22" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -1250,11 +1313,14 @@
       <c r="C23" t="str">
         <v/>
       </c>
+      <c r="D23" t="str">
+        <v>Cascoon</v>
+      </c>
       <c r="E23" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F23" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -1288,11 +1354,14 @@
       <c r="C24" t="str">
         <v/>
       </c>
+      <c r="D24" t="str">
+        <v>Taillow</v>
+      </c>
       <c r="E24" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F24" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -1326,11 +1395,14 @@
       <c r="C25" t="str">
         <v/>
       </c>
+      <c r="D25" t="str">
+        <v>Shroomish</v>
+      </c>
       <c r="E25" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F25" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -1364,11 +1436,14 @@
       <c r="C26" t="str">
         <v/>
       </c>
+      <c r="D26" t="str">
+        <v>Slakoth</v>
+      </c>
       <c r="E26" t="str">
-        <v>undefined-undefined</v>
+        <v>7-10</v>
       </c>
       <c r="F26" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1402,11 +1477,14 @@
       <c r="C27" t="str">
         <v/>
       </c>
+      <c r="D27" t="str">
+        <v>Poochyena</v>
+      </c>
       <c r="E27" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F27" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1440,11 +1518,14 @@
       <c r="C28" t="str">
         <v/>
       </c>
+      <c r="D28" t="str">
+        <v>Taillow</v>
+      </c>
       <c r="E28" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F28" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1478,11 +1559,14 @@
       <c r="C29" t="str">
         <v/>
       </c>
+      <c r="D29" t="str">
+        <v>Whismur</v>
+      </c>
       <c r="E29" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F29" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1516,11 +1600,14 @@
       <c r="C30" t="str">
         <v/>
       </c>
+      <c r="D30" t="str">
+        <v>Nincada</v>
+      </c>
       <c r="E30" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F30" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1554,11 +1641,14 @@
       <c r="C31" t="str">
         <v/>
       </c>
+      <c r="D31" t="str">
+        <v>Skitty</v>
+      </c>
       <c r="E31" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F31" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1592,11 +1682,14 @@
       <c r="C32" t="str">
         <v/>
       </c>
+      <c r="D32" t="str">
+        <v>Shedinja</v>
+      </c>
       <c r="E32" t="str">
-        <v>undefined-undefined</v>
+        <v>9-12</v>
       </c>
       <c r="F32" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1630,11 +1723,14 @@
       <c r="C33" t="str">
         <v/>
       </c>
+      <c r="D33" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E33" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F33" t="str">
-        <v>0.1805%</v>
+        <v>18%</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1668,11 +1764,14 @@
       <c r="C34" t="str">
         <v/>
       </c>
+      <c r="D34" t="str">
+        <v>Makuhita</v>
+      </c>
       <c r="E34" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F34" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1706,11 +1805,14 @@
       <c r="C35" t="str">
         <v/>
       </c>
+      <c r="D35" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E35" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F35" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1744,11 +1846,14 @@
       <c r="C36" t="str">
         <v/>
       </c>
+      <c r="D36" t="str">
+        <v>Aron</v>
+      </c>
       <c r="E36" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F36" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1782,11 +1887,14 @@
       <c r="C37" t="str">
         <v/>
       </c>
+      <c r="D37" t="str">
+        <v>Abra</v>
+      </c>
       <c r="E37" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F37" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1820,11 +1928,14 @@
       <c r="C38" t="str">
         <v/>
       </c>
+      <c r="D38" t="str">
+        <v>Sableye</v>
+      </c>
       <c r="E38" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F38" t="str">
-        <v>0.076%</v>
+        <v>8%</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1858,11 +1969,14 @@
       <c r="C39" t="str">
         <v/>
       </c>
+      <c r="D39" t="str">
+        <v>Mawile</v>
+      </c>
       <c r="E39" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F39" t="str">
-        <v>0.076%</v>
+        <v>8%</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1896,11 +2010,14 @@
       <c r="C40" t="str">
         <v/>
       </c>
+      <c r="D40" t="str">
+        <v>Nosepass</v>
+      </c>
       <c r="E40" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F40" t="str">
-        <v>0.0475%</v>
+        <v>5%</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1934,11 +2051,14 @@
       <c r="C41" t="str">
         <v/>
       </c>
+      <c r="D41" t="str">
+        <v>Kadabra</v>
+      </c>
       <c r="E41" t="str">
-        <v>undefined-undefined</v>
+        <v>12-15</v>
       </c>
       <c r="F41" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1972,11 +2092,14 @@
       <c r="C42" t="str">
         <v/>
       </c>
+      <c r="D42" t="str">
+        <v>Magikarp</v>
+      </c>
       <c r="E42" t="str">
-        <v>undefined-undefined</v>
+        <v>14-17</v>
       </c>
       <c r="F42" t="str">
-        <v>0.45%</v>
+        <v>45%</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -2010,11 +2133,14 @@
       <c r="C43" t="str">
         <v/>
       </c>
+      <c r="D43" t="str">
+        <v>Goldeen</v>
+      </c>
       <c r="E43" t="str">
-        <v>undefined-undefined</v>
+        <v>14-17</v>
       </c>
       <c r="F43" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -2048,11 +2174,14 @@
       <c r="C44" t="str">
         <v/>
       </c>
+      <c r="D44" t="str">
+        <v>Tentacool</v>
+      </c>
       <c r="E44" t="str">
-        <v>undefined-undefined</v>
+        <v>14-17</v>
       </c>
       <c r="F44" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -2086,11 +2215,14 @@
       <c r="C45" t="str">
         <v/>
       </c>
+      <c r="D45" t="str">
+        <v>Surskit</v>
+      </c>
       <c r="E45" t="str">
-        <v>undefined-undefined</v>
+        <v>14-17</v>
       </c>
       <c r="F45" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -2124,11 +2256,14 @@
       <c r="C46" t="str">
         <v/>
       </c>
+      <c r="D46" t="str">
+        <v>Staryu</v>
+      </c>
       <c r="E46" t="str">
-        <v>undefined-undefined</v>
+        <v>14-17</v>
       </c>
       <c r="F46" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -2162,11 +2297,14 @@
       <c r="C47" t="str">
         <v/>
       </c>
+      <c r="D47" t="str">
+        <v>Tentacool</v>
+      </c>
       <c r="E47" t="str">
-        <v>undefined-undefined</v>
+        <v>17-20</v>
       </c>
       <c r="F47" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -2200,11 +2338,14 @@
       <c r="C48" t="str">
         <v/>
       </c>
+      <c r="D48" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E48" t="str">
-        <v>undefined-undefined</v>
+        <v>17-20</v>
       </c>
       <c r="F48" t="str">
-        <v>0.4%</v>
+        <v>40%</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -2238,11 +2379,14 @@
       <c r="C49" t="str">
         <v/>
       </c>
+      <c r="D49" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E49" t="str">
-        <v>undefined-undefined</v>
+        <v>17-20</v>
       </c>
       <c r="F49" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -2276,11 +2420,14 @@
       <c r="C50" t="str">
         <v/>
       </c>
+      <c r="D50" t="str">
+        <v>Electrike</v>
+      </c>
       <c r="E50" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F50" t="str">
-        <v>0.225%</v>
+        <v>23%</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -2314,11 +2461,14 @@
       <c r="C51" t="str">
         <v/>
       </c>
+      <c r="D51" t="str">
+        <v>Gulpin</v>
+      </c>
       <c r="E51" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F51" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -2352,11 +2502,14 @@
       <c r="C52" t="str">
         <v/>
       </c>
+      <c r="D52" t="str">
+        <v>Minun</v>
+      </c>
       <c r="E52" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F52" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -2390,11 +2543,14 @@
       <c r="C53" t="str">
         <v/>
       </c>
+      <c r="D53" t="str">
+        <v>Plusle</v>
+      </c>
       <c r="E53" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F53" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -2428,11 +2584,14 @@
       <c r="C54" t="str">
         <v/>
       </c>
+      <c r="D54" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E54" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F54" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -2466,11 +2625,14 @@
       <c r="C55" t="str">
         <v/>
       </c>
+      <c r="D55" t="str">
+        <v>Oddish</v>
+      </c>
       <c r="E55" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F55" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -2504,11 +2666,14 @@
       <c r="C56" t="str">
         <v/>
       </c>
+      <c r="D56" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E56" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F56" t="str">
-        <v>0.045%</v>
+        <v>5%</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -2542,11 +2707,14 @@
       <c r="C57" t="str">
         <v/>
       </c>
+      <c r="D57" t="str">
+        <v>Magnemite</v>
+      </c>
       <c r="E57" t="str">
-        <v>undefined-undefined</v>
+        <v>20-23</v>
       </c>
       <c r="F57" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -2580,11 +2748,14 @@
       <c r="C58" t="str">
         <v/>
       </c>
+      <c r="D58" t="str">
+        <v>Oddish</v>
+      </c>
       <c r="E58" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F58" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -2618,11 +2789,14 @@
       <c r="C59" t="str">
         <v/>
       </c>
+      <c r="D59" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E59" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F59" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -2656,11 +2830,14 @@
       <c r="C60" t="str">
         <v/>
       </c>
+      <c r="D60" t="str">
+        <v>Illumise</v>
+      </c>
       <c r="E60" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F60" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -2694,11 +2871,14 @@
       <c r="C61" t="str">
         <v/>
       </c>
+      <c r="D61" t="str">
+        <v>Volbeat</v>
+      </c>
       <c r="E61" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F61" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -2732,11 +2912,14 @@
       <c r="C62" t="str">
         <v/>
       </c>
+      <c r="D62" t="str">
+        <v>Roselia</v>
+      </c>
       <c r="E62" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F62" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -2770,11 +2953,14 @@
       <c r="C63" t="str">
         <v/>
       </c>
+      <c r="D63" t="str">
+        <v>Seedot</v>
+      </c>
       <c r="E63" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F63" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -2808,11 +2994,14 @@
       <c r="C64" t="str">
         <v/>
       </c>
+      <c r="D64" t="str">
+        <v>Surskit</v>
+      </c>
       <c r="E64" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F64" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -2846,11 +3035,14 @@
       <c r="C65" t="str">
         <v/>
       </c>
+      <c r="D65" t="str">
+        <v>Kirlia</v>
+      </c>
       <c r="E65" t="str">
-        <v>undefined-undefined</v>
+        <v>22-25</v>
       </c>
       <c r="F65" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -2884,11 +3076,14 @@
       <c r="C66" t="str">
         <v/>
       </c>
+      <c r="D66" t="str">
+        <v>Sandshrew</v>
+      </c>
       <c r="E66" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F66" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -2922,11 +3117,14 @@
       <c r="C67" t="str">
         <v/>
       </c>
+      <c r="D67" t="str">
+        <v>Trapinch</v>
+      </c>
       <c r="E67" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F67" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G67" t="str">
         <v/>
@@ -2960,11 +3158,14 @@
       <c r="C68" t="str">
         <v/>
       </c>
+      <c r="D68" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E68" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F68" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G68" t="str">
         <v/>
@@ -2998,11 +3199,14 @@
       <c r="C69" t="str">
         <v/>
       </c>
+      <c r="D69" t="str">
+        <v>Cacnea</v>
+      </c>
       <c r="E69" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F69" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G69" t="str">
         <v/>
@@ -3036,11 +3240,14 @@
       <c r="C70" t="str">
         <v/>
       </c>
+      <c r="D70" t="str">
+        <v>Baltoy</v>
+      </c>
       <c r="E70" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F70" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G70" t="str">
         <v/>
@@ -3074,11 +3281,14 @@
       <c r="C71" t="str">
         <v/>
       </c>
+      <c r="D71" t="str">
+        <v>Flygon</v>
+      </c>
       <c r="E71" t="str">
-        <v>undefined-undefined</v>
+        <v>23-27</v>
       </c>
       <c r="F71" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G71" t="str">
         <v/>
@@ -3087,7 +3297,7 @@
         <v>Yes</v>
       </c>
       <c r="I71" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J71" t="str">
         <v>NONONO</v>
@@ -3112,11 +3322,14 @@
       <c r="C72" t="str">
         <v/>
       </c>
+      <c r="D72" t="str">
+        <v>Numel</v>
+      </c>
       <c r="E72" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F72" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G72" t="str">
         <v/>
@@ -3150,11 +3363,14 @@
       <c r="C73" t="str">
         <v/>
       </c>
+      <c r="D73" t="str">
+        <v>Machop</v>
+      </c>
       <c r="E73" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F73" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G73" t="str">
         <v/>
@@ -3188,11 +3404,14 @@
       <c r="C74" t="str">
         <v/>
       </c>
+      <c r="D74" t="str">
+        <v>Slugma</v>
+      </c>
       <c r="E74" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F74" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G74" t="str">
         <v/>
@@ -3226,11 +3445,14 @@
       <c r="C75" t="str">
         <v/>
       </c>
+      <c r="D75" t="str">
+        <v>Torkoal</v>
+      </c>
       <c r="E75" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F75" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G75" t="str">
         <v/>
@@ -3264,11 +3486,14 @@
       <c r="C76" t="str">
         <v/>
       </c>
+      <c r="D76" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E76" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F76" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G76" t="str">
         <v/>
@@ -3302,11 +3527,14 @@
       <c r="C77" t="str">
         <v/>
       </c>
+      <c r="D77" t="str">
+        <v>Grimer</v>
+      </c>
       <c r="E77" t="str">
-        <v>undefined-undefined</v>
+        <v>27-30</v>
       </c>
       <c r="F77" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G77" t="str">
         <v/>
@@ -3340,11 +3568,14 @@
       <c r="C78" t="str">
         <v/>
       </c>
+      <c r="D78" t="str">
+        <v>Machop</v>
+      </c>
       <c r="E78" t="str">
-        <v>undefined-undefined</v>
+        <v>28-32</v>
       </c>
       <c r="F78" t="str">
-        <v>0.4275%</v>
+        <v>43%</v>
       </c>
       <c r="G78" t="str">
         <v/>
@@ -3378,11 +3609,14 @@
       <c r="C79" t="str">
         <v/>
       </c>
+      <c r="D79" t="str">
+        <v>Numel</v>
+      </c>
       <c r="E79" t="str">
-        <v>undefined-undefined</v>
+        <v>28-32</v>
       </c>
       <c r="F79" t="str">
-        <v>0.4275%</v>
+        <v>43%</v>
       </c>
       <c r="G79" t="str">
         <v/>
@@ -3416,11 +3650,14 @@
       <c r="C80" t="str">
         <v/>
       </c>
+      <c r="D80" t="str">
+        <v>Spoink</v>
+      </c>
       <c r="E80" t="str">
-        <v>undefined-undefined</v>
+        <v>28-32</v>
       </c>
       <c r="F80" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G80" t="str">
         <v/>
@@ -3454,11 +3691,14 @@
       <c r="C81" t="str">
         <v/>
       </c>
+      <c r="D81" t="str">
+        <v>Machoke</v>
+      </c>
       <c r="E81" t="str">
-        <v>undefined-undefined</v>
+        <v>28-32</v>
       </c>
       <c r="F81" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G81" t="str">
         <v/>
@@ -3492,11 +3732,14 @@
       <c r="C82" t="str">
         <v/>
       </c>
+      <c r="D82" t="str">
+        <v>Spinda</v>
+      </c>
       <c r="E82" t="str">
-        <v>undefined-undefined</v>
+        <v>30-33</v>
       </c>
       <c r="F82" t="str">
-        <v>0.7%</v>
+        <v>70%</v>
       </c>
       <c r="G82" t="str">
         <v/>
@@ -3530,11 +3773,14 @@
       <c r="C83" t="str">
         <v/>
       </c>
+      <c r="D83" t="str">
+        <v>Skarmory</v>
+      </c>
       <c r="E83" t="str">
-        <v>undefined-undefined</v>
+        <v>30-33</v>
       </c>
       <c r="F83" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G83" t="str">
         <v/>
@@ -3568,11 +3814,14 @@
       <c r="C84" t="str">
         <v/>
       </c>
+      <c r="D84" t="str">
+        <v>Sandshrew</v>
+      </c>
       <c r="E84" t="str">
-        <v>undefined-undefined</v>
+        <v>30-33</v>
       </c>
       <c r="F84" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G84" t="str">
         <v/>
@@ -3606,11 +3855,14 @@
       <c r="C85" t="str">
         <v/>
       </c>
+      <c r="D85" t="str">
+        <v>Swablu</v>
+      </c>
       <c r="E85" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F85" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G85" t="str">
         <v/>
@@ -3644,11 +3896,14 @@
       <c r="C86" t="str">
         <v/>
       </c>
+      <c r="D86" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E86" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F86" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G86" t="str">
         <v/>
@@ -3682,11 +3937,14 @@
       <c r="C87" t="str">
         <v/>
       </c>
+      <c r="D87" t="str">
+        <v>Lombre</v>
+      </c>
       <c r="E87" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F87" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G87" t="str">
         <v/>
@@ -3720,11 +3978,14 @@
       <c r="C88" t="str">
         <v/>
       </c>
+      <c r="D88" t="str">
+        <v>Nuzleaf</v>
+      </c>
       <c r="E88" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F88" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G88" t="str">
         <v/>
@@ -3758,11 +4019,14 @@
       <c r="C89" t="str">
         <v/>
       </c>
+      <c r="D89" t="str">
+        <v>Seviper</v>
+      </c>
       <c r="E89" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F89" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G89" t="str">
         <v/>
@@ -3796,11 +4060,14 @@
       <c r="C90" t="str">
         <v/>
       </c>
+      <c r="D90" t="str">
+        <v>Zangoose</v>
+      </c>
       <c r="E90" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F90" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G90" t="str">
         <v/>
@@ -3834,11 +4101,14 @@
       <c r="C91" t="str">
         <v/>
       </c>
+      <c r="D91" t="str">
+        <v>Surskit</v>
+      </c>
       <c r="E91" t="str">
-        <v>undefined-undefined</v>
+        <v>31-35</v>
       </c>
       <c r="F91" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G91" t="str">
         <v/>
@@ -3872,11 +4142,14 @@
       <c r="C92" t="str">
         <v/>
       </c>
+      <c r="D92" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E92" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F92" t="str">
-        <v>0.3325%</v>
+        <v>33%</v>
       </c>
       <c r="G92" t="str">
         <v/>
@@ -3910,11 +4183,14 @@
       <c r="C93" t="str">
         <v/>
       </c>
+      <c r="D93" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E93" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F93" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G93" t="str">
         <v/>
@@ -3948,11 +4224,14 @@
       <c r="C94" t="str">
         <v/>
       </c>
+      <c r="D94" t="str">
+        <v>Solrock</v>
+      </c>
       <c r="E94" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F94" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G94" t="str">
         <v/>
@@ -3986,11 +4265,14 @@
       <c r="C95" t="str">
         <v/>
       </c>
+      <c r="D95" t="str">
+        <v>Lunatone</v>
+      </c>
       <c r="E95" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F95" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G95" t="str">
         <v/>
@@ -4024,11 +4306,14 @@
       <c r="C96" t="str">
         <v/>
       </c>
+      <c r="D96" t="str">
+        <v>Bagon</v>
+      </c>
       <c r="E96" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F96" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G96" t="str">
         <v/>
@@ -4062,11 +4347,14 @@
       <c r="C97" t="str">
         <v/>
       </c>
+      <c r="D97" t="str">
+        <v>Beldum</v>
+      </c>
       <c r="E97" t="str">
-        <v>undefined-undefined</v>
+        <v>33-37</v>
       </c>
       <c r="F97" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G97" t="str">
         <v/>
@@ -4100,11 +4388,14 @@
       <c r="C98" t="str">
         <v/>
       </c>
+      <c r="D98" t="str">
+        <v>Swablu</v>
+      </c>
       <c r="E98" t="str">
-        <v>undefined-undefined</v>
+        <v>35-38</v>
       </c>
       <c r="F98" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G98" t="str">
         <v/>
@@ -4138,11 +4429,14 @@
       <c r="C99" t="str">
         <v/>
       </c>
+      <c r="D99" t="str">
+        <v>Taillow</v>
+      </c>
       <c r="E99" t="str">
-        <v>undefined-undefined</v>
+        <v>35-38</v>
       </c>
       <c r="F99" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G99" t="str">
         <v/>
@@ -4176,11 +4470,14 @@
       <c r="C100" t="str">
         <v/>
       </c>
+      <c r="D100" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E100" t="str">
-        <v>undefined-undefined</v>
+        <v>35-38</v>
       </c>
       <c r="F100" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G100" t="str">
         <v/>
@@ -4214,11 +4511,14 @@
       <c r="C101" t="str">
         <v/>
       </c>
+      <c r="D101" t="str">
+        <v>Jigglypuff</v>
+      </c>
       <c r="E101" t="str">
-        <v>undefined-undefined</v>
+        <v>35-38</v>
       </c>
       <c r="F101" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G101" t="str">
         <v/>
@@ -4252,11 +4552,14 @@
       <c r="C102" t="str">
         <v/>
       </c>
+      <c r="D102" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E102" t="str">
-        <v>undefined-undefined</v>
+        <v>35-38</v>
       </c>
       <c r="F102" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G102" t="str">
         <v/>
@@ -4290,11 +4593,14 @@
       <c r="C103" t="str">
         <v/>
       </c>
+      <c r="D103" t="str">
+        <v>Electrike</v>
+      </c>
       <c r="E103" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F103" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G103" t="str">
         <v/>
@@ -4328,11 +4634,14 @@
       <c r="C104" t="str">
         <v/>
       </c>
+      <c r="D104" t="str">
+        <v>Linoone</v>
+      </c>
       <c r="E104" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F104" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G104" t="str">
         <v/>
@@ -4366,11 +4675,14 @@
       <c r="C105" t="str">
         <v/>
       </c>
+      <c r="D105" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E105" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F105" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G105" t="str">
         <v/>
@@ -4404,11 +4716,14 @@
       <c r="C106" t="str">
         <v/>
       </c>
+      <c r="D106" t="str">
+        <v>Manectric</v>
+      </c>
       <c r="E106" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F106" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G106" t="str">
         <v/>
@@ -4442,11 +4757,14 @@
       <c r="C107" t="str">
         <v/>
       </c>
+      <c r="D107" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E107" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F107" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G107" t="str">
         <v/>
@@ -4480,11 +4798,14 @@
       <c r="C108" t="str">
         <v/>
       </c>
+      <c r="D108" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E108" t="str">
-        <v>undefined-undefined</v>
+        <v>38-41</v>
       </c>
       <c r="F108" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G108" t="str">
         <v/>
@@ -4518,11 +4839,14 @@
       <c r="C109" t="str">
         <v/>
       </c>
+      <c r="D109" t="str">
+        <v>Carvanha</v>
+      </c>
       <c r="E109" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F109" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G109" t="str">
         <v/>
@@ -4556,11 +4880,14 @@
       <c r="C110" t="str">
         <v/>
       </c>
+      <c r="D110" t="str">
+        <v>Barboach</v>
+      </c>
       <c r="E110" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F110" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G110" t="str">
         <v/>
@@ -4594,11 +4921,14 @@
       <c r="C111" t="str">
         <v/>
       </c>
+      <c r="D111" t="str">
+        <v>Corphish</v>
+      </c>
       <c r="E111" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F111" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G111" t="str">
         <v/>
@@ -4632,11 +4962,14 @@
       <c r="C112" t="str">
         <v/>
       </c>
+      <c r="D112" t="str">
+        <v>Wailmer</v>
+      </c>
       <c r="E112" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F112" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G112" t="str">
         <v/>
@@ -4670,11 +5003,14 @@
       <c r="C113" t="str">
         <v/>
       </c>
+      <c r="D113" t="str">
+        <v>Goldeen</v>
+      </c>
       <c r="E113" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F113" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G113" t="str">
         <v/>
@@ -4708,11 +5044,14 @@
       <c r="C114" t="str">
         <v/>
       </c>
+      <c r="D114" t="str">
+        <v>Tentacool</v>
+      </c>
       <c r="E114" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F114" t="str">
-        <v>0.18%</v>
+        <v>18%</v>
       </c>
       <c r="G114" t="str">
         <v/>
@@ -4746,11 +5085,14 @@
       <c r="C115" t="str">
         <v/>
       </c>
+      <c r="D115" t="str">
+        <v>Luvdisc</v>
+      </c>
       <c r="E115" t="str">
-        <v>undefined-undefined</v>
+        <v>40-43</v>
       </c>
       <c r="F115" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G115" t="str">
         <v/>
@@ -4784,11 +5126,14 @@
       <c r="C116" t="str">
         <v/>
       </c>
+      <c r="D116" t="str">
+        <v>Linoone</v>
+      </c>
       <c r="E116" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F116" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G116" t="str">
         <v/>
@@ -4822,11 +5167,14 @@
       <c r="C117" t="str">
         <v/>
       </c>
+      <c r="D117" t="str">
+        <v>Oddish</v>
+      </c>
       <c r="E117" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F117" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G117" t="str">
         <v/>
@@ -4860,11 +5208,14 @@
       <c r="C118" t="str">
         <v/>
       </c>
+      <c r="D118" t="str">
+        <v>Tropius</v>
+      </c>
       <c r="E118" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F118" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G118" t="str">
         <v/>
@@ -4898,11 +5249,14 @@
       <c r="C119" t="str">
         <v/>
       </c>
+      <c r="D119" t="str">
+        <v>Wingull</v>
+      </c>
       <c r="E119" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F119" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G119" t="str">
         <v/>
@@ -4936,11 +5290,14 @@
       <c r="C120" t="str">
         <v/>
       </c>
+      <c r="D120" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E120" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F120" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G120" t="str">
         <v/>
@@ -4974,11 +5331,14 @@
       <c r="C121" t="str">
         <v/>
       </c>
+      <c r="D121" t="str">
+        <v>Pelipper</v>
+      </c>
       <c r="E121" t="str">
-        <v>undefined-undefined</v>
+        <v>41-45</v>
       </c>
       <c r="F121" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G121" t="str">
         <v/>
@@ -5012,11 +5372,14 @@
       <c r="C122" t="str">
         <v/>
       </c>
+      <c r="D122" t="str">
+        <v>Linoone</v>
+      </c>
       <c r="E122" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F122" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G122" t="str">
         <v/>
@@ -5050,11 +5413,14 @@
       <c r="C123" t="str">
         <v/>
       </c>
+      <c r="D123" t="str">
+        <v>Mightyena</v>
+      </c>
       <c r="E123" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F123" t="str">
-        <v>0.19%</v>
+        <v>19%</v>
       </c>
       <c r="G123" t="str">
         <v/>
@@ -5088,11 +5454,14 @@
       <c r="C124" t="str">
         <v/>
       </c>
+      <c r="D124" t="str">
+        <v>Oddish</v>
+      </c>
       <c r="E124" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F124" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G124" t="str">
         <v/>
@@ -5126,11 +5495,14 @@
       <c r="C125" t="str">
         <v/>
       </c>
+      <c r="D125" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E125" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F125" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G125" t="str">
         <v/>
@@ -5164,11 +5536,14 @@
       <c r="C126" t="str">
         <v/>
       </c>
+      <c r="D126" t="str">
+        <v>Absol</v>
+      </c>
       <c r="E126" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F126" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G126" t="str">
         <v/>
@@ -5202,11 +5577,14 @@
       <c r="C127" t="str">
         <v/>
       </c>
+      <c r="D127" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E127" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F127" t="str">
-        <v>0.095%</v>
+        <v>10%</v>
       </c>
       <c r="G127" t="str">
         <v/>
@@ -5240,11 +5618,14 @@
       <c r="C128" t="str">
         <v/>
       </c>
+      <c r="D128" t="str">
+        <v>Surskit</v>
+      </c>
       <c r="E128" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F128" t="str">
-        <v>0.0475%</v>
+        <v>5%</v>
       </c>
       <c r="G128" t="str">
         <v/>
@@ -5278,11 +5659,14 @@
       <c r="C129" t="str">
         <v/>
       </c>
+      <c r="D129" t="str">
+        <v>Masquerain</v>
+      </c>
       <c r="E129" t="str">
-        <v>undefined-undefined</v>
+        <v>43-46</v>
       </c>
       <c r="F129" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G129" t="str">
         <v/>
@@ -5316,11 +5700,14 @@
       <c r="C130" t="str">
         <v/>
       </c>
+      <c r="D130" t="str">
+        <v>Poochyena</v>
+      </c>
       <c r="E130" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F130" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G130" t="str">
         <v/>
@@ -5354,11 +5741,14 @@
       <c r="C131" t="str">
         <v/>
       </c>
+      <c r="D131" t="str">
+        <v>Mightyena</v>
+      </c>
       <c r="E131" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F131" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G131" t="str">
         <v/>
@@ -5392,11 +5782,14 @@
       <c r="C132" t="str">
         <v/>
       </c>
+      <c r="D132" t="str">
+        <v>Shuppet</v>
+      </c>
       <c r="E132" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F132" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G132" t="str">
         <v/>
@@ -5430,11 +5823,14 @@
       <c r="C133" t="str">
         <v/>
       </c>
+      <c r="D133" t="str">
+        <v>Duskull</v>
+      </c>
       <c r="E133" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F133" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G133" t="str">
         <v/>
@@ -5468,11 +5864,14 @@
       <c r="C134" t="str">
         <v/>
       </c>
+      <c r="D134" t="str">
+        <v>Gloom</v>
+      </c>
       <c r="E134" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F134" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G134" t="str">
         <v/>
@@ -5506,11 +5905,14 @@
       <c r="C135" t="str">
         <v/>
       </c>
+      <c r="D135" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E135" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F135" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G135" t="str">
         <v/>
@@ -5544,11 +5946,14 @@
       <c r="C136" t="str">
         <v/>
       </c>
+      <c r="D136" t="str">
+        <v>Pikachu</v>
+      </c>
       <c r="E136" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F136" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G136" t="str">
         <v/>
@@ -5582,11 +5987,14 @@
       <c r="C137" t="str">
         <v/>
       </c>
+      <c r="D137" t="str">
+        <v>Natu</v>
+      </c>
       <c r="E137" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F137" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G137" t="str">
         <v/>
@@ -5620,11 +6028,14 @@
       <c r="C138" t="str">
         <v/>
       </c>
+      <c r="D138" t="str">
+        <v>Pinsir</v>
+      </c>
       <c r="E138" t="str">
-        <v>undefined-undefined</v>
+        <v>51-55</v>
       </c>
       <c r="F138" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G138" t="str">
         <v/>
@@ -5633,7 +6044,7 @@
         <v>Yes</v>
       </c>
       <c r="I138" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J138" t="str">
         <v>NONONO</v>
@@ -5658,11 +6069,14 @@
       <c r="C139" t="str">
         <v/>
       </c>
+      <c r="D139" t="str">
+        <v>Phanpy</v>
+      </c>
       <c r="E139" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F139" t="str">
-        <v>0.07%</v>
+        <v>7%</v>
       </c>
       <c r="G139" t="str">
         <v/>
@@ -5696,11 +6110,14 @@
       <c r="C140" t="str">
         <v/>
       </c>
+      <c r="D140" t="str">
+        <v>Geodude</v>
+      </c>
       <c r="E140" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F140" t="str">
-        <v>0.11%</v>
+        <v>11%</v>
       </c>
       <c r="G140" t="str">
         <v/>
@@ -5734,11 +6151,14 @@
       <c r="C141" t="str">
         <v/>
       </c>
+      <c r="D141" t="str">
+        <v>Aipom</v>
+      </c>
       <c r="E141" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F141" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G141" t="str">
         <v/>
@@ -5772,11 +6192,14 @@
       <c r="C142" t="str">
         <v/>
       </c>
+      <c r="D142" t="str">
+        <v>Houndour</v>
+      </c>
       <c r="E142" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F142" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G142" t="str">
         <v/>
@@ -5810,11 +6233,14 @@
       <c r="C143" t="str">
         <v/>
       </c>
+      <c r="D143" t="str">
+        <v>Sunkern</v>
+      </c>
       <c r="E143" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F143" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G143" t="str">
         <v/>
@@ -5848,11 +6274,14 @@
       <c r="C144" t="str">
         <v/>
       </c>
+      <c r="D144" t="str">
+        <v>Shuckle</v>
+      </c>
       <c r="E144" t="str">
-        <v>undefined-undefined</v>
+        <v>51-55</v>
       </c>
       <c r="F144" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G144" t="str">
         <v/>
@@ -5861,7 +6290,7 @@
         <v>Yes</v>
       </c>
       <c r="I144" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J144" t="str">
         <v>NONONO</v>
@@ -5886,11 +6315,14 @@
       <c r="C145" t="str">
         <v/>
       </c>
+      <c r="D145" t="str">
+        <v>Doduo</v>
+      </c>
       <c r="E145" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F145" t="str">
-        <v>0.12%</v>
+        <v>12%</v>
       </c>
       <c r="G145" t="str">
         <v/>
@@ -5924,11 +6356,14 @@
       <c r="C146" t="str">
         <v/>
       </c>
+      <c r="D146" t="str">
+        <v>Rhyhorn</v>
+      </c>
       <c r="E146" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F146" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G146" t="str">
         <v/>
@@ -5962,11 +6397,14 @@
       <c r="C147" t="str">
         <v/>
       </c>
+      <c r="D147" t="str">
+        <v>Girafarig</v>
+      </c>
       <c r="E147" t="str">
-        <v>undefined-undefined</v>
+        <v>50-54</v>
       </c>
       <c r="F147" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G147" t="str">
         <v/>
@@ -6000,11 +6438,14 @@
       <c r="C148" t="str">
         <v/>
       </c>
+      <c r="D148" t="str">
+        <v>Psyduck</v>
+      </c>
       <c r="E148" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F148" t="str">
-        <v>0.12%</v>
+        <v>12%</v>
       </c>
       <c r="G148" t="str">
         <v/>
@@ -6038,11 +6479,14 @@
       <c r="C149" t="str">
         <v/>
       </c>
+      <c r="D149" t="str">
+        <v>Xatu</v>
+      </c>
       <c r="E149" t="str">
-        <v>undefined-undefined</v>
+        <v>50-54</v>
       </c>
       <c r="F149" t="str">
-        <v>0.12%</v>
+        <v>12%</v>
       </c>
       <c r="G149" t="str">
         <v/>
@@ -6076,11 +6520,14 @@
       <c r="C150" t="str">
         <v/>
       </c>
+      <c r="D150" t="str">
+        <v>Teddiursa</v>
+      </c>
       <c r="E150" t="str">
-        <v>undefined-undefined</v>
+        <v>46-50</v>
       </c>
       <c r="F150" t="str">
-        <v>0.08%</v>
+        <v>8%</v>
       </c>
       <c r="G150" t="str">
         <v/>
@@ -6114,11 +6561,14 @@
       <c r="C151" t="str">
         <v/>
       </c>
+      <c r="D151" t="str">
+        <v>Stantler</v>
+      </c>
       <c r="E151" t="str">
-        <v>undefined-undefined</v>
+        <v>50-54</v>
       </c>
       <c r="F151" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G151" t="str">
         <v/>
@@ -6152,11 +6602,14 @@
       <c r="C152" t="str">
         <v/>
       </c>
+      <c r="D152" t="str">
+        <v>Wooper</v>
+      </c>
       <c r="E152" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F152" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G152" t="str">
         <v/>
@@ -6190,11 +6643,14 @@
       <c r="C153" t="str">
         <v/>
       </c>
+      <c r="D153" t="str">
+        <v>Ledyba</v>
+      </c>
       <c r="E153" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F153" t="str">
-        <v>0.11%</v>
+        <v>11%</v>
       </c>
       <c r="G153" t="str">
         <v/>
@@ -6228,11 +6684,14 @@
       <c r="C154" t="str">
         <v/>
       </c>
+      <c r="D154" t="str">
+        <v>Gloom</v>
+      </c>
       <c r="E154" t="str">
-        <v>undefined-undefined</v>
+        <v>48-52</v>
       </c>
       <c r="F154" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G154" t="str">
         <v/>
@@ -6266,11 +6725,14 @@
       <c r="C155" t="str">
         <v/>
       </c>
+      <c r="D155" t="str">
+        <v>Heracross</v>
+      </c>
       <c r="E155" t="str">
-        <v>undefined-undefined</v>
+        <v>51-55</v>
       </c>
       <c r="F155" t="str">
-        <v>0.16%</v>
+        <v>16%</v>
       </c>
       <c r="G155" t="str">
         <v/>
@@ -6304,11 +6766,14 @@
       <c r="C156" t="str">
         <v/>
       </c>
+      <c r="D156" t="str">
+        <v>Wobbuffet</v>
+      </c>
       <c r="E156" t="str">
-        <v>undefined-undefined</v>
+        <v>48-52</v>
       </c>
       <c r="F156" t="str">
-        <v>0.16%</v>
+        <v>16%</v>
       </c>
       <c r="G156" t="str">
         <v/>
@@ -6342,11 +6807,14 @@
       <c r="C157" t="str">
         <v/>
       </c>
+      <c r="D157" t="str">
+        <v>Golduck</v>
+      </c>
       <c r="E157" t="str">
-        <v>undefined-undefined</v>
+        <v>51-55</v>
       </c>
       <c r="F157" t="str">
-        <v>0.12%</v>
+        <v>12%</v>
       </c>
       <c r="G157" t="str">
         <v/>
@@ -6380,11 +6848,14 @@
       <c r="C158" t="str">
         <v/>
       </c>
+      <c r="D158" t="str">
+        <v>Mareep</v>
+      </c>
       <c r="E158" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F158" t="str">
-        <v>0.12%</v>
+        <v>12%</v>
       </c>
       <c r="G158" t="str">
         <v/>
@@ -6418,11 +6889,14 @@
       <c r="C159" t="str">
         <v/>
       </c>
+      <c r="D159" t="str">
+        <v>Gligar</v>
+      </c>
       <c r="E159" t="str">
-        <v>undefined-undefined</v>
+        <v>48-52</v>
       </c>
       <c r="F159" t="str">
-        <v>0.13%</v>
+        <v>13%</v>
       </c>
       <c r="G159" t="str">
         <v/>
@@ -6456,11 +6930,14 @@
       <c r="C160" t="str">
         <v/>
       </c>
+      <c r="D160" t="str">
+        <v>Pineco</v>
+      </c>
       <c r="E160" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F160" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G160" t="str">
         <v/>
@@ -6494,11 +6971,14 @@
       <c r="C161" t="str">
         <v/>
       </c>
+      <c r="D161" t="str">
+        <v>Quagsire</v>
+      </c>
       <c r="E161" t="str">
-        <v>undefined-undefined</v>
+        <v>48-52</v>
       </c>
       <c r="F161" t="str">
-        <v>0.13%</v>
+        <v>13%</v>
       </c>
       <c r="G161" t="str">
         <v/>
@@ -6532,11 +7012,14 @@
       <c r="C162" t="str">
         <v/>
       </c>
+      <c r="D162" t="str">
+        <v>Spinarak</v>
+      </c>
       <c r="E162" t="str">
-        <v>undefined-undefined</v>
+        <v>44-48</v>
       </c>
       <c r="F162" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G162" t="str">
         <v/>
@@ -6570,11 +7053,14 @@
       <c r="C163" t="str">
         <v/>
       </c>
+      <c r="D163" t="str">
+        <v>Shuppet</v>
+      </c>
       <c r="E163" t="str">
-        <v>undefined-undefined</v>
+        <v>48-51</v>
       </c>
       <c r="F163" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G163" t="str">
         <v/>
@@ -6608,11 +7094,14 @@
       <c r="C164" t="str">
         <v/>
       </c>
+      <c r="D164" t="str">
+        <v>Duskull</v>
+      </c>
       <c r="E164" t="str">
-        <v>undefined-undefined</v>
+        <v>48-51</v>
       </c>
       <c r="F164" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G164" t="str">
         <v/>
@@ -6646,11 +7135,14 @@
       <c r="C165" t="str">
         <v/>
       </c>
+      <c r="D165" t="str">
+        <v>Vulpix</v>
+      </c>
       <c r="E165" t="str">
-        <v>undefined-undefined</v>
+        <v>48-51</v>
       </c>
       <c r="F165" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G165" t="str">
         <v/>
@@ -6684,11 +7176,14 @@
       <c r="C166" t="str">
         <v/>
       </c>
+      <c r="D166" t="str">
+        <v>Meditite</v>
+      </c>
       <c r="E166" t="str">
-        <v>undefined-undefined</v>
+        <v>48-51</v>
       </c>
       <c r="F166" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G166" t="str">
         <v/>
@@ -6722,11 +7217,14 @@
       <c r="C167" t="str">
         <v/>
       </c>
+      <c r="D167" t="str">
+        <v>Chimecho</v>
+      </c>
       <c r="E167" t="str">
-        <v>undefined-undefined</v>
+        <v>48-51</v>
       </c>
       <c r="F167" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G167" t="str">
         <v/>
@@ -6760,11 +7258,14 @@
       <c r="C168" t="str">
         <v/>
       </c>
+      <c r="D168" t="str">
+        <v>Mightyena</v>
+      </c>
       <c r="E168" t="str">
-        <v>undefined-undefined</v>
+        <v>49-53</v>
       </c>
       <c r="F168" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G168" t="str">
         <v/>
@@ -6798,11 +7299,14 @@
       <c r="C169" t="str">
         <v/>
       </c>
+      <c r="D169" t="str">
+        <v>Shuppet</v>
+      </c>
       <c r="E169" t="str">
-        <v>undefined-undefined</v>
+        <v>49-53</v>
       </c>
       <c r="F169" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G169" t="str">
         <v/>
@@ -6836,11 +7340,14 @@
       <c r="C170" t="str">
         <v/>
       </c>
+      <c r="D170" t="str">
+        <v>Duskull</v>
+      </c>
       <c r="E170" t="str">
-        <v>undefined-undefined</v>
+        <v>49-53</v>
       </c>
       <c r="F170" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G170" t="str">
         <v/>
@@ -6874,11 +7381,14 @@
       <c r="C171" t="str">
         <v/>
       </c>
+      <c r="D171" t="str">
+        <v>Gloom</v>
+      </c>
       <c r="E171" t="str">
-        <v>undefined-undefined</v>
+        <v>49-53</v>
       </c>
       <c r="F171" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G171" t="str">
         <v/>
@@ -6912,11 +7422,14 @@
       <c r="C172" t="str">
         <v/>
       </c>
+      <c r="D172" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E172" t="str">
-        <v>undefined-undefined</v>
+        <v>49-53</v>
       </c>
       <c r="F172" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G172" t="str">
         <v/>
@@ -6950,11 +7463,14 @@
       <c r="C173" t="str">
         <v/>
       </c>
+      <c r="D173" t="str">
+        <v>Wailmer</v>
+      </c>
       <c r="E173" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F173" t="str">
-        <v>0.198%</v>
+        <v>20%</v>
       </c>
       <c r="G173" t="str">
         <v/>
@@ -6988,11 +7504,14 @@
       <c r="C174" t="str">
         <v/>
       </c>
+      <c r="D174" t="str">
+        <v>Sharpedo</v>
+      </c>
       <c r="E174" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F174" t="str">
-        <v>0.198%</v>
+        <v>20%</v>
       </c>
       <c r="G174" t="str">
         <v/>
@@ -7026,11 +7545,14 @@
       <c r="C175" t="str">
         <v/>
       </c>
+      <c r="D175" t="str">
+        <v>Seaking</v>
+      </c>
       <c r="E175" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F175" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G175" t="str">
         <v/>
@@ -7064,11 +7586,14 @@
       <c r="C176" t="str">
         <v/>
       </c>
+      <c r="D176" t="str">
+        <v>Whiscash</v>
+      </c>
       <c r="E176" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F176" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G176" t="str">
         <v/>
@@ -7102,11 +7627,14 @@
       <c r="C177" t="str">
         <v/>
       </c>
+      <c r="D177" t="str">
+        <v>Corsola</v>
+      </c>
       <c r="E177" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F177" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G177" t="str">
         <v/>
@@ -7140,11 +7668,14 @@
       <c r="C178" t="str">
         <v/>
       </c>
+      <c r="D178" t="str">
+        <v>Tentacruel</v>
+      </c>
       <c r="E178" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F178" t="str">
-        <v>0.072%</v>
+        <v>7%</v>
       </c>
       <c r="G178" t="str">
         <v/>
@@ -7178,11 +7709,14 @@
       <c r="C179" t="str">
         <v/>
       </c>
+      <c r="D179" t="str">
+        <v>Feebas</v>
+      </c>
       <c r="E179" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F179" t="str">
-        <v>0.072%</v>
+        <v>7%</v>
       </c>
       <c r="G179" t="str">
         <v/>
@@ -7216,11 +7750,14 @@
       <c r="C180" t="str">
         <v/>
       </c>
+      <c r="D180" t="str">
+        <v>Horsea</v>
+      </c>
       <c r="E180" t="str">
-        <v>undefined-undefined</v>
+        <v>54-58</v>
       </c>
       <c r="F180" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G180" t="str">
         <v/>
@@ -7254,11 +7791,14 @@
       <c r="C181" t="str">
         <v/>
       </c>
+      <c r="D181" t="str">
+        <v>Clamperl</v>
+      </c>
       <c r="E181" t="str">
-        <v>undefined-undefined</v>
+        <v>56-60</v>
       </c>
       <c r="F181" t="str">
-        <v>0.585%</v>
+        <v>59%</v>
       </c>
       <c r="G181" t="str">
         <v/>
@@ -7292,11 +7832,14 @@
       <c r="C182" t="str">
         <v/>
       </c>
+      <c r="D182" t="str">
+        <v>Chinchou</v>
+      </c>
       <c r="E182" t="str">
-        <v>undefined-undefined</v>
+        <v>56-60</v>
       </c>
       <c r="F182" t="str">
-        <v>0.225%</v>
+        <v>23%</v>
       </c>
       <c r="G182" t="str">
         <v/>
@@ -7330,11 +7873,14 @@
       <c r="C183" t="str">
         <v/>
       </c>
+      <c r="D183" t="str">
+        <v>Relicanth</v>
+      </c>
       <c r="E183" t="str">
-        <v>undefined-undefined</v>
+        <v>56-60</v>
       </c>
       <c r="F183" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G183" t="str">
         <v/>
@@ -7368,11 +7914,14 @@
       <c r="C184" t="str">
         <v/>
       </c>
+      <c r="D184" t="str">
+        <v>Seadra</v>
+      </c>
       <c r="E184" t="str">
-        <v>undefined-undefined</v>
+        <v>56-60</v>
       </c>
       <c r="F184" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G184" t="str">
         <v/>
@@ -7406,11 +7955,14 @@
       <c r="C185" t="str">
         <v/>
       </c>
+      <c r="D185" t="str">
+        <v>Spheal</v>
+      </c>
       <c r="E185" t="str">
-        <v>undefined-undefined</v>
+        <v>59-63</v>
       </c>
       <c r="F185" t="str">
-        <v>0.405%</v>
+        <v>41%</v>
       </c>
       <c r="G185" t="str">
         <v/>
@@ -7444,11 +7996,14 @@
       <c r="C186" t="str">
         <v/>
       </c>
+      <c r="D186" t="str">
+        <v>Zubat</v>
+      </c>
       <c r="E186" t="str">
-        <v>undefined-undefined</v>
+        <v>59-63</v>
       </c>
       <c r="F186" t="str">
-        <v>0.27%</v>
+        <v>27%</v>
       </c>
       <c r="G186" t="str">
         <v/>
@@ -7482,11 +8037,14 @@
       <c r="C187" t="str">
         <v/>
       </c>
+      <c r="D187" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E187" t="str">
-        <v>undefined-undefined</v>
+        <v>59-63</v>
       </c>
       <c r="F187" t="str">
-        <v>0.135%</v>
+        <v>14%</v>
       </c>
       <c r="G187" t="str">
         <v/>
@@ -7520,11 +8078,14 @@
       <c r="C188" t="str">
         <v/>
       </c>
+      <c r="D188" t="str">
+        <v>Snorunt</v>
+      </c>
       <c r="E188" t="str">
-        <v>undefined-undefined</v>
+        <v>59-63</v>
       </c>
       <c r="F188" t="str">
-        <v>0.09%</v>
+        <v>9%</v>
       </c>
       <c r="G188" t="str">
         <v/>
@@ -7558,11 +8119,14 @@
       <c r="C189" t="str">
         <v/>
       </c>
+      <c r="D189" t="str">
+        <v>Sealeo</v>
+      </c>
       <c r="E189" t="str">
-        <v>undefined-undefined</v>
+        <v>59-63</v>
       </c>
       <c r="F189" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G189" t="str">
         <v/>
@@ -7596,11 +8160,14 @@
       <c r="C190" t="str">
         <v/>
       </c>
+      <c r="D190" t="str">
+        <v>Wynaut</v>
+      </c>
       <c r="E190" t="str">
-        <v>undefined-undefined</v>
+        <v>61-65</v>
       </c>
       <c r="F190" t="str">
-        <v>1%</v>
+        <v>100%</v>
       </c>
       <c r="G190" t="str">
         <v/>
@@ -7634,11 +8201,14 @@
       <c r="C191" t="str">
         <v/>
       </c>
+      <c r="D191" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E191" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F191" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G191" t="str">
         <v/>
@@ -7672,11 +8242,14 @@
       <c r="C192" t="str">
         <v/>
       </c>
+      <c r="D192" t="str">
+        <v>Hariyama</v>
+      </c>
       <c r="E192" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F192" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G192" t="str">
         <v/>
@@ -7710,11 +8283,14 @@
       <c r="C193" t="str">
         <v/>
       </c>
+      <c r="D193" t="str">
+        <v>Lairon</v>
+      </c>
       <c r="E193" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F193" t="str">
-        <v>0.152%</v>
+        <v>15%</v>
       </c>
       <c r="G193" t="str">
         <v/>
@@ -7748,11 +8324,14 @@
       <c r="C194" t="str">
         <v/>
       </c>
+      <c r="D194" t="str">
+        <v>Medicham</v>
+      </c>
       <c r="E194" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F194" t="str">
-        <v>0.152%</v>
+        <v>15%</v>
       </c>
       <c r="G194" t="str">
         <v/>
@@ -7786,11 +8365,14 @@
       <c r="C195" t="str">
         <v/>
       </c>
+      <c r="D195" t="str">
+        <v>Loudred</v>
+      </c>
       <c r="E195" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F195" t="str">
-        <v>0.114%</v>
+        <v>11%</v>
       </c>
       <c r="G195" t="str">
         <v/>
@@ -7824,11 +8406,14 @@
       <c r="C196" t="str">
         <v/>
       </c>
+      <c r="D196" t="str">
+        <v>Graveler</v>
+      </c>
       <c r="E196" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F196" t="str">
-        <v>0.057%</v>
+        <v>6%</v>
       </c>
       <c r="G196" t="str">
         <v/>
@@ -7862,11 +8447,14 @@
       <c r="C197" t="str">
         <v/>
       </c>
+      <c r="D197" t="str">
+        <v>Exploud</v>
+      </c>
       <c r="E197" t="str">
-        <v>undefined-undefined</v>
+        <v>64-68</v>
       </c>
       <c r="F197" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G197" t="str">
         <v/>
@@ -7900,11 +8488,14 @@
       <c r="C198" t="str">
         <v/>
       </c>
+      <c r="D198" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E198" t="str">
-        <v>undefined-undefined</v>
+        <v>62-66</v>
       </c>
       <c r="F198" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G198" t="str">
         <v/>
@@ -7938,11 +8529,14 @@
       <c r="C199" t="str">
         <v/>
       </c>
+      <c r="D199" t="str">
+        <v>Claydol</v>
+      </c>
       <c r="E199" t="str">
-        <v>undefined-undefined</v>
+        <v>62-66</v>
       </c>
       <c r="F199" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G199" t="str">
         <v/>
@@ -7976,11 +8570,14 @@
       <c r="C200" t="str">
         <v/>
       </c>
+      <c r="D200" t="str">
+        <v>Altaria</v>
+      </c>
       <c r="E200" t="str">
-        <v>undefined-undefined</v>
+        <v>62-66</v>
       </c>
       <c r="F200" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G200" t="str">
         <v/>
@@ -8014,11 +8611,14 @@
       <c r="C201" t="str">
         <v/>
       </c>
+      <c r="D201" t="str">
+        <v>Dusclops</v>
+      </c>
       <c r="E201" t="str">
-        <v>undefined-undefined</v>
+        <v>62-66</v>
       </c>
       <c r="F201" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G201" t="str">
         <v/>
@@ -8052,11 +8652,14 @@
       <c r="C202" t="str">
         <v/>
       </c>
+      <c r="D202" t="str">
+        <v>Banette</v>
+      </c>
       <c r="E202" t="str">
-        <v>undefined-undefined</v>
+        <v>62-66</v>
       </c>
       <c r="F202" t="str">
-        <v>0.1%</v>
+        <v>10%</v>
       </c>
       <c r="G202" t="str">
         <v/>
@@ -8090,11 +8693,14 @@
       <c r="C203" t="str">
         <v/>
       </c>
+      <c r="D203" t="str">
+        <v>Deoxys</v>
+      </c>
       <c r="E203" t="str">
-        <v>undefined-undefined</v>
+        <v>120-120</v>
       </c>
       <c r="F203" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G203" t="str">
         <v/>
@@ -8128,11 +8734,14 @@
       <c r="C204" t="str">
         <v/>
       </c>
+      <c r="D204" t="str">
+        <v>Jirachi</v>
+      </c>
       <c r="E204" t="str">
-        <v>undefined-undefined</v>
+        <v>120-120</v>
       </c>
       <c r="F204" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G204" t="str">
         <v/>
@@ -8166,11 +8775,14 @@
       <c r="C205" t="str">
         <v/>
       </c>
+      <c r="D205" t="str">
+        <v>Latias</v>
+      </c>
       <c r="E205" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F205" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G205" t="str">
         <v/>
@@ -8204,11 +8816,14 @@
       <c r="C206" t="str">
         <v/>
       </c>
+      <c r="D206" t="str">
+        <v>Latios</v>
+      </c>
       <c r="E206" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F206" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G206" t="str">
         <v/>
@@ -8242,11 +8857,14 @@
       <c r="C207" t="str">
         <v/>
       </c>
+      <c r="D207" t="str">
+        <v>Kecleon</v>
+      </c>
       <c r="E207" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F207" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G207" t="str">
         <v/>
@@ -8280,11 +8898,14 @@
       <c r="C208" t="str">
         <v/>
       </c>
+      <c r="D208" t="str">
+        <v>Voltorb</v>
+      </c>
       <c r="E208" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F208" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G208" t="str">
         <v/>
@@ -8318,11 +8939,14 @@
       <c r="C209" t="str">
         <v/>
       </c>
+      <c r="D209" t="str">
+        <v>Electrike</v>
+      </c>
       <c r="E209" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F209" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G209" t="str">
         <v/>
@@ -8356,11 +8980,14 @@
       <c r="C210" t="str">
         <v/>
       </c>
+      <c r="D210" t="str">
+        <v>Electrode</v>
+      </c>
       <c r="E210" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F210" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G210" t="str">
         <v/>
@@ -8394,11 +9021,14 @@
       <c r="C211" t="str">
         <v/>
       </c>
+      <c r="D211" t="str">
+        <v>Lileep</v>
+      </c>
       <c r="E211" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F211" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G211" t="str">
         <v/>
@@ -8432,11 +9062,14 @@
       <c r="C212" t="str">
         <v/>
       </c>
+      <c r="D212" t="str">
+        <v>Anorith</v>
+      </c>
       <c r="E212" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F212" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G212" t="str">
         <v/>
@@ -8470,11 +9103,14 @@
       <c r="C213" t="str">
         <v/>
       </c>
+      <c r="D213" t="str">
+        <v>Cradily</v>
+      </c>
       <c r="E213" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F213" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G213" t="str">
         <v/>
@@ -8508,11 +9144,14 @@
       <c r="C214" t="str">
         <v/>
       </c>
+      <c r="D214" t="str">
+        <v>Armaldo</v>
+      </c>
       <c r="E214" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F214" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G214" t="str">
         <v/>
@@ -8546,11 +9185,14 @@
       <c r="C215" t="str">
         <v/>
       </c>
+      <c r="D215" t="str">
+        <v>Tentacruel</v>
+      </c>
       <c r="E215" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F215" t="str">
-        <v>0.3325%</v>
+        <v>33%</v>
       </c>
       <c r="G215" t="str">
         <v/>
@@ -8584,11 +9226,14 @@
       <c r="C216" t="str">
         <v/>
       </c>
+      <c r="D216" t="str">
+        <v>Golduck</v>
+      </c>
       <c r="E216" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F216" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G216" t="str">
         <v/>
@@ -8622,11 +9267,14 @@
       <c r="C217" t="str">
         <v/>
       </c>
+      <c r="D217" t="str">
+        <v>Marill</v>
+      </c>
       <c r="E217" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F217" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G217" t="str">
         <v/>
@@ -8635,7 +9283,7 @@
         <v>Yes</v>
       </c>
       <c r="I217" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J217" t="str">
         <v>NONONO</v>
@@ -8660,11 +9308,14 @@
       <c r="C218" t="str">
         <v/>
       </c>
+      <c r="D218" t="str">
+        <v>Azumarill</v>
+      </c>
       <c r="E218" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F218" t="str">
-        <v>0.1425%</v>
+        <v>14%</v>
       </c>
       <c r="G218" t="str">
         <v/>
@@ -8698,11 +9349,14 @@
       <c r="C219" t="str">
         <v/>
       </c>
+      <c r="D219" t="str">
+        <v>Gorebyss</v>
+      </c>
       <c r="E219" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F219" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G219" t="str">
         <v/>
@@ -8736,11 +9390,14 @@
       <c r="C220" t="str">
         <v/>
       </c>
+      <c r="D220" t="str">
+        <v>Mightyena</v>
+      </c>
       <c r="E220" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F220" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G220" t="str">
         <v/>
@@ -8774,11 +9431,14 @@
       <c r="C221" t="str">
         <v/>
       </c>
+      <c r="D221" t="str">
+        <v>Golbat</v>
+      </c>
       <c r="E221" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F221" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G221" t="str">
         <v/>
@@ -8812,11 +9472,14 @@
       <c r="C222" t="str">
         <v/>
       </c>
+      <c r="D222" t="str">
+        <v>Koffing</v>
+      </c>
       <c r="E222" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F222" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G222" t="str">
         <v/>
@@ -8825,7 +9488,7 @@
         <v>Yes</v>
       </c>
       <c r="I222" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J222" t="str">
         <v>NONONO</v>
@@ -8850,11 +9513,14 @@
       <c r="C223" t="str">
         <v/>
       </c>
+      <c r="D223" t="str">
+        <v>Weezing</v>
+      </c>
       <c r="E223" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F223" t="str">
-        <v>0.2%</v>
+        <v>20%</v>
       </c>
       <c r="G223" t="str">
         <v/>
@@ -8888,11 +9554,14 @@
       <c r="C224" t="str">
         <v/>
       </c>
+      <c r="D224" t="str">
+        <v>Relicanth</v>
+      </c>
       <c r="E224" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F224" t="str">
-        <v>0.38%</v>
+        <v>38%</v>
       </c>
       <c r="G224" t="str">
         <v/>
@@ -8926,11 +9595,14 @@
       <c r="C225" t="str">
         <v/>
       </c>
+      <c r="D225" t="str">
+        <v>Wailord</v>
+      </c>
       <c r="E225" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F225" t="str">
-        <v>0.3325%</v>
+        <v>33%</v>
       </c>
       <c r="G225" t="str">
         <v/>
@@ -8964,11 +9636,14 @@
       <c r="C226" t="str">
         <v/>
       </c>
+      <c r="D226" t="str">
+        <v>Clamperl</v>
+      </c>
       <c r="E226" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F226" t="str">
-        <v>0.2375%</v>
+        <v>24%</v>
       </c>
       <c r="G226" t="str">
         <v/>
@@ -8977,7 +9652,7 @@
         <v>Yes</v>
       </c>
       <c r="I226" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J226" t="str">
         <v>NONONO</v>
@@ -9002,11 +9677,14 @@
       <c r="C227" t="str">
         <v/>
       </c>
+      <c r="D227" t="str">
+        <v>Kingdra</v>
+      </c>
       <c r="E227" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F227" t="str">
-        <v>0.05%</v>
+        <v>5%</v>
       </c>
       <c r="G227" t="str">
         <v/>
@@ -9040,11 +9718,14 @@
       <c r="C228" t="str">
         <v/>
       </c>
+      <c r="D228" t="str">
+        <v>Regirock</v>
+      </c>
       <c r="E228" t="str">
-        <v>undefined-undefined</v>
+        <v>105-105</v>
       </c>
       <c r="F228" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G228" t="str">
         <v/>
@@ -9078,11 +9759,14 @@
       <c r="C229" t="str">
         <v/>
       </c>
+      <c r="D229" t="str">
+        <v>Regice</v>
+      </c>
       <c r="E229" t="str">
-        <v>undefined-undefined</v>
+        <v>105-105</v>
       </c>
       <c r="F229" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G229" t="str">
         <v/>
@@ -9116,11 +9800,14 @@
       <c r="C230" t="str">
         <v/>
       </c>
+      <c r="D230" t="str">
+        <v>Registeel</v>
+      </c>
       <c r="E230" t="str">
-        <v>undefined-undefined</v>
+        <v>105-105</v>
       </c>
       <c r="F230" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G230" t="str">
         <v/>
@@ -9154,11 +9841,14 @@
       <c r="C231" t="str">
         <v/>
       </c>
+      <c r="D231" t="str">
+        <v>Slakoth</v>
+      </c>
       <c r="E231" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F231" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G231" t="str">
         <v/>
@@ -9167,7 +9857,7 @@
         <v>Yes</v>
       </c>
       <c r="I231" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J231" t="str">
         <v>NONONO</v>
@@ -9192,11 +9882,14 @@
       <c r="C232" t="str">
         <v/>
       </c>
+      <c r="D232" t="str">
+        <v>Abra</v>
+      </c>
       <c r="E232" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F232" t="str">
-        <v>0.3%</v>
+        <v>30%</v>
       </c>
       <c r="G232" t="str">
         <v/>
@@ -9205,7 +9898,7 @@
         <v>Yes</v>
       </c>
       <c r="I232" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J232" t="str">
         <v>NONONO</v>
@@ -9230,11 +9923,14 @@
       <c r="C233" t="str">
         <v/>
       </c>
+      <c r="D233" t="str">
+        <v>Castform</v>
+      </c>
       <c r="E233" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F233" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G233" t="str">
         <v/>
@@ -9268,11 +9964,14 @@
       <c r="C234" t="str">
         <v/>
       </c>
+      <c r="D234" t="str">
+        <v>Porygon</v>
+      </c>
       <c r="E234" t="str">
-        <v>undefined-undefined</v>
+        <v>70-75</v>
       </c>
       <c r="F234" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G234" t="str">
         <v/>
@@ -9306,11 +10005,14 @@
       <c r="C235" t="str">
         <v/>
       </c>
+      <c r="D235" t="str">
+        <v>Treecko</v>
+      </c>
       <c r="E235" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F235" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G235" t="str">
         <v/>
@@ -9319,7 +10021,7 @@
         <v>Yes</v>
       </c>
       <c r="I235" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J235" t="str">
         <v>NONONO</v>
@@ -9344,11 +10046,14 @@
       <c r="C236" t="str">
         <v/>
       </c>
+      <c r="D236" t="str">
+        <v>Torchic</v>
+      </c>
       <c r="E236" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F236" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G236" t="str">
         <v/>
@@ -9357,7 +10062,7 @@
         <v>Yes</v>
       </c>
       <c r="I236" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J236" t="str">
         <v>NONONO</v>
@@ -9382,11 +10087,14 @@
       <c r="C237" t="str">
         <v/>
       </c>
+      <c r="D237" t="str">
+        <v>Mudkip</v>
+      </c>
       <c r="E237" t="str">
-        <v>undefined-undefined</v>
+        <v>76-81</v>
       </c>
       <c r="F237" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G237" t="str">
         <v/>
@@ -9395,7 +10103,7 @@
         <v>Yes</v>
       </c>
       <c r="I237" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J237" t="str">
         <v>NONONO</v>
@@ -9420,11 +10128,14 @@
       <c r="C238" t="str">
         <v/>
       </c>
+      <c r="D238" t="str">
+        <v>Wynaut</v>
+      </c>
       <c r="E238" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F238" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G238" t="str">
         <v/>
@@ -9433,7 +10144,7 @@
         <v>Yes</v>
       </c>
       <c r="I238" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J238" t="str">
         <v>NONONO</v>
@@ -9458,11 +10169,14 @@
       <c r="C239" t="str">
         <v/>
       </c>
+      <c r="D239" t="str">
+        <v>Azurill</v>
+      </c>
       <c r="E239" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F239" t="str">
-        <v>0.35%</v>
+        <v>35%</v>
       </c>
       <c r="G239" t="str">
         <v/>
@@ -9471,7 +10185,7 @@
         <v>Yes</v>
       </c>
       <c r="I239" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J239" t="str">
         <v>NONONO</v>
@@ -9496,11 +10210,14 @@
       <c r="C240" t="str">
         <v/>
       </c>
+      <c r="D240" t="str">
+        <v>Pichu</v>
+      </c>
       <c r="E240" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F240" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G240" t="str">
         <v/>
@@ -9509,7 +10226,7 @@
         <v>Yes</v>
       </c>
       <c r="I240" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J240" t="str">
         <v>NONONO</v>
@@ -9534,11 +10251,14 @@
       <c r="C241" t="str">
         <v/>
       </c>
+      <c r="D241" t="str">
+        <v>Igglybuff</v>
+      </c>
       <c r="E241" t="str">
-        <v>undefined-undefined</v>
+        <v>88-93</v>
       </c>
       <c r="F241" t="str">
-        <v>0.15%</v>
+        <v>15%</v>
       </c>
       <c r="G241" t="str">
         <v/>
@@ -9547,7 +10267,7 @@
         <v>Yes</v>
       </c>
       <c r="I241" t="str">
-        <v>Ok</v>
+        <v>NONONO</v>
       </c>
       <c r="J241" t="str">
         <v>NONONO</v>
@@ -9572,11 +10292,14 @@
       <c r="C242" t="str">
         <v/>
       </c>
+      <c r="D242" t="str">
+        <v>Salamence</v>
+      </c>
       <c r="E242" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F242" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G242" t="str">
         <v/>
@@ -9610,11 +10333,14 @@
       <c r="C243" t="str">
         <v/>
       </c>
+      <c r="D243" t="str">
+        <v>Metagross</v>
+      </c>
       <c r="E243" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F243" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G243" t="str">
         <v/>
@@ -9648,11 +10374,14 @@
       <c r="C244" t="str">
         <v/>
       </c>
+      <c r="D244" t="str">
+        <v>Milotic</v>
+      </c>
       <c r="E244" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F244" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G244" t="str">
         <v/>
@@ -9686,11 +10415,14 @@
       <c r="C245" t="str">
         <v/>
       </c>
+      <c r="D245" t="str">
+        <v>Slaking</v>
+      </c>
       <c r="E245" t="str">
-        <v>undefined-undefined</v>
+        <v>95-100</v>
       </c>
       <c r="F245" t="str">
-        <v>0.25%</v>
+        <v>25%</v>
       </c>
       <c r="G245" t="str">
         <v/>
@@ -9724,11 +10456,14 @@
       <c r="C246" t="str">
         <v/>
       </c>
+      <c r="D246" t="str">
+        <v>Kyogre</v>
+      </c>
       <c r="E246" t="str">
-        <v>undefined-undefined</v>
+        <v>115-115</v>
       </c>
       <c r="F246" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G246" t="str">
         <v/>
@@ -9762,11 +10497,14 @@
       <c r="C247" t="str">
         <v/>
       </c>
+      <c r="D247" t="str">
+        <v>Groudon</v>
+      </c>
       <c r="E247" t="str">
-        <v>undefined-undefined</v>
+        <v>115-115</v>
       </c>
       <c r="F247" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G247" t="str">
         <v/>
@@ -9800,11 +10538,14 @@
       <c r="C248" t="str">
         <v/>
       </c>
+      <c r="D248" t="str">
+        <v>Rayquaza</v>
+      </c>
       <c r="E248" t="str">
-        <v>undefined-undefined</v>
+        <v>115-115</v>
       </c>
       <c r="F248" t="str">
-        <v>0.33%</v>
+        <v>33%</v>
       </c>
       <c r="G248" t="str">
         <v/>
@@ -9838,11 +10579,14 @@
       <c r="C249" t="str">
         <v/>
       </c>
+      <c r="D249" t="str">
+        <v>Latias</v>
+      </c>
       <c r="E249" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F249" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G249" t="str">
         <v/>
@@ -9876,11 +10620,14 @@
       <c r="C250" t="str">
         <v/>
       </c>
+      <c r="D250" t="str">
+        <v>Latios</v>
+      </c>
       <c r="E250" t="str">
-        <v>undefined-undefined</v>
+        <v>110-110</v>
       </c>
       <c r="F250" t="str">
-        <v>0.5%</v>
+        <v>50%</v>
       </c>
       <c r="G250" t="str">
         <v/>
@@ -9914,11 +10661,14 @@
       <c r="C251" t="str">
         <v/>
       </c>
+      <c r="D251" t="str">
+        <v>Grovyle</v>
+      </c>
       <c r="E251" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F251" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G251" t="str">
         <v/>
@@ -9952,11 +10702,14 @@
       <c r="C252" t="str">
         <v/>
       </c>
+      <c r="D252" t="str">
+        <v>Combusken</v>
+      </c>
       <c r="E252" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F252" t="str">
-        <v>0.3333%</v>
+        <v>33%</v>
       </c>
       <c r="G252" t="str">
         <v/>
@@ -9990,11 +10743,14 @@
       <c r="C253" t="str">
         <v/>
       </c>
+      <c r="D253" t="str">
+        <v>Marshtomp</v>
+      </c>
       <c r="E253" t="str">
-        <v>undefined-undefined</v>
+        <v>82-87</v>
       </c>
       <c r="F253" t="str">
-        <v>0.3334%</v>
+        <v>33%</v>
       </c>
       <c r="G253" t="str">
         <v/>
@@ -10871,7 +11627,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B45"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10883,1623 +11639,359 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Treecko</v>
+        <v>Sceptile</v>
       </c>
       <c r="B2" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Grovyle</v>
+        <v>Blaziken</v>
       </c>
       <c r="B3" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Sceptile</v>
+        <v>Swampert</v>
       </c>
       <c r="B4" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Torchic</v>
+        <v>Beautifly</v>
       </c>
       <c r="B5" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Combusken</v>
+        <v>Dustox</v>
       </c>
       <c r="B6" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Blaziken</v>
+        <v>Ludicolo</v>
       </c>
       <c r="B7" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Mudkip</v>
+        <v>Shiftry</v>
       </c>
       <c r="B8" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Marshtomp</v>
+        <v>Swellow</v>
       </c>
       <c r="B9" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Swampert</v>
+        <v>Gardevoir</v>
       </c>
       <c r="B10" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Poochyena</v>
+        <v>Breloom</v>
       </c>
       <c r="B11" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mightyena</v>
+        <v>Vigoroth</v>
       </c>
       <c r="B12" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Zigzagoon</v>
+        <v>Alakazam</v>
       </c>
       <c r="B13" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Linoone</v>
+        <v>Ninjask</v>
       </c>
       <c r="B14" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Wurmple</v>
+        <v>Gyarados</v>
       </c>
       <c r="B15" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Silcoon</v>
+        <v>Golem</v>
       </c>
       <c r="B16" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Beautifly</v>
+        <v>Delcatty</v>
       </c>
       <c r="B17" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cascoon</v>
+        <v>Crobat</v>
       </c>
       <c r="B18" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Dustox</v>
+        <v>Aggron</v>
       </c>
       <c r="B19" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Lotad</v>
+        <v>Machamp</v>
       </c>
       <c r="B20" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Lombre</v>
+        <v>Magneton</v>
       </c>
       <c r="B21" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Ludicolo</v>
+        <v>Vileplume</v>
       </c>
       <c r="B22" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Seedot</v>
+        <v>Bellossom</v>
       </c>
       <c r="B23" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Nuzleaf</v>
+        <v>Dodrio</v>
       </c>
       <c r="B24" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Shiftry</v>
+        <v>Swalot</v>
       </c>
       <c r="B25" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Taillow</v>
+        <v>Camerupt</v>
       </c>
       <c r="B26" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Swellow</v>
+        <v>Magcargo</v>
       </c>
       <c r="B27" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Wingull</v>
+        <v>Muk</v>
       </c>
       <c r="B28" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Pelipper</v>
+        <v>Grumpig</v>
       </c>
       <c r="B29" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Ralts</v>
+        <v>Sandslash</v>
       </c>
       <c r="B30" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Kirlia</v>
+        <v>Vibrava</v>
       </c>
       <c r="B31" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Gardevoir</v>
+        <v>Cacturne</v>
       </c>
       <c r="B32" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Surskit</v>
+        <v>Crawdaunt</v>
       </c>
       <c r="B33" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Masquerain</v>
+        <v>Wigglytuff</v>
       </c>
       <c r="B34" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Shroomish</v>
+        <v>Starmie</v>
       </c>
       <c r="B35" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Breloom</v>
+        <v>Ninetales</v>
       </c>
       <c r="B36" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Slakoth</v>
+        <v>Raichu</v>
       </c>
       <c r="B37" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Vigoroth</v>
+        <v>Donphan</v>
       </c>
       <c r="B38" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Slaking</v>
+        <v>Rhydon</v>
       </c>
       <c r="B39" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Abra</v>
+        <v>Glalie</v>
       </c>
       <c r="B40" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Kadabra</v>
+        <v>Walrein</v>
       </c>
       <c r="B41" t="str">
-        <v>No</v>
+        <v>2xEvolution</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Alakazam</v>
+        <v>Huntail</v>
       </c>
       <c r="B42" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Nincada</v>
+        <v>Lanturn</v>
       </c>
       <c r="B43" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Ninjask</v>
+        <v>Shelgon</v>
       </c>
       <c r="B44" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Shedinja</v>
+        <v>Metang</v>
       </c>
       <c r="B45" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Whismur</v>
-      </c>
-      <c r="B46" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Loudred</v>
-      </c>
-      <c r="B47" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Exploud</v>
-      </c>
-      <c r="B48" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Makuhita</v>
-      </c>
-      <c r="B49" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>Hariyama</v>
-      </c>
-      <c r="B50" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>Goldeen</v>
-      </c>
-      <c r="B51" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>Seaking</v>
-      </c>
-      <c r="B52" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>Magikarp</v>
-      </c>
-      <c r="B53" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>Gyarados</v>
-      </c>
-      <c r="B54" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>Azurill</v>
-      </c>
-      <c r="B55" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>Marill</v>
-      </c>
-      <c r="B56" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>Azumarill</v>
-      </c>
-      <c r="B57" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>Geodude</v>
-      </c>
-      <c r="B58" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Graveler</v>
-      </c>
-      <c r="B59" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Golem</v>
-      </c>
-      <c r="B60" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Nosepass</v>
-      </c>
-      <c r="B61" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Skitty</v>
-      </c>
-      <c r="B62" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>Delcatty</v>
-      </c>
-      <c r="B63" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>Zubat</v>
-      </c>
-      <c r="B64" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>Golbat</v>
-      </c>
-      <c r="B65" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>Crobat</v>
-      </c>
-      <c r="B66" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>Tentacool</v>
-      </c>
-      <c r="B67" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Tentacruel</v>
-      </c>
-      <c r="B68" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Sableye</v>
-      </c>
-      <c r="B69" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Mawile</v>
-      </c>
-      <c r="B70" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Aron</v>
-      </c>
-      <c r="B71" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Lairon</v>
-      </c>
-      <c r="B72" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Aggron</v>
-      </c>
-      <c r="B73" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Machop</v>
-      </c>
-      <c r="B74" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>Machoke</v>
-      </c>
-      <c r="B75" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Machamp</v>
-      </c>
-      <c r="B76" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>Meditite</v>
-      </c>
-      <c r="B77" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>Medicham</v>
-      </c>
-      <c r="B78" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>Electrike</v>
-      </c>
-      <c r="B79" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>Manectric</v>
-      </c>
-      <c r="B80" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>Plusle</v>
-      </c>
-      <c r="B81" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>Minun</v>
-      </c>
-      <c r="B82" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>Magnemite</v>
-      </c>
-      <c r="B83" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>Magneton</v>
-      </c>
-      <c r="B84" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>Voltorb</v>
-      </c>
-      <c r="B85" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>Electrode</v>
-      </c>
-      <c r="B86" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>Volbeat</v>
-      </c>
-      <c r="B87" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>Illumise</v>
-      </c>
-      <c r="B88" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>Oddish</v>
-      </c>
-      <c r="B89" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>Gloom</v>
-      </c>
-      <c r="B90" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>Vileplume</v>
-      </c>
-      <c r="B91" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>Bellossom</v>
-      </c>
-      <c r="B92" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>Doduo</v>
-      </c>
-      <c r="B93" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>Dodrio</v>
-      </c>
-      <c r="B94" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>Roselia</v>
-      </c>
-      <c r="B95" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>Gulpin</v>
-      </c>
-      <c r="B96" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>Swalot</v>
-      </c>
-      <c r="B97" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>Carvanha</v>
-      </c>
-      <c r="B98" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>Sharpedo</v>
-      </c>
-      <c r="B99" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>Wailmer</v>
-      </c>
-      <c r="B100" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>Wailord</v>
-      </c>
-      <c r="B101" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>Numel</v>
-      </c>
-      <c r="B102" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>Camerupt</v>
-      </c>
-      <c r="B103" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>Slugma</v>
-      </c>
-      <c r="B104" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>Magcargo</v>
-      </c>
-      <c r="B105" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>Torkoal</v>
-      </c>
-      <c r="B106" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>Grimer</v>
-      </c>
-      <c r="B107" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="str">
-        <v>Muk</v>
-      </c>
-      <c r="B108" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="str">
-        <v>Koffing</v>
-      </c>
-      <c r="B109" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="str">
-        <v>Weezing</v>
-      </c>
-      <c r="B110" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
-        <v>Spoink</v>
-      </c>
-      <c r="B111" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="str">
-        <v>Grumpig</v>
-      </c>
-      <c r="B112" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="str">
-        <v>Sandshrew</v>
-      </c>
-      <c r="B113" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="str">
-        <v>Sandslash</v>
-      </c>
-      <c r="B114" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="str">
-        <v>Spinda</v>
-      </c>
-      <c r="B115" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="str">
-        <v>Skarmory</v>
-      </c>
-      <c r="B116" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="str">
-        <v>Trapinch</v>
-      </c>
-      <c r="B117" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="str">
-        <v>Vibrava</v>
-      </c>
-      <c r="B118" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="str">
-        <v>Flygon</v>
-      </c>
-      <c r="B119" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="str">
-        <v>Cacnea</v>
-      </c>
-      <c r="B120" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="str">
-        <v>Cacturne</v>
-      </c>
-      <c r="B121" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="str">
-        <v>Swablu</v>
-      </c>
-      <c r="B122" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="str">
-        <v>Altaria</v>
-      </c>
-      <c r="B123" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="str">
-        <v>Zangoose</v>
-      </c>
-      <c r="B124" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="str">
-        <v>Seviper</v>
-      </c>
-      <c r="B125" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="str">
-        <v>Lunatone</v>
-      </c>
-      <c r="B126" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="str">
-        <v>Solrock</v>
-      </c>
-      <c r="B127" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="str">
-        <v>Barboach</v>
-      </c>
-      <c r="B128" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="str">
-        <v>Whiscash</v>
-      </c>
-      <c r="B129" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="str">
-        <v>Corphish</v>
-      </c>
-      <c r="B130" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="str">
-        <v>Crawdaunt</v>
-      </c>
-      <c r="B131" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="str">
-        <v>Baltoy</v>
-      </c>
-      <c r="B132" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="str">
-        <v>Claydol</v>
-      </c>
-      <c r="B133" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="str">
-        <v>Lileep</v>
-      </c>
-      <c r="B134" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="str">
-        <v>Cradily</v>
-      </c>
-      <c r="B135" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="str">
-        <v>Anorith</v>
-      </c>
-      <c r="B136" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="str">
-        <v>Armaldo</v>
-      </c>
-      <c r="B137" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="str">
-        <v>Igglybuff</v>
-      </c>
-      <c r="B138" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
-        <v>Jigglypuff</v>
-      </c>
-      <c r="B139" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
-        <v>Wigglytuff</v>
-      </c>
-      <c r="B140" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
-        <v>Feebas</v>
-      </c>
-      <c r="B141" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
-        <v>Milotic</v>
-      </c>
-      <c r="B142" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
-        <v>Castform</v>
-      </c>
-      <c r="B143" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
-        <v>Staryu</v>
-      </c>
-      <c r="B144" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
-        <v>Starmie</v>
-      </c>
-      <c r="B145" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
-        <v>Kecleon</v>
-      </c>
-      <c r="B146" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
-        <v>Shuppet</v>
-      </c>
-      <c r="B147" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
-        <v>Banette</v>
-      </c>
-      <c r="B148" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
-        <v>Duskull</v>
-      </c>
-      <c r="B149" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
-        <v>Dusclops</v>
-      </c>
-      <c r="B150" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
-        <v>Tropius</v>
-      </c>
-      <c r="B151" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
-        <v>Chimecho</v>
-      </c>
-      <c r="B152" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
-        <v>Absol</v>
-      </c>
-      <c r="B153" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
-        <v>Vulpix</v>
-      </c>
-      <c r="B154" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
-        <v>Ninetales</v>
-      </c>
-      <c r="B155" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
-        <v>Pichu</v>
-      </c>
-      <c r="B156" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
-        <v>Pikachu</v>
-      </c>
-      <c r="B157" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
-        <v>Raichu</v>
-      </c>
-      <c r="B158" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
-        <v>Psyduck</v>
-      </c>
-      <c r="B159" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
-        <v>Golduck</v>
-      </c>
-      <c r="B160" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
-        <v>Wynaut</v>
-      </c>
-      <c r="B161" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
-        <v>Wobbuffet</v>
-      </c>
-      <c r="B162" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
-        <v>Natu</v>
-      </c>
-      <c r="B163" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
-        <v>Xatu</v>
-      </c>
-      <c r="B164" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
-        <v>Girafarig</v>
-      </c>
-      <c r="B165" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="str">
-        <v>Phanpy</v>
-      </c>
-      <c r="B166" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="str">
-        <v>Donphan</v>
-      </c>
-      <c r="B167" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="str">
-        <v>Pinsir</v>
-      </c>
-      <c r="B168" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="str">
-        <v>Heracross</v>
-      </c>
-      <c r="B169" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="str">
-        <v>Rhyhorn</v>
-      </c>
-      <c r="B170" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="str">
-        <v>Rhydon</v>
-      </c>
-      <c r="B171" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="str">
-        <v>Snorunt</v>
-      </c>
-      <c r="B172" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="str">
-        <v>Glalie</v>
-      </c>
-      <c r="B173" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="str">
-        <v>Spheal</v>
-      </c>
-      <c r="B174" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="str">
-        <v>Sealeo</v>
-      </c>
-      <c r="B175" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="str">
-        <v>Walrein</v>
-      </c>
-      <c r="B176" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="str">
-        <v>Clamperl</v>
-      </c>
-      <c r="B177" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="str">
-        <v>Huntail</v>
-      </c>
-      <c r="B178" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="str">
-        <v>Gorebyss</v>
-      </c>
-      <c r="B179" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="str">
-        <v>Relicanth</v>
-      </c>
-      <c r="B180" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="str">
-        <v>Corsola</v>
-      </c>
-      <c r="B181" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="str">
-        <v>Chinchou</v>
-      </c>
-      <c r="B182" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="str">
-        <v>Lanturn</v>
-      </c>
-      <c r="B183" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="str">
-        <v>Luvdisc</v>
-      </c>
-      <c r="B184" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="str">
-        <v>Horsea</v>
-      </c>
-      <c r="B185" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="str">
-        <v>Seadra</v>
-      </c>
-      <c r="B186" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="str">
-        <v>Kingdra</v>
-      </c>
-      <c r="B187" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="str">
-        <v>Bagon</v>
-      </c>
-      <c r="B188" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="str">
-        <v>Shelgon</v>
-      </c>
-      <c r="B189" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="str">
-        <v>Salamence</v>
-      </c>
-      <c r="B190" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="str">
-        <v>Beldum</v>
-      </c>
-      <c r="B191" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="str">
-        <v>Metang</v>
-      </c>
-      <c r="B192" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="str">
-        <v>Metagross</v>
-      </c>
-      <c r="B193" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="str">
-        <v>Regirock</v>
-      </c>
-      <c r="B194" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="str">
-        <v>Regice</v>
-      </c>
-      <c r="B195" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>Registeel</v>
-      </c>
-      <c r="B196" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>Latias</v>
-      </c>
-      <c r="B197" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Latios</v>
-      </c>
-      <c r="B198" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Kyogre</v>
-      </c>
-      <c r="B199" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Groudon</v>
-      </c>
-      <c r="B200" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Rayquaza</v>
-      </c>
-      <c r="B201" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>Jirachi</v>
-      </c>
-      <c r="B202" t="str">
-        <v>No</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>Deoxys</v>
-      </c>
-      <c r="B203" t="str">
-        <v>No</v>
+        <v>Evolve</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B203"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B45"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -474,8 +474,8 @@
       <c r="H2" s="1">
         <v>0.45</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
+      <c r="I2" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J2" t="str">
         <v>Legacy</v>
@@ -521,8 +521,8 @@
       <c r="H3" s="1">
         <v>0.45</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
+      <c r="I3" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J3" t="str">
         <v>Legacy</v>
@@ -568,8 +568,8 @@
       <c r="H4" s="1">
         <v>0.1</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
+      <c r="I4" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J4" t="str">
         <v>Legacy</v>
@@ -615,8 +615,8 @@
       <c r="H5" s="1">
         <v>0.3</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
+      <c r="I5" s="1">
+        <v>0.2</v>
       </c>
       <c r="J5" t="str">
         <v>Yes</v>
@@ -756,8 +756,8 @@
       <c r="H8" s="1">
         <v>0.1</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
+      <c r="I8" s="1">
+        <v>0.2</v>
       </c>
       <c r="J8" t="str">
         <v>Legacy</v>
@@ -803,8 +803,8 @@
       <c r="H9" s="1">
         <v>0.1</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
+      <c r="I9" s="1">
+        <v>0.2</v>
       </c>
       <c r="J9" t="str">
         <v>Legacy</v>
@@ -845,7 +845,7 @@
         <v>4-7</v>
       </c>
       <c r="G10" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H10" s="1">
         <v>0.25</v>
@@ -892,7 +892,7 @@
         <v>4-7</v>
       </c>
       <c r="G11" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H11" s="1">
         <v>0.25</v>
@@ -939,7 +939,7 @@
         <v>4-7</v>
       </c>
       <c r="G12" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H12" s="1">
         <v>0.2</v>
@@ -986,7 +986,7 @@
         <v>4-7</v>
       </c>
       <c r="G13" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H13" s="1">
         <v>0.15</v>
@@ -1033,7 +1033,7 @@
         <v>4-7</v>
       </c>
       <c r="G14" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H14" s="1">
         <v>0.1</v>
@@ -1080,13 +1080,13 @@
         <v>4-7</v>
       </c>
       <c r="G15" t="str">
-        <v>2-4</v>
+        <v>1-3</v>
       </c>
       <c r="H15" s="1">
         <v>0.05</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
+      <c r="I15" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J15" t="str">
         <v>Legacy</v>
@@ -1320,8 +1320,8 @@
       <c r="H20" s="1">
         <v>0.1</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
+      <c r="I20" s="1">
+        <v>0.2</v>
       </c>
       <c r="J20" t="str">
         <v>Yes</v>
@@ -1367,8 +1367,8 @@
       <c r="H21" s="1">
         <v>0.3</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
+      <c r="I21" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J21" t="str">
         <v>Legacy</v>
@@ -1602,8 +1602,8 @@
       <c r="H26" s="1">
         <v>0.05</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
+      <c r="I26" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J26" t="str">
         <v>Legacy</v>
@@ -1644,7 +1644,7 @@
         <v>9-12</v>
       </c>
       <c r="G27" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H27" s="1">
         <v>0.2375</v>
@@ -1691,7 +1691,7 @@
         <v>9-12</v>
       </c>
       <c r="G28" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H28" s="1">
         <v>0.2375</v>
@@ -1738,7 +1738,7 @@
         <v>9-12</v>
       </c>
       <c r="G29" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H29" s="1">
         <v>0.19</v>
@@ -1785,7 +1785,7 @@
         <v>9-12</v>
       </c>
       <c r="G30" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H30" s="1">
         <v>0.19</v>
@@ -1832,7 +1832,7 @@
         <v>9-12</v>
       </c>
       <c r="G31" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H31" s="1">
         <v>0.095</v>
@@ -1879,13 +1879,13 @@
         <v>9-12</v>
       </c>
       <c r="G32" t="str">
-        <v>7-9</v>
+        <v>6-8</v>
       </c>
       <c r="H32" s="1">
         <v>0.05</v>
       </c>
-      <c r="I32" t="str">
-        <v/>
+      <c r="I32" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J32" t="str">
         <v>Yes</v>
@@ -1926,7 +1926,7 @@
         <v>12-15</v>
       </c>
       <c r="G33" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H33" s="1">
         <v>0.1805</v>
@@ -1973,7 +1973,7 @@
         <v>12-15</v>
       </c>
       <c r="G34" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H34" s="1">
         <v>0.1425</v>
@@ -2020,7 +2020,7 @@
         <v>12-15</v>
       </c>
       <c r="G35" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H35" s="1">
         <v>0.1425</v>
@@ -2067,7 +2067,7 @@
         <v>12-15</v>
       </c>
       <c r="G36" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H36" s="1">
         <v>0.1425</v>
@@ -2114,7 +2114,7 @@
         <v>12-15</v>
       </c>
       <c r="G37" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H37" s="1">
         <v>0.1425</v>
@@ -2161,7 +2161,7 @@
         <v>12-15</v>
       </c>
       <c r="G38" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H38" s="1">
         <v>0.076</v>
@@ -2208,7 +2208,7 @@
         <v>12-15</v>
       </c>
       <c r="G39" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H39" s="1">
         <v>0.076</v>
@@ -2255,7 +2255,7 @@
         <v>12-15</v>
       </c>
       <c r="G40" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H40" s="1">
         <v>0.0475</v>
@@ -2302,7 +2302,7 @@
         <v>12-15</v>
       </c>
       <c r="G41" t="str">
-        <v>9-11</v>
+        <v>8-10</v>
       </c>
       <c r="H41" s="1">
         <v>0.05</v>
@@ -2349,13 +2349,13 @@
         <v>14-17</v>
       </c>
       <c r="G42" t="str">
-        <v>11-13</v>
+        <v>10-12</v>
       </c>
       <c r="H42" s="1">
         <v>0.45</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
+      <c r="I42" s="1">
+        <v>0.2</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -2396,7 +2396,7 @@
         <v>14-17</v>
       </c>
       <c r="G43" t="str">
-        <v>11-13</v>
+        <v>10-12</v>
       </c>
       <c r="H43" s="1">
         <v>0.18</v>
@@ -2443,7 +2443,7 @@
         <v>14-17</v>
       </c>
       <c r="G44" t="str">
-        <v>11-13</v>
+        <v>10-12</v>
       </c>
       <c r="H44" s="1">
         <v>0.18</v>
@@ -2490,13 +2490,13 @@
         <v>14-17</v>
       </c>
       <c r="G45" t="str">
-        <v>11-13</v>
+        <v>10-12</v>
       </c>
       <c r="H45" s="1">
         <v>0.09</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
+      <c r="I45" s="1">
+        <v>0.2</v>
       </c>
       <c r="J45" t="str">
         <v/>
@@ -2537,13 +2537,13 @@
         <v>14-17</v>
       </c>
       <c r="G46" t="str">
-        <v>11-13</v>
+        <v>10-12</v>
       </c>
       <c r="H46" s="1">
         <v>0.1</v>
       </c>
-      <c r="I46" t="str">
-        <v/>
+      <c r="I46" s="1">
+        <v>0.2</v>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -2584,13 +2584,13 @@
         <v>17-20</v>
       </c>
       <c r="G47" t="str">
-        <v>13-16</v>
+        <v>12-15</v>
       </c>
       <c r="H47" s="1">
         <v>0.5</v>
       </c>
-      <c r="I47" t="str">
-        <v/>
+      <c r="I47" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J47" t="str">
         <v>Yes</v>
@@ -2631,7 +2631,7 @@
         <v>17-20</v>
       </c>
       <c r="G48" t="str">
-        <v>13-16</v>
+        <v>12-15</v>
       </c>
       <c r="H48" s="1">
         <v>0.4</v>
@@ -2678,13 +2678,13 @@
         <v>17-20</v>
       </c>
       <c r="G49" t="str">
-        <v>13-16</v>
+        <v>12-15</v>
       </c>
       <c r="H49" s="1">
         <v>0.1</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
+      <c r="I49" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J49" t="str">
         <v>Yes</v>
@@ -2725,13 +2725,13 @@
         <v>20-23</v>
       </c>
       <c r="G50" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H50" s="1">
         <v>0.225</v>
       </c>
-      <c r="I50" t="str">
-        <v/>
+      <c r="I50" s="1">
+        <v>0.125</v>
       </c>
       <c r="J50" t="str">
         <v>Legacy</v>
@@ -2772,7 +2772,7 @@
         <v>20-23</v>
       </c>
       <c r="G51" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H51" s="1">
         <v>0.135</v>
@@ -2819,7 +2819,7 @@
         <v>20-23</v>
       </c>
       <c r="G52" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H52" s="1">
         <v>0.135</v>
@@ -2866,7 +2866,7 @@
         <v>20-23</v>
       </c>
       <c r="G53" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H53" s="1">
         <v>0.135</v>
@@ -2913,7 +2913,7 @@
         <v>20-23</v>
       </c>
       <c r="G54" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H54" s="1">
         <v>0.135</v>
@@ -2960,7 +2960,7 @@
         <v>20-23</v>
       </c>
       <c r="G55" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H55" s="1">
         <v>0.09</v>
@@ -3007,7 +3007,7 @@
         <v>20-23</v>
       </c>
       <c r="G56" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H56" s="1">
         <v>0.045</v>
@@ -3054,7 +3054,7 @@
         <v>20-23</v>
       </c>
       <c r="G57" t="str">
-        <v>15-18</v>
+        <v>14-17</v>
       </c>
       <c r="H57" s="1">
         <v>0.1</v>
@@ -3717,8 +3717,8 @@
       <c r="H71" s="1">
         <v>0.05</v>
       </c>
-      <c r="I71" t="str">
-        <v/>
+      <c r="I71" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J71" t="str">
         <v>Yes</v>
@@ -3764,8 +3764,8 @@
       <c r="H72" s="1">
         <v>0.3</v>
       </c>
-      <c r="I72" t="str">
-        <v/>
+      <c r="I72" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J72" t="str">
         <v>Legacy</v>
@@ -3999,8 +3999,8 @@
       <c r="H77" s="1">
         <v>0.05</v>
       </c>
-      <c r="I77" t="str">
-        <v/>
+      <c r="I77" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J77" t="str">
         <v>Legacy</v>
@@ -4041,13 +4041,13 @@
         <v>28-32</v>
       </c>
       <c r="G78" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H78" s="1">
         <v>0.4275</v>
       </c>
-      <c r="I78" t="str">
-        <v/>
+      <c r="I78" s="1">
+        <v>0.25</v>
       </c>
       <c r="J78" t="str">
         <v>Legacy</v>
@@ -4088,13 +4088,13 @@
         <v>28-32</v>
       </c>
       <c r="G79" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H79" s="1">
         <v>0.4275</v>
       </c>
-      <c r="I79" t="str">
-        <v/>
+      <c r="I79" s="1">
+        <v>0.25</v>
       </c>
       <c r="J79" t="str">
         <v>Legacy</v>
@@ -4135,13 +4135,13 @@
         <v>28-32</v>
       </c>
       <c r="G80" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H80" s="1">
         <v>0.095</v>
       </c>
-      <c r="I80" t="str">
-        <v/>
+      <c r="I80" s="1">
+        <v>0.25</v>
       </c>
       <c r="J80" t="str">
         <v>Legacy</v>
@@ -4182,13 +4182,13 @@
         <v>28-32</v>
       </c>
       <c r="G81" t="str">
-        <v>22-25</v>
+        <v>21-24</v>
       </c>
       <c r="H81" s="1">
         <v>0.05</v>
       </c>
-      <c r="I81" t="str">
-        <v/>
+      <c r="I81" s="1">
+        <v>0.25</v>
       </c>
       <c r="J81" t="str">
         <v>Yes</v>
@@ -4229,13 +4229,13 @@
         <v>30-33</v>
       </c>
       <c r="G82" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H82" s="1">
         <v>0.7</v>
       </c>
-      <c r="I82" t="str">
-        <v/>
+      <c r="I82" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J82" t="str">
         <v>Legacy</v>
@@ -4276,13 +4276,13 @@
         <v>30-33</v>
       </c>
       <c r="G83" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H83" s="1">
         <v>0.15</v>
       </c>
-      <c r="I83" t="str">
-        <v/>
+      <c r="I83" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J83" t="str">
         <v>Legacy</v>
@@ -4323,13 +4323,13 @@
         <v>30-33</v>
       </c>
       <c r="G84" t="str">
-        <v>24-27</v>
+        <v>23-26</v>
       </c>
       <c r="H84" s="1">
         <v>0.15</v>
       </c>
-      <c r="I84" t="str">
-        <v/>
+      <c r="I84" s="1">
+        <v>0.3333333333333333</v>
       </c>
       <c r="J84" t="str">
         <v>Yes</v>
@@ -4370,13 +4370,13 @@
         <v>31-35</v>
       </c>
       <c r="G85" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H85" s="1">
         <v>0.25</v>
       </c>
-      <c r="I85" t="str">
-        <v/>
+      <c r="I85" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J85" t="str">
         <v>Legacy</v>
@@ -4417,7 +4417,7 @@
         <v>31-35</v>
       </c>
       <c r="G86" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H86" s="1">
         <v>0.2</v>
@@ -4464,7 +4464,7 @@
         <v>31-35</v>
       </c>
       <c r="G87" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H87" s="1">
         <v>0.15</v>
@@ -4511,7 +4511,7 @@
         <v>31-35</v>
       </c>
       <c r="G88" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H88" s="1">
         <v>0.15</v>
@@ -4558,7 +4558,7 @@
         <v>31-35</v>
       </c>
       <c r="G89" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H89" s="1">
         <v>0.1</v>
@@ -4605,7 +4605,7 @@
         <v>31-35</v>
       </c>
       <c r="G90" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H90" s="1">
         <v>0.1</v>
@@ -4652,7 +4652,7 @@
         <v>31-35</v>
       </c>
       <c r="G91" t="str">
-        <v>26-29</v>
+        <v>25-28</v>
       </c>
       <c r="H91" s="1">
         <v>0.05</v>
@@ -4699,13 +4699,13 @@
         <v>33-37</v>
       </c>
       <c r="G92" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H92" s="1">
         <v>0.3325</v>
       </c>
-      <c r="I92" t="str">
-        <v/>
+      <c r="I92" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J92" t="str">
         <v>Legacy</v>
@@ -4746,7 +4746,7 @@
         <v>33-37</v>
       </c>
       <c r="G93" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H93" s="1">
         <v>0.2375</v>
@@ -4793,7 +4793,7 @@
         <v>33-37</v>
       </c>
       <c r="G94" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H94" s="1">
         <v>0.1425</v>
@@ -4840,7 +4840,7 @@
         <v>33-37</v>
       </c>
       <c r="G95" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H95" s="1">
         <v>0.1425</v>
@@ -4887,7 +4887,7 @@
         <v>33-37</v>
       </c>
       <c r="G96" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H96" s="1">
         <v>0.095</v>
@@ -4934,13 +4934,13 @@
         <v>33-37</v>
       </c>
       <c r="G97" t="str">
-        <v>28-31</v>
+        <v>27-30</v>
       </c>
       <c r="H97" s="1">
         <v>0.05</v>
       </c>
-      <c r="I97" t="str">
-        <v/>
+      <c r="I97" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J97" t="str">
         <v>Yes</v>
@@ -4986,8 +4986,8 @@
       <c r="H98" s="1">
         <v>0.3</v>
       </c>
-      <c r="I98" t="str">
-        <v/>
+      <c r="I98" s="1">
+        <v>0.2</v>
       </c>
       <c r="J98" t="str">
         <v>Yes</v>
@@ -5127,8 +5127,8 @@
       <c r="H101" s="1">
         <v>0.1</v>
       </c>
-      <c r="I101" t="str">
-        <v/>
+      <c r="I101" s="1">
+        <v>0.2</v>
       </c>
       <c r="J101" t="str">
         <v>Legacy</v>
@@ -5174,8 +5174,8 @@
       <c r="H102" s="1">
         <v>0.1</v>
       </c>
-      <c r="I102" t="str">
-        <v/>
+      <c r="I102" s="1">
+        <v>0.2</v>
       </c>
       <c r="J102" t="str">
         <v>Yes</v>
@@ -5216,7 +5216,7 @@
         <v>38-41</v>
       </c>
       <c r="G103" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H103" s="1">
         <v>0.25</v>
@@ -5263,7 +5263,7 @@
         <v>38-41</v>
       </c>
       <c r="G104" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H104" s="1">
         <v>0.2</v>
@@ -5310,7 +5310,7 @@
         <v>38-41</v>
       </c>
       <c r="G105" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H105" s="1">
         <v>0.2</v>
@@ -5357,7 +5357,7 @@
         <v>38-41</v>
       </c>
       <c r="G106" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H106" s="1">
         <v>0.15</v>
@@ -5404,7 +5404,7 @@
         <v>38-41</v>
       </c>
       <c r="G107" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H107" s="1">
         <v>0.1</v>
@@ -5451,7 +5451,7 @@
         <v>38-41</v>
       </c>
       <c r="G108" t="str">
-        <v>31-35</v>
+        <v>31-34</v>
       </c>
       <c r="H108" s="1">
         <v>0.1</v>
@@ -5498,7 +5498,7 @@
         <v>40-43</v>
       </c>
       <c r="G109" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H109" s="1">
         <v>0.09</v>
@@ -5545,7 +5545,7 @@
         <v>40-43</v>
       </c>
       <c r="G110" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H110" s="1">
         <v>0.18</v>
@@ -5592,7 +5592,7 @@
         <v>40-43</v>
       </c>
       <c r="G111" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H111" s="1">
         <v>0.18</v>
@@ -5639,7 +5639,7 @@
         <v>40-43</v>
       </c>
       <c r="G112" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H112" s="1">
         <v>0.09</v>
@@ -5686,7 +5686,7 @@
         <v>40-43</v>
       </c>
       <c r="G113" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H113" s="1">
         <v>0.18</v>
@@ -5733,7 +5733,7 @@
         <v>40-43</v>
       </c>
       <c r="G114" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H114" s="1">
         <v>0.18</v>
@@ -5780,7 +5780,7 @@
         <v>40-43</v>
       </c>
       <c r="G115" t="str">
-        <v>33-37</v>
+        <v>33-36</v>
       </c>
       <c r="H115" s="1">
         <v>0.1</v>
@@ -5827,13 +5827,13 @@
         <v>41-45</v>
       </c>
       <c r="G116" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H116" s="1">
         <v>0.3</v>
       </c>
-      <c r="I116" t="str">
-        <v/>
+      <c r="I116" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J116" t="str">
         <v>Yes</v>
@@ -5874,13 +5874,13 @@
         <v>41-45</v>
       </c>
       <c r="G117" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H117" s="1">
         <v>0.3</v>
       </c>
-      <c r="I117" t="str">
-        <v/>
+      <c r="I117" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -5921,7 +5921,7 @@
         <v>41-45</v>
       </c>
       <c r="G118" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H118" s="1">
         <v>0.15</v>
@@ -5968,7 +5968,7 @@
         <v>41-45</v>
       </c>
       <c r="G119" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H119" s="1">
         <v>0.1</v>
@@ -6015,7 +6015,7 @@
         <v>41-45</v>
       </c>
       <c r="G120" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H120" s="1">
         <v>0.1</v>
@@ -6062,13 +6062,13 @@
         <v>41-45</v>
       </c>
       <c r="G121" t="str">
-        <v>35-39</v>
+        <v>35-38</v>
       </c>
       <c r="H121" s="1">
         <v>0.05</v>
       </c>
-      <c r="I121" t="str">
-        <v/>
+      <c r="I121" s="1">
+        <v>0.16666666666666666</v>
       </c>
       <c r="J121" t="str">
         <v>Yes</v>
@@ -6109,13 +6109,13 @@
         <v>43-46</v>
       </c>
       <c r="G122" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H122" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
+      <c r="I122" s="1">
+        <v>0.125</v>
       </c>
       <c r="J122" t="str">
         <v>Yes</v>
@@ -6156,7 +6156,7 @@
         <v>43-46</v>
       </c>
       <c r="G123" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H123" s="1">
         <v>0.19</v>
@@ -6203,7 +6203,7 @@
         <v>43-46</v>
       </c>
       <c r="G124" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H124" s="1">
         <v>0.1425</v>
@@ -6250,7 +6250,7 @@
         <v>43-46</v>
       </c>
       <c r="G125" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H125" s="1">
         <v>0.1425</v>
@@ -6297,7 +6297,7 @@
         <v>43-46</v>
       </c>
       <c r="G126" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H126" s="1">
         <v>0.095</v>
@@ -6344,7 +6344,7 @@
         <v>43-46</v>
       </c>
       <c r="G127" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H127" s="1">
         <v>0.095</v>
@@ -6391,7 +6391,7 @@
         <v>43-46</v>
       </c>
       <c r="G128" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H128" s="1">
         <v>0.0475</v>
@@ -6438,7 +6438,7 @@
         <v>43-46</v>
       </c>
       <c r="G129" t="str">
-        <v>37-41</v>
+        <v>37-40</v>
       </c>
       <c r="H129" s="1">
         <v>0.05</v>
@@ -6485,7 +6485,7 @@
         <v>44-48</v>
       </c>
       <c r="G130" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H130" s="1">
         <v>0.2</v>
@@ -6532,7 +6532,7 @@
         <v>44-48</v>
       </c>
       <c r="G131" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H131" s="1">
         <v>0.25</v>
@@ -6579,7 +6579,7 @@
         <v>44-48</v>
       </c>
       <c r="G132" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6626,7 +6626,7 @@
         <v>44-48</v>
       </c>
       <c r="G133" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H133" s="1">
         <v>0.15</v>
@@ -6673,7 +6673,7 @@
         <v>44-48</v>
       </c>
       <c r="G134" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H134" s="1">
         <v>0.1</v>
@@ -6720,7 +6720,7 @@
         <v>44-48</v>
       </c>
       <c r="G135" t="str">
-        <v>39-43</v>
+        <v>38-41</v>
       </c>
       <c r="H135" s="1">
         <v>0.1</v>
@@ -6767,7 +6767,7 @@
         <v>46-50</v>
       </c>
       <c r="G136" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H136" s="1">
         <v>0.15</v>
@@ -6814,7 +6814,7 @@
         <v>46-50</v>
       </c>
       <c r="G137" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H137" s="1">
         <v>0.15</v>
@@ -6861,7 +6861,7 @@
         <v>51-55</v>
       </c>
       <c r="G138" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H138" s="1">
         <v>0.08</v>
@@ -6908,7 +6908,7 @@
         <v>46-50</v>
       </c>
       <c r="G139" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H139" s="1">
         <v>0.07</v>
@@ -6955,7 +6955,7 @@
         <v>46-50</v>
       </c>
       <c r="G140" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H140" s="1">
         <v>0.11</v>
@@ -7002,7 +7002,7 @@
         <v>46-50</v>
       </c>
       <c r="G141" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7049,7 +7049,7 @@
         <v>46-50</v>
       </c>
       <c r="G142" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H142" s="1">
         <v>0.09</v>
@@ -7096,7 +7096,7 @@
         <v>44-48</v>
       </c>
       <c r="G143" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H143" s="1">
         <v>0.15</v>
@@ -7143,7 +7143,7 @@
         <v>51-55</v>
       </c>
       <c r="G144" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H144" s="1">
         <v>0.1</v>
@@ -7190,7 +7190,7 @@
         <v>46-50</v>
       </c>
       <c r="G145" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H145" s="1">
         <v>0.12</v>
@@ -7237,7 +7237,7 @@
         <v>46-50</v>
       </c>
       <c r="G146" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H146" s="1">
         <v>0.08</v>
@@ -7284,7 +7284,7 @@
         <v>50-54</v>
       </c>
       <c r="G147" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H147" s="1">
         <v>0.08</v>
@@ -7331,7 +7331,7 @@
         <v>46-50</v>
       </c>
       <c r="G148" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H148" s="1">
         <v>0.12</v>
@@ -7378,7 +7378,7 @@
         <v>50-54</v>
       </c>
       <c r="G149" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H149" s="1">
         <v>0.12</v>
@@ -7425,7 +7425,7 @@
         <v>46-50</v>
       </c>
       <c r="G150" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H150" s="1">
         <v>0.08</v>
@@ -7472,7 +7472,7 @@
         <v>50-54</v>
       </c>
       <c r="G151" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H151" s="1">
         <v>0.1</v>
@@ -7519,7 +7519,7 @@
         <v>44-48</v>
       </c>
       <c r="G152" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H152" s="1">
         <v>0.1</v>
@@ -7566,7 +7566,7 @@
         <v>44-48</v>
       </c>
       <c r="G153" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H153" s="1">
         <v>0.11</v>
@@ -7613,7 +7613,7 @@
         <v>48-52</v>
       </c>
       <c r="G154" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H154" s="1">
         <v>0.09</v>
@@ -7660,7 +7660,7 @@
         <v>51-55</v>
       </c>
       <c r="G155" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H155" s="1">
         <v>0.16</v>
@@ -7707,7 +7707,7 @@
         <v>48-52</v>
       </c>
       <c r="G156" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H156" s="1">
         <v>0.16</v>
@@ -7754,7 +7754,7 @@
         <v>51-55</v>
       </c>
       <c r="G157" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H157" s="1">
         <v>0.12</v>
@@ -7801,7 +7801,7 @@
         <v>44-48</v>
       </c>
       <c r="G158" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H158" s="1">
         <v>0.12</v>
@@ -7848,7 +7848,7 @@
         <v>48-52</v>
       </c>
       <c r="G159" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H159" s="1">
         <v>0.13</v>
@@ -7895,7 +7895,7 @@
         <v>44-48</v>
       </c>
       <c r="G160" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H160" s="1">
         <v>0.09</v>
@@ -7942,7 +7942,7 @@
         <v>48-52</v>
       </c>
       <c r="G161" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H161" s="1">
         <v>0.13</v>
@@ -7989,7 +7989,7 @@
         <v>44-48</v>
       </c>
       <c r="G162" t="str">
-        <v>41-46</v>
+        <v>40-44</v>
       </c>
       <c r="H162" s="1">
         <v>0.09</v>
@@ -8036,13 +8036,13 @@
         <v>48-51</v>
       </c>
       <c r="G163" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H163" s="1">
         <v>0.3</v>
       </c>
-      <c r="I163" t="str">
-        <v/>
+      <c r="I163" s="1">
+        <v>0.2</v>
       </c>
       <c r="J163" t="str">
         <v>Yes</v>
@@ -8083,7 +8083,7 @@
         <v>48-51</v>
       </c>
       <c r="G164" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H164" s="1">
         <v>0.25</v>
@@ -8130,7 +8130,7 @@
         <v>48-51</v>
       </c>
       <c r="G165" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H165" s="1">
         <v>0.2</v>
@@ -8177,7 +8177,7 @@
         <v>48-51</v>
       </c>
       <c r="G166" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H166" s="1">
         <v>0.15</v>
@@ -8224,13 +8224,13 @@
         <v>48-51</v>
       </c>
       <c r="G167" t="str">
-        <v>43-48</v>
+        <v>42-46</v>
       </c>
       <c r="H167" s="1">
         <v>0.1</v>
       </c>
-      <c r="I167" t="str">
-        <v/>
+      <c r="I167" s="1">
+        <v>0.2</v>
       </c>
       <c r="J167" t="str">
         <v>Yes</v>
@@ -8271,13 +8271,13 @@
         <v>49-53</v>
       </c>
       <c r="G168" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H168" s="1">
         <v>0.3</v>
       </c>
-      <c r="I168" t="str">
-        <v/>
+      <c r="I168" s="1">
+        <v>0.2</v>
       </c>
       <c r="J168" t="str">
         <v>Yes</v>
@@ -8318,7 +8318,7 @@
         <v>49-53</v>
       </c>
       <c r="G169" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H169" s="1">
         <v>0.25</v>
@@ -8365,7 +8365,7 @@
         <v>49-53</v>
       </c>
       <c r="G170" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H170" s="1">
         <v>0.2</v>
@@ -8412,7 +8412,7 @@
         <v>49-53</v>
       </c>
       <c r="G171" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H171" s="1">
         <v>0.15</v>
@@ -8459,13 +8459,13 @@
         <v>49-53</v>
       </c>
       <c r="G172" t="str">
-        <v>44-49</v>
+        <v>44-48</v>
       </c>
       <c r="H172" s="1">
         <v>0.1</v>
       </c>
-      <c r="I172" t="str">
-        <v/>
+      <c r="I172" s="1">
+        <v>0.2</v>
       </c>
       <c r="J172" t="str">
         <v>Yes</v>
@@ -8506,7 +8506,7 @@
         <v>54-58</v>
       </c>
       <c r="G173" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H173" s="1">
         <v>0.198</v>
@@ -8553,7 +8553,7 @@
         <v>54-58</v>
       </c>
       <c r="G174" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H174" s="1">
         <v>0.198</v>
@@ -8600,7 +8600,7 @@
         <v>54-58</v>
       </c>
       <c r="G175" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H175" s="1">
         <v>0.135</v>
@@ -8647,7 +8647,7 @@
         <v>54-58</v>
       </c>
       <c r="G176" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H176" s="1">
         <v>0.135</v>
@@ -8694,7 +8694,7 @@
         <v>54-58</v>
       </c>
       <c r="G177" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H177" s="1">
         <v>0.09</v>
@@ -8741,7 +8741,7 @@
         <v>54-58</v>
       </c>
       <c r="G178" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H178" s="1">
         <v>0.072</v>
@@ -8788,7 +8788,7 @@
         <v>54-58</v>
       </c>
       <c r="G179" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H179" s="1">
         <v>0.072</v>
@@ -8835,7 +8835,7 @@
         <v>54-58</v>
       </c>
       <c r="G180" t="str">
-        <v>46-51</v>
+        <v>46-50</v>
       </c>
       <c r="H180" s="1">
         <v>0.1</v>
@@ -8882,13 +8882,13 @@
         <v>56-60</v>
       </c>
       <c r="G181" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H181" s="1">
         <v>0.585</v>
       </c>
-      <c r="I181" t="str">
-        <v/>
+      <c r="I181" s="1">
+        <v>0.25</v>
       </c>
       <c r="J181" t="str">
         <v/>
@@ -8929,7 +8929,7 @@
         <v>56-60</v>
       </c>
       <c r="G182" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H182" s="1">
         <v>0.225</v>
@@ -8976,13 +8976,13 @@
         <v>56-60</v>
       </c>
       <c r="G183" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H183" s="1">
         <v>0.09</v>
       </c>
-      <c r="I183" t="str">
-        <v/>
+      <c r="I183" s="1">
+        <v>0.25</v>
       </c>
       <c r="J183" t="str">
         <v/>
@@ -9023,13 +9023,13 @@
         <v>56-60</v>
       </c>
       <c r="G184" t="str">
-        <v>48-53</v>
+        <v>48-52</v>
       </c>
       <c r="H184" s="1">
         <v>0.1</v>
       </c>
-      <c r="I184" t="str">
-        <v/>
+      <c r="I184" s="1">
+        <v>0.25</v>
       </c>
       <c r="J184" t="str">
         <v/>
@@ -9070,13 +9070,13 @@
         <v>59-63</v>
       </c>
       <c r="G185" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H185" s="1">
         <v>0.405</v>
       </c>
-      <c r="I185" t="str">
-        <v/>
+      <c r="I185" s="1">
+        <v>0.2</v>
       </c>
       <c r="J185" t="str">
         <v>Legacy</v>
@@ -9117,7 +9117,7 @@
         <v>59-63</v>
       </c>
       <c r="G186" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H186" s="1">
         <v>0.27</v>
@@ -9164,7 +9164,7 @@
         <v>59-63</v>
       </c>
       <c r="G187" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H187" s="1">
         <v>0.135</v>
@@ -9211,13 +9211,13 @@
         <v>59-63</v>
       </c>
       <c r="G188" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H188" s="1">
         <v>0.09</v>
       </c>
-      <c r="I188" t="str">
-        <v/>
+      <c r="I188" s="1">
+        <v>0.2</v>
       </c>
       <c r="J188" t="str">
         <v>Legacy</v>
@@ -9258,13 +9258,13 @@
         <v>59-63</v>
       </c>
       <c r="G189" t="str">
-        <v>50-56</v>
+        <v>50-55</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
       </c>
-      <c r="I189" t="str">
-        <v/>
+      <c r="I189" s="1">
+        <v>0.2</v>
       </c>
       <c r="J189" t="str">
         <v>Legacy</v>
@@ -9305,7 +9305,7 @@
         <v>61-65</v>
       </c>
       <c r="G190" t="str">
-        <v>52-58</v>
+        <v>52-57</v>
       </c>
       <c r="H190" s="1">
         <v>1</v>
@@ -9352,13 +9352,13 @@
         <v>64-68</v>
       </c>
       <c r="G191" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H191" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I191" t="str">
-        <v/>
+      <c r="I191" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J191" t="str">
         <v>Legacy</v>
@@ -9399,13 +9399,13 @@
         <v>64-68</v>
       </c>
       <c r="G192" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H192" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I192" t="str">
-        <v/>
+      <c r="I192" s="1">
+        <v>0.14285714285714285</v>
       </c>
       <c r="J192" t="str">
         <v>Legacy</v>
@@ -9446,7 +9446,7 @@
         <v>64-68</v>
       </c>
       <c r="G193" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H193" s="1">
         <v>0.152</v>
@@ -9493,7 +9493,7 @@
         <v>64-68</v>
       </c>
       <c r="G194" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H194" s="1">
         <v>0.152</v>
@@ -9540,7 +9540,7 @@
         <v>64-68</v>
       </c>
       <c r="G195" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H195" s="1">
         <v>0.114</v>
@@ -9587,7 +9587,7 @@
         <v>64-68</v>
       </c>
       <c r="G196" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H196" s="1">
         <v>0.057</v>
@@ -9634,7 +9634,7 @@
         <v>64-68</v>
       </c>
       <c r="G197" t="str">
-        <v>54-60</v>
+        <v>53-58</v>
       </c>
       <c r="H197" s="1">
         <v>0.05</v>
@@ -9681,13 +9681,13 @@
         <v>62-66</v>
       </c>
       <c r="G198" t="str">
-        <v>56-62</v>
+        <v>55-60</v>
       </c>
       <c r="H198" s="1">
         <v>0.3</v>
       </c>
-      <c r="I198" t="str">
-        <v/>
+      <c r="I198" s="1">
+        <v>0.2</v>
       </c>
       <c r="J198" t="str">
         <v>Legacy</v>
@@ -9728,7 +9728,7 @@
         <v>62-66</v>
       </c>
       <c r="G199" t="str">
-        <v>56-62</v>
+        <v>55-60</v>
       </c>
       <c r="H199" s="1">
         <v>0.25</v>
@@ -9775,7 +9775,7 @@
         <v>62-66</v>
       </c>
       <c r="G200" t="str">
-        <v>56-62</v>
+        <v>55-60</v>
       </c>
       <c r="H200" s="1">
         <v>0.2</v>
@@ -9822,7 +9822,7 @@
         <v>62-66</v>
       </c>
       <c r="G201" t="str">
-        <v>56-62</v>
+        <v>55-60</v>
       </c>
       <c r="H201" s="1">
         <v>0.15</v>
@@ -9869,13 +9869,13 @@
         <v>62-66</v>
       </c>
       <c r="G202" t="str">
-        <v>56-62</v>
+        <v>55-60</v>
       </c>
       <c r="H202" s="1">
         <v>0.1</v>
       </c>
-      <c r="I202" t="str">
-        <v/>
+      <c r="I202" s="1">
+        <v>0.2</v>
       </c>
       <c r="J202" t="str">
         <v>Legacy</v>
@@ -9916,7 +9916,7 @@
         <v>120-120</v>
       </c>
       <c r="G203" t="str">
-        <v>57-63</v>
+        <v>120-120</v>
       </c>
       <c r="H203" s="1">
         <v>0.25</v>
@@ -9963,7 +9963,7 @@
         <v>120-120</v>
       </c>
       <c r="G204" t="str">
-        <v>57-63</v>
+        <v>120-120</v>
       </c>
       <c r="H204" s="1">
         <v>0.25</v>
@@ -10010,7 +10010,7 @@
         <v>110-110</v>
       </c>
       <c r="G205" t="str">
-        <v>57-63</v>
+        <v>110-110</v>
       </c>
       <c r="H205" s="1">
         <v>0.25</v>
@@ -10057,7 +10057,7 @@
         <v>110-110</v>
       </c>
       <c r="G206" t="str">
-        <v>57-63</v>
+        <v>110-110</v>
       </c>
       <c r="H206" s="1">
         <v>0.25</v>
@@ -10104,13 +10104,13 @@
         <v>70-75</v>
       </c>
       <c r="G207" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H207" s="1">
         <v>0.35</v>
       </c>
-      <c r="I207" t="str">
-        <v/>
+      <c r="I207" s="1">
+        <v>0.25</v>
       </c>
       <c r="J207" t="str">
         <v>Yes</v>
@@ -10151,7 +10151,7 @@
         <v>70-75</v>
       </c>
       <c r="G208" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H208" s="1">
         <v>0.3</v>
@@ -10198,7 +10198,7 @@
         <v>70-75</v>
       </c>
       <c r="G209" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H209" s="1">
         <v>0.2</v>
@@ -10245,13 +10245,13 @@
         <v>70-75</v>
       </c>
       <c r="G210" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H210" s="1">
         <v>0.15</v>
       </c>
-      <c r="I210" t="str">
-        <v/>
+      <c r="I210" s="1">
+        <v>0.25</v>
       </c>
       <c r="J210" t="str">
         <v>Yes</v>
@@ -10292,13 +10292,13 @@
         <v>76-81</v>
       </c>
       <c r="G211" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H211" s="1">
         <v>0.35</v>
       </c>
-      <c r="I211" t="str">
-        <v/>
+      <c r="I211" s="1">
+        <v>0.25</v>
       </c>
       <c r="J211" t="str">
         <v/>
@@ -10339,13 +10339,13 @@
         <v>76-81</v>
       </c>
       <c r="G212" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H212" s="1">
         <v>0.35</v>
       </c>
-      <c r="I212" t="str">
-        <v/>
+      <c r="I212" s="1">
+        <v>0.25</v>
       </c>
       <c r="J212" t="str">
         <v/>
@@ -10386,13 +10386,13 @@
         <v>76-81</v>
       </c>
       <c r="G213" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H213" s="1">
         <v>0.15</v>
       </c>
-      <c r="I213" t="str">
-        <v/>
+      <c r="I213" s="1">
+        <v>0.25</v>
       </c>
       <c r="J213" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v>76-81</v>
       </c>
       <c r="G214" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H214" s="1">
         <v>0.15</v>
       </c>
-      <c r="I214" t="str">
-        <v/>
+      <c r="I214" s="1">
+        <v>0.25</v>
       </c>
       <c r="J214" t="str">
         <v/>
@@ -10480,13 +10480,13 @@
         <v>82-87</v>
       </c>
       <c r="G215" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H215" s="1">
         <v>0.3325</v>
       </c>
-      <c r="I215" t="str">
-        <v/>
+      <c r="I215" s="1">
+        <v>0.2</v>
       </c>
       <c r="J215" t="str">
         <v>Legacy</v>
@@ -10527,7 +10527,7 @@
         <v>82-87</v>
       </c>
       <c r="G216" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H216" s="1">
         <v>0.2375</v>
@@ -10574,7 +10574,7 @@
         <v>82-87</v>
       </c>
       <c r="G217" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H217" s="1">
         <v>0.2375</v>
@@ -10621,7 +10621,7 @@
         <v>82-87</v>
       </c>
       <c r="G218" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H218" s="1">
         <v>0.1425</v>
@@ -10668,13 +10668,13 @@
         <v>82-87</v>
       </c>
       <c r="G219" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H219" s="1">
         <v>0.05</v>
       </c>
-      <c r="I219" t="str">
-        <v/>
+      <c r="I219" s="1">
+        <v>0.2</v>
       </c>
       <c r="J219" t="str">
         <v>Yes</v>
@@ -10715,7 +10715,7 @@
         <v>88-93</v>
       </c>
       <c r="G220" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H220" s="1">
         <v>0.3</v>
@@ -10762,7 +10762,7 @@
         <v>88-93</v>
       </c>
       <c r="G221" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H221" s="1">
         <v>0.3</v>
@@ -10809,7 +10809,7 @@
         <v>88-93</v>
       </c>
       <c r="G222" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H222" s="1">
         <v>0.2</v>
@@ -10856,7 +10856,7 @@
         <v>88-93</v>
       </c>
       <c r="G223" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H223" s="1">
         <v>0.2</v>
@@ -10903,13 +10903,13 @@
         <v>95-100</v>
       </c>
       <c r="G224" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H224" s="1">
         <v>0.38</v>
       </c>
-      <c r="I224" t="str">
-        <v/>
+      <c r="I224" s="1">
+        <v>0.25</v>
       </c>
       <c r="J224" t="str">
         <v>Yes</v>
@@ -10950,7 +10950,7 @@
         <v>95-100</v>
       </c>
       <c r="G225" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H225" s="1">
         <v>0.3325</v>
@@ -10997,7 +10997,7 @@
         <v>95-100</v>
       </c>
       <c r="G226" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H226" s="1">
         <v>0.2375</v>
@@ -11044,13 +11044,13 @@
         <v>95-100</v>
       </c>
       <c r="G227" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H227" s="1">
         <v>0.05</v>
       </c>
-      <c r="I227" t="str">
-        <v/>
+      <c r="I227" s="1">
+        <v>0.25</v>
       </c>
       <c r="J227" t="str">
         <v>Yes</v>
@@ -11091,7 +11091,7 @@
         <v>105-105</v>
       </c>
       <c r="G228" t="str">
-        <v>57-63</v>
+        <v>105-105</v>
       </c>
       <c r="H228" s="1">
         <v>0.33</v>
@@ -11138,7 +11138,7 @@
         <v>105-105</v>
       </c>
       <c r="G229" t="str">
-        <v>57-63</v>
+        <v>105-105</v>
       </c>
       <c r="H229" s="1">
         <v>0.33</v>
@@ -11185,7 +11185,7 @@
         <v>105-105</v>
       </c>
       <c r="G230" t="str">
-        <v>57-63</v>
+        <v>105-105</v>
       </c>
       <c r="H230" s="1">
         <v>0.33</v>
@@ -11232,7 +11232,7 @@
         <v>70-75</v>
       </c>
       <c r="G231" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H231" s="1">
         <v>0.3</v>
@@ -11279,7 +11279,7 @@
         <v>70-75</v>
       </c>
       <c r="G232" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H232" s="1">
         <v>0.3</v>
@@ -11326,7 +11326,7 @@
         <v>70-75</v>
       </c>
       <c r="G233" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H233" s="1">
         <v>0.25</v>
@@ -11373,13 +11373,13 @@
         <v>70-75</v>
       </c>
       <c r="G234" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H234" s="1">
         <v>0.15</v>
       </c>
-      <c r="I234" t="str">
-        <v/>
+      <c r="I234" s="1">
+        <v>0.25</v>
       </c>
       <c r="J234" t="str">
         <v>Yes</v>
@@ -11420,7 +11420,7 @@
         <v>76-81</v>
       </c>
       <c r="G235" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H235" s="1">
         <v>0.3334</v>
@@ -11467,7 +11467,7 @@
         <v>76-81</v>
       </c>
       <c r="G236" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H236" s="1">
         <v>0.3333</v>
@@ -11514,7 +11514,7 @@
         <v>76-81</v>
       </c>
       <c r="G237" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H237" s="1">
         <v>0.3333</v>
@@ -11561,13 +11561,13 @@
         <v>88-93</v>
       </c>
       <c r="G238" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H238" s="1">
         <v>0.35</v>
       </c>
-      <c r="I238" t="str">
-        <v/>
+      <c r="I238" s="1">
+        <v>0.25</v>
       </c>
       <c r="J238" t="str">
         <v/>
@@ -11608,13 +11608,13 @@
         <v>88-93</v>
       </c>
       <c r="G239" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H239" s="1">
         <v>0.35</v>
       </c>
-      <c r="I239" t="str">
-        <v/>
+      <c r="I239" s="1">
+        <v>0.25</v>
       </c>
       <c r="J239" t="str">
         <v/>
@@ -11655,13 +11655,13 @@
         <v>88-93</v>
       </c>
       <c r="G240" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H240" s="1">
         <v>0.15</v>
       </c>
-      <c r="I240" t="str">
-        <v/>
+      <c r="I240" s="1">
+        <v>0.25</v>
       </c>
       <c r="J240" t="str">
         <v/>
@@ -11702,13 +11702,13 @@
         <v>88-93</v>
       </c>
       <c r="G241" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H241" s="1">
         <v>0.15</v>
       </c>
-      <c r="I241" t="str">
-        <v/>
+      <c r="I241" s="1">
+        <v>0.25</v>
       </c>
       <c r="J241" t="str">
         <v/>
@@ -11749,7 +11749,7 @@
         <v>95-100</v>
       </c>
       <c r="G242" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H242" s="1">
         <v>0.25</v>
@@ -11796,7 +11796,7 @@
         <v>95-100</v>
       </c>
       <c r="G243" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H243" s="1">
         <v>0.25</v>
@@ -11843,7 +11843,7 @@
         <v>95-100</v>
       </c>
       <c r="G244" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H244" s="1">
         <v>0.25</v>
@@ -11890,7 +11890,7 @@
         <v>95-100</v>
       </c>
       <c r="G245" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H245" s="1">
         <v>0.25</v>
@@ -11937,7 +11937,7 @@
         <v>115-115</v>
       </c>
       <c r="G246" t="str">
-        <v>57-63</v>
+        <v>115-115</v>
       </c>
       <c r="H246" s="1">
         <v>0.33</v>
@@ -11984,7 +11984,7 @@
         <v>115-115</v>
       </c>
       <c r="G247" t="str">
-        <v>57-63</v>
+        <v>115-115</v>
       </c>
       <c r="H247" s="1">
         <v>0.33</v>
@@ -12031,7 +12031,7 @@
         <v>115-115</v>
       </c>
       <c r="G248" t="str">
-        <v>57-63</v>
+        <v>115-115</v>
       </c>
       <c r="H248" s="1">
         <v>0.33</v>
@@ -12078,7 +12078,7 @@
         <v>110-110</v>
       </c>
       <c r="G249" t="str">
-        <v>57-63</v>
+        <v>110-110</v>
       </c>
       <c r="H249" s="1">
         <v>0.5</v>
@@ -12125,7 +12125,7 @@
         <v>110-110</v>
       </c>
       <c r="G250" t="str">
-        <v>57-63</v>
+        <v>110-110</v>
       </c>
       <c r="H250" s="1">
         <v>0.5</v>
@@ -12172,7 +12172,7 @@
         <v>82-87</v>
       </c>
       <c r="G251" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H251" s="1">
         <v>0.3333</v>
@@ -12219,7 +12219,7 @@
         <v>82-87</v>
       </c>
       <c r="G252" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H252" s="1">
         <v>0.3333</v>
@@ -12266,7 +12266,7 @@
         <v>82-87</v>
       </c>
       <c r="G253" t="str">
-        <v>57-63</v>
+        <v>96-104</v>
       </c>
       <c r="H253" s="1">
         <v>0.3334</v>

--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O253"/>
+  <dimension ref="A1:O263"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,7 +475,7 @@
         <v>0.45</v>
       </c>
       <c r="I2" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J2" t="str">
         <v>Legacy</v>
@@ -501,7 +501,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C3" t="str">
         <v>Route 101</v>
@@ -522,7 +522,7 @@
         <v>0.45</v>
       </c>
       <c r="I3" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J3" t="str">
         <v>Legacy</v>
@@ -534,10 +534,10 @@
         <v>Yes</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>Route 103</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Poochyena","count":2}]}</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -548,7 +548,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="C4" t="str">
         <v>Route 101</v>
@@ -569,7 +569,7 @@
         <v>0.1</v>
       </c>
       <c r="I4" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J4" t="str">
         <v>Legacy</v>
@@ -581,10 +581,10 @@
         <v>Yes</v>
       </c>
       <c r="M4" t="str">
-        <v/>
+        <v>Route 103</v>
       </c>
       <c r="N4" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Poochyena","count":2}]}</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -639,10 +639,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B6" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C6" t="str">
         <v>Route 103</v>
@@ -675,10 +675,10 @@
         <v>Yes</v>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>Route 102</v>
       </c>
       <c r="N6" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wingull","count":1}]}</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -686,10 +686,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B7" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C7" t="str">
         <v>Route 103</v>
@@ -722,10 +722,10 @@
         <v>Yes</v>
       </c>
       <c r="M7" t="str">
-        <v/>
+        <v>Route 102</v>
       </c>
       <c r="N7" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wingull","count":1}]}</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -733,10 +733,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B8" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C8" t="str">
         <v>Route 103</v>
@@ -769,10 +769,10 @@
         <v>Yes</v>
       </c>
       <c r="M8" t="str">
-        <v/>
+        <v>Route 102</v>
       </c>
       <c r="N8" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wingull","count":1}]}</v>
       </c>
       <c r="O8" t="str">
         <v/>
@@ -780,10 +780,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v/>
+        <v>Challenge 1</v>
       </c>
       <c r="B9" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="C9" t="str">
         <v>Route 103</v>
@@ -816,10 +816,10 @@
         <v>Yes</v>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>Route 102</v>
       </c>
       <c r="N9" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wingull","count":1}]}</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -850,8 +850,8 @@
       <c r="H10" s="1">
         <v>0.25</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
+      <c r="I10" s="1">
+        <v>0.17</v>
       </c>
       <c r="J10" t="str">
         <v>Yes</v>
@@ -874,10 +874,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C11" t="str">
         <v>Route 102</v>
@@ -897,8 +897,8 @@
       <c r="H11" s="1">
         <v>0.25</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
+      <c r="I11" s="1">
+        <v>0.17</v>
       </c>
       <c r="J11" t="str">
         <v>Legacy</v>
@@ -910,10 +910,10 @@
         <v>Yes</v>
       </c>
       <c r="M11" t="str">
-        <v/>
+        <v>Route 104</v>
       </c>
       <c r="N11" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lotad","count":1},{"species":"Seedot","count":1}]}</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -921,10 +921,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B12" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C12" t="str">
         <v>Route 102</v>
@@ -957,10 +957,10 @@
         <v>Yes</v>
       </c>
       <c r="M12" t="str">
-        <v/>
+        <v>Route 104</v>
       </c>
       <c r="N12" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lotad","count":1},{"species":"Seedot","count":1}]}</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -968,10 +968,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B13" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C13" t="str">
         <v>Route 102</v>
@@ -1004,10 +1004,10 @@
         <v>Yes</v>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>Route 104</v>
       </c>
       <c r="N13" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lotad","count":1},{"species":"Seedot","count":1}]}</v>
       </c>
       <c r="O13" t="str">
         <v/>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C14" t="str">
         <v>Route 102</v>
@@ -1038,8 +1038,8 @@
       <c r="H14" s="1">
         <v>0.1</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
+      <c r="I14" s="1">
+        <v>0.17</v>
       </c>
       <c r="J14" t="str">
         <v>Legacy</v>
@@ -1051,10 +1051,10 @@
         <v>Yes</v>
       </c>
       <c r="M14" t="str">
-        <v/>
+        <v>Route 104</v>
       </c>
       <c r="N14" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lotad","count":1},{"species":"Seedot","count":1}]}</v>
       </c>
       <c r="O14" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Challenge 2</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="C15" t="str">
         <v>Route 102</v>
@@ -1086,7 +1086,7 @@
         <v>0.05</v>
       </c>
       <c r="I15" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J15" t="str">
         <v>Legacy</v>
@@ -1098,10 +1098,10 @@
         <v>Yes</v>
       </c>
       <c r="M15" t="str">
-        <v/>
+        <v>Route 104</v>
       </c>
       <c r="N15" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lotad","count":1},{"species":"Seedot","count":1}]}</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B17" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C17" t="str">
         <v>Route 104</v>
@@ -1192,10 +1192,10 @@
         <v>Yes</v>
       </c>
       <c r="M17" t="str">
-        <v/>
+        <v>Petalburg Woods</v>
       </c>
       <c r="N17" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Taillow","count":2}]}</v>
       </c>
       <c r="O17" t="str">
         <v/>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B18" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C18" t="str">
         <v>Route 104</v>
@@ -1239,10 +1239,10 @@
         <v>Yes</v>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>Petalburg Woods</v>
       </c>
       <c r="N18" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Taillow","count":2}]}</v>
       </c>
       <c r="O18" t="str">
         <v/>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B19" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C19" t="str">
         <v>Route 104</v>
@@ -1286,10 +1286,10 @@
         <v>Yes</v>
       </c>
       <c r="M19" t="str">
-        <v/>
+        <v>Petalburg Woods</v>
       </c>
       <c r="N19" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Taillow","count":2}]}</v>
       </c>
       <c r="O19" t="str">
         <v/>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>Challenge 3</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="C20" t="str">
         <v>Route 104</v>
@@ -1333,10 +1333,10 @@
         <v>Yes</v>
       </c>
       <c r="M20" t="str">
-        <v/>
+        <v>Petalburg Woods</v>
       </c>
       <c r="N20" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Taillow","count":2}]}</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1368,7 +1368,7 @@
         <v>0.3</v>
       </c>
       <c r="I21" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J21" t="str">
         <v>Legacy</v>
@@ -1391,10 +1391,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B22" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C22" t="str">
         <v>Petalburg Woods</v>
@@ -1427,10 +1427,10 @@
         <v>Yes</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>Route 116</v>
       </c>
       <c r="N22" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shroomish","count":1},{"species":"Slakoth","count":1}]}</v>
       </c>
       <c r="O22" t="str">
         <v/>
@@ -1438,10 +1438,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C23" t="str">
         <v>Petalburg Woods</v>
@@ -1474,10 +1474,10 @@
         <v>Yes</v>
       </c>
       <c r="M23" t="str">
-        <v/>
+        <v>Route 116</v>
       </c>
       <c r="N23" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shroomish","count":1},{"species":"Slakoth","count":1}]}</v>
       </c>
       <c r="O23" t="str">
         <v/>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B24" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C24" t="str">
         <v>Petalburg Woods</v>
@@ -1521,10 +1521,10 @@
         <v>Yes</v>
       </c>
       <c r="M24" t="str">
-        <v/>
+        <v>Route 116</v>
       </c>
       <c r="N24" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shroomish","count":1},{"species":"Slakoth","count":1}]}</v>
       </c>
       <c r="O24" t="str">
         <v/>
@@ -1532,10 +1532,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B25" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C25" t="str">
         <v>Petalburg Woods</v>
@@ -1555,8 +1555,8 @@
       <c r="H25" s="1">
         <v>0.1</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
+      <c r="I25" s="1">
+        <v>0.17</v>
       </c>
       <c r="J25" t="str">
         <v>Legacy</v>
@@ -1568,10 +1568,10 @@
         <v>Yes</v>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>Route 116</v>
       </c>
       <c r="N25" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shroomish","count":1},{"species":"Slakoth","count":1}]}</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1579,10 +1579,10 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v/>
+        <v>Challenge 4</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="C26" t="str">
         <v>Petalburg Woods</v>
@@ -1603,7 +1603,7 @@
         <v>0.05</v>
       </c>
       <c r="I26" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J26" t="str">
         <v>Legacy</v>
@@ -1615,10 +1615,10 @@
         <v>Yes</v>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>Route 116</v>
       </c>
       <c r="N26" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shroomish","count":1},{"species":"Slakoth","count":1}]}</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1644,13 +1644,13 @@
         <v>9-12</v>
       </c>
       <c r="G27" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H27" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
+      <c r="I27" s="1">
+        <v>0.17</v>
       </c>
       <c r="J27" t="str">
         <v>Yes</v>
@@ -1673,10 +1673,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B28" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C28" t="str">
         <v>Route 116</v>
@@ -1691,13 +1691,13 @@
         <v>9-12</v>
       </c>
       <c r="G28" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H28" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
+      <c r="I28" s="1">
+        <v>0.17</v>
       </c>
       <c r="J28" t="str">
         <v>Yes</v>
@@ -1709,10 +1709,10 @@
         <v>Yes</v>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>Rustboro Gym</v>
       </c>
       <c r="N28" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Whismur","count":2}]}</v>
       </c>
       <c r="O28" t="str">
         <v/>
@@ -1720,10 +1720,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B29" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C29" t="str">
         <v>Route 116</v>
@@ -1738,7 +1738,7 @@
         <v>9-12</v>
       </c>
       <c r="G29" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H29" s="1">
         <v>0.19</v>
@@ -1756,10 +1756,10 @@
         <v>Yes</v>
       </c>
       <c r="M29" t="str">
-        <v/>
+        <v>Rustboro Gym</v>
       </c>
       <c r="N29" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Whismur","count":2}]}</v>
       </c>
       <c r="O29" t="str">
         <v/>
@@ -1767,10 +1767,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B30" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C30" t="str">
         <v>Route 116</v>
@@ -1785,7 +1785,7 @@
         <v>9-12</v>
       </c>
       <c r="G30" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H30" s="1">
         <v>0.19</v>
@@ -1803,10 +1803,10 @@
         <v>Yes</v>
       </c>
       <c r="M30" t="str">
-        <v/>
+        <v>Rustboro Gym</v>
       </c>
       <c r="N30" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Whismur","count":2}]}</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C31" t="str">
         <v>Route 116</v>
@@ -1832,13 +1832,13 @@
         <v>9-12</v>
       </c>
       <c r="G31" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H31" s="1">
         <v>0.095</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
+      <c r="I31" s="1">
+        <v>0.17</v>
       </c>
       <c r="J31" t="str">
         <v>Legacy</v>
@@ -1850,10 +1850,10 @@
         <v>Yes</v>
       </c>
       <c r="M31" t="str">
-        <v/>
+        <v>Rustboro Gym</v>
       </c>
       <c r="N31" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Whismur","count":2}]}</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v/>
+        <v>Challenge 5</v>
       </c>
       <c r="B32" t="str">
-        <v/>
+        <v>Challenge 6</v>
       </c>
       <c r="C32" t="str">
         <v>Route 116</v>
@@ -1879,13 +1879,13 @@
         <v>9-12</v>
       </c>
       <c r="G32" t="str">
-        <v>6-8</v>
+        <v>7-9</v>
       </c>
       <c r="H32" s="1">
         <v>0.05</v>
       </c>
       <c r="I32" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J32" t="str">
         <v>Yes</v>
@@ -1897,10 +1897,10 @@
         <v>Yes</v>
       </c>
       <c r="M32" t="str">
-        <v/>
+        <v>Rustboro Gym</v>
       </c>
       <c r="N32" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Whismur","count":2}]}</v>
       </c>
       <c r="O32" t="str">
         <v/>
@@ -1926,13 +1926,13 @@
         <v>12-15</v>
       </c>
       <c r="G33" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H33" s="1">
         <v>0.1805</v>
       </c>
-      <c r="I33" t="str">
-        <v/>
+      <c r="I33" s="1">
+        <v>0.11</v>
       </c>
       <c r="J33" t="str">
         <v>Legacy</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B34" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C34" t="str">
         <v>Granite Cave</v>
@@ -1973,7 +1973,7 @@
         <v>12-15</v>
       </c>
       <c r="G34" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H34" s="1">
         <v>0.1425</v>
@@ -1991,10 +1991,10 @@
         <v>Yes</v>
       </c>
       <c r="M34" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N34" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O34" t="str">
         <v/>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B35" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C35" t="str">
         <v>Granite Cave</v>
@@ -2020,7 +2020,7 @@
         <v>12-15</v>
       </c>
       <c r="G35" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H35" s="1">
         <v>0.1425</v>
@@ -2038,10 +2038,10 @@
         <v>Yes</v>
       </c>
       <c r="M35" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N35" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B36" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C36" t="str">
         <v>Granite Cave</v>
@@ -2067,7 +2067,7 @@
         <v>12-15</v>
       </c>
       <c r="G36" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H36" s="1">
         <v>0.1425</v>
@@ -2085,10 +2085,10 @@
         <v>Yes</v>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N36" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C37" t="str">
         <v>Granite Cave</v>
@@ -2114,7 +2114,7 @@
         <v>12-15</v>
       </c>
       <c r="G37" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H37" s="1">
         <v>0.1425</v>
@@ -2132,10 +2132,10 @@
         <v>Yes</v>
       </c>
       <c r="M37" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N37" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O37" t="str">
         <v/>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B38" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C38" t="str">
         <v>Granite Cave</v>
@@ -2161,7 +2161,7 @@
         <v>12-15</v>
       </c>
       <c r="G38" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H38" s="1">
         <v>0.076</v>
@@ -2179,10 +2179,10 @@
         <v>Yes</v>
       </c>
       <c r="M38" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N38" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O38" t="str">
         <v/>
@@ -2190,10 +2190,10 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B39" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C39" t="str">
         <v>Granite Cave</v>
@@ -2208,7 +2208,7 @@
         <v>12-15</v>
       </c>
       <c r="G39" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H39" s="1">
         <v>0.076</v>
@@ -2226,10 +2226,10 @@
         <v>Yes</v>
       </c>
       <c r="M39" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N39" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O39" t="str">
         <v/>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C40" t="str">
         <v>Granite Cave</v>
@@ -2255,13 +2255,13 @@
         <v>12-15</v>
       </c>
       <c r="G40" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H40" s="1">
         <v>0.0475</v>
       </c>
-      <c r="I40" t="str">
-        <v/>
+      <c r="I40" s="1">
+        <v>0.11</v>
       </c>
       <c r="J40" t="str">
         <v>Legacy</v>
@@ -2273,10 +2273,10 @@
         <v>Yes</v>
       </c>
       <c r="M40" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N40" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2284,10 +2284,10 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v/>
+        <v>Challenge 7</v>
       </c>
       <c r="B41" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="C41" t="str">
         <v>Granite Cave</v>
@@ -2302,13 +2302,13 @@
         <v>12-15</v>
       </c>
       <c r="G41" t="str">
-        <v>8-10</v>
+        <v>9-11</v>
       </c>
       <c r="H41" s="1">
         <v>0.05</v>
       </c>
-      <c r="I41" t="str">
-        <v/>
+      <c r="I41" s="1">
+        <v>0.12</v>
       </c>
       <c r="J41" t="str">
         <v>Yes</v>
@@ -2320,10 +2320,10 @@
         <v>Yes</v>
       </c>
       <c r="M41" t="str">
-        <v/>
+        <v>Tiny Fishing Spot</v>
       </c>
       <c r="N41" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Makuhita","count":1},{"species":"Aron","count":1}]}</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2349,7 +2349,7 @@
         <v>14-17</v>
       </c>
       <c r="G42" t="str">
-        <v>10-12</v>
+        <v>11-13</v>
       </c>
       <c r="H42" s="1">
         <v>0.45</v>
@@ -2378,10 +2378,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B43" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C43" t="str">
         <v>Tiny Fishing Spot</v>
@@ -2396,7 +2396,7 @@
         <v>14-17</v>
       </c>
       <c r="G43" t="str">
-        <v>10-12</v>
+        <v>11-13</v>
       </c>
       <c r="H43" s="1">
         <v>0.18</v>
@@ -2414,10 +2414,10 @@
         <v>Yes</v>
       </c>
       <c r="M43" t="str">
-        <v/>
+        <v>Dewford Gym</v>
       </c>
       <c r="N43" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}]}</v>
       </c>
       <c r="O43" t="str">
         <v/>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B44" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C44" t="str">
         <v>Tiny Fishing Spot</v>
@@ -2443,7 +2443,7 @@
         <v>14-17</v>
       </c>
       <c r="G44" t="str">
-        <v>10-12</v>
+        <v>11-13</v>
       </c>
       <c r="H44" s="1">
         <v>0.18</v>
@@ -2461,10 +2461,10 @@
         <v>Yes</v>
       </c>
       <c r="M44" t="str">
-        <v/>
+        <v>Dewford Gym</v>
       </c>
       <c r="N44" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}]}</v>
       </c>
       <c r="O44" t="str">
         <v/>
@@ -2472,10 +2472,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B45" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C45" t="str">
         <v>Tiny Fishing Spot</v>
@@ -2490,7 +2490,7 @@
         <v>14-17</v>
       </c>
       <c r="G45" t="str">
-        <v>10-12</v>
+        <v>11-13</v>
       </c>
       <c r="H45" s="1">
         <v>0.09</v>
@@ -2508,10 +2508,10 @@
         <v>Yes</v>
       </c>
       <c r="M45" t="str">
-        <v/>
+        <v>Dewford Gym</v>
       </c>
       <c r="N45" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}]}</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2519,10 +2519,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v/>
+        <v>Challenge 8</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>Challenge 9</v>
       </c>
       <c r="C46" t="str">
         <v>Tiny Fishing Spot</v>
@@ -2537,7 +2537,7 @@
         <v>14-17</v>
       </c>
       <c r="G46" t="str">
-        <v>10-12</v>
+        <v>11-13</v>
       </c>
       <c r="H46" s="1">
         <v>0.1</v>
@@ -2555,10 +2555,10 @@
         <v>Yes</v>
       </c>
       <c r="M46" t="str">
-        <v/>
+        <v>Dewford Gym</v>
       </c>
       <c r="N46" t="str">
-        <v/>
+        <v>{"catchSpeciesByQuality":[{"species":"Magikarp","quality":"Epic","count":1}]}</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -2584,13 +2584,13 @@
         <v>17-20</v>
       </c>
       <c r="G47" t="str">
-        <v>12-15</v>
+        <v>13-16</v>
       </c>
       <c r="H47" s="1">
         <v>0.5</v>
       </c>
       <c r="I47" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J47" t="str">
         <v>Yes</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B48" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C48" t="str">
         <v>Route 107</v>
@@ -2631,13 +2631,13 @@
         <v>17-20</v>
       </c>
       <c r="G48" t="str">
-        <v>12-15</v>
+        <v>13-16</v>
       </c>
       <c r="H48" s="1">
         <v>0.4</v>
       </c>
-      <c r="I48" t="str">
-        <v/>
+      <c r="I48" s="1">
+        <v>0.33</v>
       </c>
       <c r="J48" t="str">
         <v>Yes</v>
@@ -2649,10 +2649,10 @@
         <v>Yes</v>
       </c>
       <c r="M48" t="str">
-        <v/>
+        <v>Mauville Gym</v>
       </c>
       <c r="N48" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 107","count":50}}</v>
       </c>
       <c r="O48" t="str">
         <v/>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v/>
+        <v>Challenge 10</v>
       </c>
       <c r="B49" t="str">
-        <v/>
+        <v>Challenge 11</v>
       </c>
       <c r="C49" t="str">
         <v>Route 107</v>
@@ -2678,13 +2678,13 @@
         <v>17-20</v>
       </c>
       <c r="G49" t="str">
-        <v>12-15</v>
+        <v>13-16</v>
       </c>
       <c r="H49" s="1">
         <v>0.1</v>
       </c>
       <c r="I49" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J49" t="str">
         <v>Yes</v>
@@ -2696,10 +2696,10 @@
         <v>Yes</v>
       </c>
       <c r="M49" t="str">
-        <v/>
+        <v>Mauville Gym</v>
       </c>
       <c r="N49" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 107","count":50}}</v>
       </c>
       <c r="O49" t="str">
         <v/>
@@ -2725,13 +2725,13 @@
         <v>20-23</v>
       </c>
       <c r="G50" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H50" s="1">
         <v>0.225</v>
       </c>
       <c r="I50" s="1">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="J50" t="str">
         <v>Legacy</v>
@@ -2754,10 +2754,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B51" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C51" t="str">
         <v>Route 110</v>
@@ -2772,7 +2772,7 @@
         <v>20-23</v>
       </c>
       <c r="G51" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H51" s="1">
         <v>0.135</v>
@@ -2790,10 +2790,10 @@
         <v>Yes</v>
       </c>
       <c r="M51" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N51" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -2801,10 +2801,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B52" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C52" t="str">
         <v>Route 110</v>
@@ -2819,7 +2819,7 @@
         <v>20-23</v>
       </c>
       <c r="G52" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H52" s="1">
         <v>0.135</v>
@@ -2837,10 +2837,10 @@
         <v>Yes</v>
       </c>
       <c r="M52" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N52" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O52" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B53" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C53" t="str">
         <v>Route 110</v>
@@ -2866,7 +2866,7 @@
         <v>20-23</v>
       </c>
       <c r="G53" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H53" s="1">
         <v>0.135</v>
@@ -2884,10 +2884,10 @@
         <v>Yes</v>
       </c>
       <c r="M53" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N53" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O53" t="str">
         <v/>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C54" t="str">
         <v>Route 110</v>
@@ -2913,7 +2913,7 @@
         <v>20-23</v>
       </c>
       <c r="G54" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H54" s="1">
         <v>0.135</v>
@@ -2931,10 +2931,10 @@
         <v>Yes</v>
       </c>
       <c r="M54" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N54" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O54" t="str">
         <v/>
@@ -2942,10 +2942,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C55" t="str">
         <v>Route 110</v>
@@ -2960,7 +2960,7 @@
         <v>20-23</v>
       </c>
       <c r="G55" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H55" s="1">
         <v>0.09</v>
@@ -2978,10 +2978,10 @@
         <v>Yes</v>
       </c>
       <c r="M55" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N55" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -2989,10 +2989,10 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B56" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C56" t="str">
         <v>Route 110</v>
@@ -3007,13 +3007,13 @@
         <v>20-23</v>
       </c>
       <c r="G56" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H56" s="1">
         <v>0.045</v>
       </c>
-      <c r="I56" t="str">
-        <v/>
+      <c r="I56" s="1">
+        <v>0.13</v>
       </c>
       <c r="J56" t="str">
         <v>Yes</v>
@@ -3025,10 +3025,10 @@
         <v>Yes</v>
       </c>
       <c r="M56" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N56" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v/>
+        <v>Challenge 12</v>
       </c>
       <c r="B57" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="C57" t="str">
         <v>Route 110</v>
@@ -3054,7 +3054,7 @@
         <v>20-23</v>
       </c>
       <c r="G57" t="str">
-        <v>14-17</v>
+        <v>15-18</v>
       </c>
       <c r="H57" s="1">
         <v>0.1</v>
@@ -3072,10 +3072,10 @@
         <v>Yes</v>
       </c>
       <c r="M57" t="str">
-        <v/>
+        <v>Route 117</v>
       </c>
       <c r="N57" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Electrike","count":2},{"species":"Plusle","count":1},{"species":"Minun","count":1}]}</v>
       </c>
       <c r="O57" t="str">
         <v/>
@@ -3101,13 +3101,13 @@
         <v>22-25</v>
       </c>
       <c r="G58" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H58" s="1">
         <v>0.19</v>
       </c>
-      <c r="I58" t="str">
-        <v/>
+      <c r="I58" s="1">
+        <v>0.13</v>
       </c>
       <c r="J58" t="str">
         <v>Yes</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B59" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C59" t="str">
         <v>Route 117</v>
@@ -3148,7 +3148,7 @@
         <v>22-25</v>
       </c>
       <c r="G59" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H59" s="1">
         <v>0.1425</v>
@@ -3166,10 +3166,10 @@
         <v>Yes</v>
       </c>
       <c r="M59" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N59" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O59" t="str">
         <v/>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B60" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C60" t="str">
         <v>Route 117</v>
@@ -3195,7 +3195,7 @@
         <v>22-25</v>
       </c>
       <c r="G60" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H60" s="1">
         <v>0.1425</v>
@@ -3213,10 +3213,10 @@
         <v>Yes</v>
       </c>
       <c r="M60" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N60" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C61" t="str">
         <v>Route 117</v>
@@ -3242,7 +3242,7 @@
         <v>22-25</v>
       </c>
       <c r="G61" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H61" s="1">
         <v>0.1425</v>
@@ -3260,10 +3260,10 @@
         <v>Yes</v>
       </c>
       <c r="M61" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N61" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3271,10 +3271,10 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B62" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C62" t="str">
         <v>Route 117</v>
@@ -3289,7 +3289,7 @@
         <v>22-25</v>
       </c>
       <c r="G62" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H62" s="1">
         <v>0.1425</v>
@@ -3307,10 +3307,10 @@
         <v>Yes</v>
       </c>
       <c r="M62" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N62" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O62" t="str">
         <v/>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C63" t="str">
         <v>Route 117</v>
@@ -3336,7 +3336,7 @@
         <v>22-25</v>
       </c>
       <c r="G63" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H63" s="1">
         <v>0.095</v>
@@ -3354,10 +3354,10 @@
         <v>Yes</v>
       </c>
       <c r="M63" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N63" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O63" t="str">
         <v/>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B64" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C64" t="str">
         <v>Route 117</v>
@@ -3383,7 +3383,7 @@
         <v>22-25</v>
       </c>
       <c r="G64" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H64" s="1">
         <v>0.095</v>
@@ -3401,10 +3401,10 @@
         <v>Yes</v>
       </c>
       <c r="M64" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N64" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O64" t="str">
         <v/>
@@ -3412,10 +3412,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v/>
+        <v>Challenge 13</v>
       </c>
       <c r="B65" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="C65" t="str">
         <v>Route 117</v>
@@ -3430,7 +3430,7 @@
         <v>22-25</v>
       </c>
       <c r="G65" t="str">
-        <v>16-19</v>
+        <v>17-20</v>
       </c>
       <c r="H65" s="1">
         <v>0.05</v>
@@ -3448,10 +3448,10 @@
         <v>Yes</v>
       </c>
       <c r="M65" t="str">
-        <v/>
+        <v>Route 111</v>
       </c>
       <c r="N65" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Illumise","count":1},{"species":"Volbeat","count":1}]}</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -3477,13 +3477,13 @@
         <v>23-27</v>
       </c>
       <c r="G66" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H66" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I66" t="str">
-        <v/>
+      <c r="I66" s="1">
+        <v>0.17</v>
       </c>
       <c r="J66" t="str">
         <v>Legacy</v>
@@ -3506,10 +3506,10 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B67" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C67" t="str">
         <v>Route 111</v>
@@ -3524,13 +3524,13 @@
         <v>23-27</v>
       </c>
       <c r="G67" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H67" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I67" t="str">
-        <v/>
+      <c r="I67" s="1">
+        <v>0.17</v>
       </c>
       <c r="J67" t="str">
         <v>Legacy</v>
@@ -3542,10 +3542,10 @@
         <v>Yes</v>
       </c>
       <c r="M67" t="str">
-        <v/>
+        <v>Lavaridge Gym</v>
       </c>
       <c r="N67" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Trapinch","count":1},{"species":"Cacnea","count":1}]}</v>
       </c>
       <c r="O67" t="str">
         <v/>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B68" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C68" t="str">
         <v>Route 111</v>
@@ -3571,13 +3571,13 @@
         <v>23-27</v>
       </c>
       <c r="G68" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H68" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I68" t="str">
-        <v/>
+      <c r="I68" s="1">
+        <v>0.17</v>
       </c>
       <c r="J68" t="str">
         <v>Legacy</v>
@@ -3589,10 +3589,10 @@
         <v>Yes</v>
       </c>
       <c r="M68" t="str">
-        <v/>
+        <v>Lavaridge Gym</v>
       </c>
       <c r="N68" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Trapinch","count":1},{"species":"Cacnea","count":1}]}</v>
       </c>
       <c r="O68" t="str">
         <v/>
@@ -3600,10 +3600,10 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C69" t="str">
         <v>Route 111</v>
@@ -3618,7 +3618,7 @@
         <v>23-27</v>
       </c>
       <c r="G69" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H69" s="1">
         <v>0.1425</v>
@@ -3636,10 +3636,10 @@
         <v>Yes</v>
       </c>
       <c r="M69" t="str">
-        <v/>
+        <v>Lavaridge Gym</v>
       </c>
       <c r="N69" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Trapinch","count":1},{"species":"Cacnea","count":1}]}</v>
       </c>
       <c r="O69" t="str">
         <v/>
@@ -3647,10 +3647,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B70" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C70" t="str">
         <v>Route 111</v>
@@ -3665,13 +3665,13 @@
         <v>23-27</v>
       </c>
       <c r="G70" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H70" s="1">
         <v>0.095</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
+      <c r="I70" s="1">
+        <v>0.17</v>
       </c>
       <c r="J70" t="str">
         <v>Legacy</v>
@@ -3683,10 +3683,10 @@
         <v>Yes</v>
       </c>
       <c r="M70" t="str">
-        <v/>
+        <v>Lavaridge Gym</v>
       </c>
       <c r="N70" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Trapinch","count":1},{"species":"Cacnea","count":1}]}</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v/>
+        <v>Challenge 14</v>
       </c>
       <c r="B71" t="str">
-        <v/>
+        <v>Challenge 15</v>
       </c>
       <c r="C71" t="str">
         <v>Route 111</v>
@@ -3712,13 +3712,13 @@
         <v>23-27</v>
       </c>
       <c r="G71" t="str">
-        <v>18-21</v>
+        <v>19-22</v>
       </c>
       <c r="H71" s="1">
         <v>0.05</v>
       </c>
       <c r="I71" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J71" t="str">
         <v>Yes</v>
@@ -3730,10 +3730,10 @@
         <v>Yes</v>
       </c>
       <c r="M71" t="str">
-        <v/>
+        <v>Lavaridge Gym</v>
       </c>
       <c r="N71" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Trapinch","count":1},{"species":"Cacnea","count":1}]}</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -3759,13 +3759,13 @@
         <v>27-30</v>
       </c>
       <c r="G72" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H72" s="1">
         <v>0.3</v>
       </c>
       <c r="I72" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J72" t="str">
         <v>Legacy</v>
@@ -3788,10 +3788,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C73" t="str">
         <v>Fiery Path</v>
@@ -3806,13 +3806,13 @@
         <v>27-30</v>
       </c>
       <c r="G73" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H73" s="1">
         <v>0.25</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
+      <c r="I73" s="1">
+        <v>0.17</v>
       </c>
       <c r="J73" t="str">
         <v>Legacy</v>
@@ -3824,10 +3824,10 @@
         <v>Yes</v>
       </c>
       <c r="M73" t="str">
-        <v/>
+        <v>Jagged Pass</v>
       </c>
       <c r="N73" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Numel","count":2},{"species":"Torkoal","count":1}]}</v>
       </c>
       <c r="O73" t="str">
         <v/>
@@ -3835,10 +3835,10 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B74" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C74" t="str">
         <v>Fiery Path</v>
@@ -3853,7 +3853,7 @@
         <v>27-30</v>
       </c>
       <c r="G74" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H74" s="1">
         <v>0.15</v>
@@ -3871,10 +3871,10 @@
         <v>Yes</v>
       </c>
       <c r="M74" t="str">
-        <v/>
+        <v>Jagged Pass</v>
       </c>
       <c r="N74" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Numel","count":2},{"species":"Torkoal","count":1}]}</v>
       </c>
       <c r="O74" t="str">
         <v/>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B75" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C75" t="str">
         <v>Fiery Path</v>
@@ -3900,7 +3900,7 @@
         <v>27-30</v>
       </c>
       <c r="G75" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H75" s="1">
         <v>0.15</v>
@@ -3918,10 +3918,10 @@
         <v>Yes</v>
       </c>
       <c r="M75" t="str">
-        <v/>
+        <v>Jagged Pass</v>
       </c>
       <c r="N75" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Numel","count":2},{"species":"Torkoal","count":1}]}</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -3929,10 +3929,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B76" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C76" t="str">
         <v>Fiery Path</v>
@@ -3947,13 +3947,13 @@
         <v>27-30</v>
       </c>
       <c r="G76" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H76" s="1">
         <v>0.1</v>
       </c>
-      <c r="I76" t="str">
-        <v/>
+      <c r="I76" s="1">
+        <v>0.17</v>
       </c>
       <c r="J76" t="str">
         <v>Legacy</v>
@@ -3965,10 +3965,10 @@
         <v>Yes</v>
       </c>
       <c r="M76" t="str">
-        <v/>
+        <v>Jagged Pass</v>
       </c>
       <c r="N76" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Numel","count":2},{"species":"Torkoal","count":1}]}</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -3976,10 +3976,10 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v/>
+        <v>Challenge 16</v>
       </c>
       <c r="B77" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="C77" t="str">
         <v>Fiery Path</v>
@@ -3994,13 +3994,13 @@
         <v>27-30</v>
       </c>
       <c r="G77" t="str">
-        <v>20-23</v>
+        <v>21-24</v>
       </c>
       <c r="H77" s="1">
         <v>0.05</v>
       </c>
       <c r="I77" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J77" t="str">
         <v>Legacy</v>
@@ -4012,10 +4012,10 @@
         <v>Yes</v>
       </c>
       <c r="M77" t="str">
-        <v/>
+        <v>Jagged Pass</v>
       </c>
       <c r="N77" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Numel","count":2},{"species":"Torkoal","count":1}]}</v>
       </c>
       <c r="O77" t="str">
         <v/>
@@ -4041,7 +4041,7 @@
         <v>28-32</v>
       </c>
       <c r="G78" t="str">
-        <v>21-24</v>
+        <v>23-26</v>
       </c>
       <c r="H78" s="1">
         <v>0.4275</v>
@@ -4070,10 +4070,10 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C79" t="str">
         <v>Jagged Pass</v>
@@ -4088,7 +4088,7 @@
         <v>28-32</v>
       </c>
       <c r="G79" t="str">
-        <v>21-24</v>
+        <v>23-26</v>
       </c>
       <c r="H79" s="1">
         <v>0.4275</v>
@@ -4106,10 +4106,10 @@
         <v>Yes</v>
       </c>
       <c r="M79" t="str">
-        <v/>
+        <v>Route 113</v>
       </c>
       <c r="N79" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Jagged Pass","count":100}}</v>
       </c>
       <c r="O79" t="str">
         <v/>
@@ -4117,10 +4117,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B80" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C80" t="str">
         <v>Jagged Pass</v>
@@ -4135,7 +4135,7 @@
         <v>28-32</v>
       </c>
       <c r="G80" t="str">
-        <v>21-24</v>
+        <v>23-26</v>
       </c>
       <c r="H80" s="1">
         <v>0.095</v>
@@ -4153,10 +4153,10 @@
         <v>Yes</v>
       </c>
       <c r="M80" t="str">
-        <v/>
+        <v>Route 113</v>
       </c>
       <c r="N80" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Jagged Pass","count":100}}</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4164,10 +4164,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v/>
+        <v>Challenge 17</v>
       </c>
       <c r="B81" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="C81" t="str">
         <v>Jagged Pass</v>
@@ -4182,7 +4182,7 @@
         <v>28-32</v>
       </c>
       <c r="G81" t="str">
-        <v>21-24</v>
+        <v>23-26</v>
       </c>
       <c r="H81" s="1">
         <v>0.05</v>
@@ -4200,10 +4200,10 @@
         <v>Yes</v>
       </c>
       <c r="M81" t="str">
-        <v/>
+        <v>Route 113</v>
       </c>
       <c r="N81" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Jagged Pass","count":100}}</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -4229,13 +4229,13 @@
         <v>30-33</v>
       </c>
       <c r="G82" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H82" s="1">
         <v>0.7</v>
       </c>
       <c r="I82" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J82" t="str">
         <v>Legacy</v>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B83" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C83" t="str">
         <v>Route 113</v>
@@ -4276,13 +4276,13 @@
         <v>30-33</v>
       </c>
       <c r="G83" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H83" s="1">
         <v>0.15</v>
       </c>
       <c r="I83" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.33</v>
       </c>
       <c r="J83" t="str">
         <v>Legacy</v>
@@ -4294,10 +4294,10 @@
         <v>Yes</v>
       </c>
       <c r="M83" t="str">
-        <v/>
+        <v>Route 114</v>
       </c>
       <c r="N83" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spinda","count":5}]}</v>
       </c>
       <c r="O83" t="str">
         <v/>
@@ -4305,10 +4305,10 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v/>
+        <v>Challenge 18</v>
       </c>
       <c r="B84" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="C84" t="str">
         <v>Route 113</v>
@@ -4323,13 +4323,13 @@
         <v>30-33</v>
       </c>
       <c r="G84" t="str">
-        <v>23-26</v>
+        <v>25-28</v>
       </c>
       <c r="H84" s="1">
         <v>0.15</v>
       </c>
       <c r="I84" s="1">
-        <v>0.3333333333333333</v>
+        <v>0.34</v>
       </c>
       <c r="J84" t="str">
         <v>Yes</v>
@@ -4341,10 +4341,10 @@
         <v>Yes</v>
       </c>
       <c r="M84" t="str">
-        <v/>
+        <v>Route 114</v>
       </c>
       <c r="N84" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spinda","count":5}]}</v>
       </c>
       <c r="O84" t="str">
         <v/>
@@ -4370,13 +4370,13 @@
         <v>31-35</v>
       </c>
       <c r="G85" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H85" s="1">
         <v>0.25</v>
       </c>
       <c r="I85" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J85" t="str">
         <v>Legacy</v>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B86" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C86" t="str">
         <v>Route 114</v>
@@ -4417,13 +4417,13 @@
         <v>31-35</v>
       </c>
       <c r="G86" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H86" s="1">
         <v>0.2</v>
       </c>
-      <c r="I86" t="str">
-        <v/>
+      <c r="I86" s="1">
+        <v>0.14</v>
       </c>
       <c r="J86" t="str">
         <v>Yes</v>
@@ -4435,10 +4435,10 @@
         <v>Yes</v>
       </c>
       <c r="M86" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N86" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -4446,10 +4446,10 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B87" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C87" t="str">
         <v>Route 114</v>
@@ -4464,7 +4464,7 @@
         <v>31-35</v>
       </c>
       <c r="G87" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H87" s="1">
         <v>0.15</v>
@@ -4482,10 +4482,10 @@
         <v>Yes</v>
       </c>
       <c r="M87" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N87" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O87" t="str">
         <v/>
@@ -4493,10 +4493,10 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C88" t="str">
         <v>Route 114</v>
@@ -4511,7 +4511,7 @@
         <v>31-35</v>
       </c>
       <c r="G88" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H88" s="1">
         <v>0.15</v>
@@ -4529,10 +4529,10 @@
         <v>Yes</v>
       </c>
       <c r="M88" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N88" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O88" t="str">
         <v/>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B89" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C89" t="str">
         <v>Route 114</v>
@@ -4558,7 +4558,7 @@
         <v>31-35</v>
       </c>
       <c r="G89" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H89" s="1">
         <v>0.1</v>
@@ -4576,10 +4576,10 @@
         <v>Yes</v>
       </c>
       <c r="M89" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N89" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O89" t="str">
         <v/>
@@ -4587,10 +4587,10 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B90" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C90" t="str">
         <v>Route 114</v>
@@ -4605,7 +4605,7 @@
         <v>31-35</v>
       </c>
       <c r="G90" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H90" s="1">
         <v>0.1</v>
@@ -4623,10 +4623,10 @@
         <v>Yes</v>
       </c>
       <c r="M90" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N90" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -4634,10 +4634,10 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v/>
+        <v>Challenge 19</v>
       </c>
       <c r="B91" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="C91" t="str">
         <v>Route 114</v>
@@ -4652,13 +4652,13 @@
         <v>31-35</v>
       </c>
       <c r="G91" t="str">
-        <v>25-28</v>
+        <v>27-30</v>
       </c>
       <c r="H91" s="1">
         <v>0.05</v>
       </c>
-      <c r="I91" t="str">
-        <v/>
+      <c r="I91" s="1">
+        <v>0.16</v>
       </c>
       <c r="J91" t="str">
         <v>Yes</v>
@@ -4670,10 +4670,10 @@
         <v>Yes</v>
       </c>
       <c r="M91" t="str">
-        <v/>
+        <v>Meteor Falls</v>
       </c>
       <c r="N91" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Zangoose","count":1},{"species":"Seviper","count":1}]}</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -4699,13 +4699,13 @@
         <v>33-37</v>
       </c>
       <c r="G92" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H92" s="1">
         <v>0.3325</v>
       </c>
       <c r="I92" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J92" t="str">
         <v>Legacy</v>
@@ -4728,10 +4728,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B93" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C93" t="str">
         <v>Meteor Falls</v>
@@ -4746,13 +4746,13 @@
         <v>33-37</v>
       </c>
       <c r="G93" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H93" s="1">
         <v>0.2375</v>
       </c>
-      <c r="I93" t="str">
-        <v/>
+      <c r="I93" s="1">
+        <v>0.17</v>
       </c>
       <c r="J93" t="str">
         <v>Legacy</v>
@@ -4764,10 +4764,10 @@
         <v>Yes</v>
       </c>
       <c r="M93" t="str">
-        <v/>
+        <v>Route 115</v>
       </c>
       <c r="N93" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bagon","count":1},{"species":"Solrock","count":1},{"species":"Lunatone","count":1}]}</v>
       </c>
       <c r="O93" t="str">
         <v/>
@@ -4775,10 +4775,10 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C94" t="str">
         <v>Meteor Falls</v>
@@ -4793,7 +4793,7 @@
         <v>33-37</v>
       </c>
       <c r="G94" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H94" s="1">
         <v>0.1425</v>
@@ -4811,10 +4811,10 @@
         <v>Yes</v>
       </c>
       <c r="M94" t="str">
-        <v/>
+        <v>Route 115</v>
       </c>
       <c r="N94" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bagon","count":1},{"species":"Solrock","count":1},{"species":"Lunatone","count":1}]}</v>
       </c>
       <c r="O94" t="str">
         <v/>
@@ -4822,10 +4822,10 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B95" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C95" t="str">
         <v>Meteor Falls</v>
@@ -4840,7 +4840,7 @@
         <v>33-37</v>
       </c>
       <c r="G95" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H95" s="1">
         <v>0.1425</v>
@@ -4858,10 +4858,10 @@
         <v>Yes</v>
       </c>
       <c r="M95" t="str">
-        <v/>
+        <v>Route 115</v>
       </c>
       <c r="N95" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bagon","count":1},{"species":"Solrock","count":1},{"species":"Lunatone","count":1}]}</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -4869,10 +4869,10 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B96" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C96" t="str">
         <v>Meteor Falls</v>
@@ -4887,13 +4887,13 @@
         <v>33-37</v>
       </c>
       <c r="G96" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H96" s="1">
         <v>0.095</v>
       </c>
-      <c r="I96" t="str">
-        <v/>
+      <c r="I96" s="1">
+        <v>0.17</v>
       </c>
       <c r="J96" t="str">
         <v>Legacy</v>
@@ -4905,10 +4905,10 @@
         <v>Yes</v>
       </c>
       <c r="M96" t="str">
-        <v/>
+        <v>Route 115</v>
       </c>
       <c r="N96" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bagon","count":1},{"species":"Solrock","count":1},{"species":"Lunatone","count":1}]}</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -4916,10 +4916,10 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v/>
+        <v>Challenge 20</v>
       </c>
       <c r="B97" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="C97" t="str">
         <v>Meteor Falls</v>
@@ -4934,13 +4934,13 @@
         <v>33-37</v>
       </c>
       <c r="G97" t="str">
-        <v>27-30</v>
+        <v>29-32</v>
       </c>
       <c r="H97" s="1">
         <v>0.05</v>
       </c>
       <c r="I97" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J97" t="str">
         <v>Yes</v>
@@ -4952,10 +4952,10 @@
         <v>Yes</v>
       </c>
       <c r="M97" t="str">
-        <v/>
+        <v>Route 115</v>
       </c>
       <c r="N97" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Bagon","count":1},{"species":"Solrock","count":1},{"species":"Lunatone","count":1}]}</v>
       </c>
       <c r="O97" t="str">
         <v/>
@@ -4981,7 +4981,7 @@
         <v>35-38</v>
       </c>
       <c r="G98" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H98" s="1">
         <v>0.3</v>
@@ -5010,10 +5010,10 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B99" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C99" t="str">
         <v>Route 115</v>
@@ -5028,7 +5028,7 @@
         <v>35-38</v>
       </c>
       <c r="G99" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H99" s="1">
         <v>0.25</v>
@@ -5046,10 +5046,10 @@
         <v>Yes</v>
       </c>
       <c r="M99" t="str">
-        <v/>
+        <v>Petalburg Gym</v>
       </c>
       <c r="N99" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swablu","count":2}]}</v>
       </c>
       <c r="O99" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C100" t="str">
         <v>Route 115</v>
@@ -5075,7 +5075,7 @@
         <v>35-38</v>
       </c>
       <c r="G100" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H100" s="1">
         <v>0.25</v>
@@ -5093,10 +5093,10 @@
         <v>Yes</v>
       </c>
       <c r="M100" t="str">
-        <v/>
+        <v>Petalburg Gym</v>
       </c>
       <c r="N100" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swablu","count":2}]}</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -5104,10 +5104,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B101" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C101" t="str">
         <v>Route 115</v>
@@ -5122,7 +5122,7 @@
         <v>35-38</v>
       </c>
       <c r="G101" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H101" s="1">
         <v>0.1</v>
@@ -5140,10 +5140,10 @@
         <v>Yes</v>
       </c>
       <c r="M101" t="str">
-        <v/>
+        <v>Petalburg Gym</v>
       </c>
       <c r="N101" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swablu","count":2}]}</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -5151,10 +5151,10 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v/>
+        <v>Challenge 21</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>Challenge 22</v>
       </c>
       <c r="C102" t="str">
         <v>Route 115</v>
@@ -5169,7 +5169,7 @@
         <v>35-38</v>
       </c>
       <c r="G102" t="str">
-        <v>29-32</v>
+        <v>31-34</v>
       </c>
       <c r="H102" s="1">
         <v>0.1</v>
@@ -5187,10 +5187,10 @@
         <v>Yes</v>
       </c>
       <c r="M102" t="str">
-        <v/>
+        <v>Petalburg Gym</v>
       </c>
       <c r="N102" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Swablu","count":2}]}</v>
       </c>
       <c r="O102" t="str">
         <v/>
@@ -5216,13 +5216,13 @@
         <v>38-41</v>
       </c>
       <c r="G103" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H103" s="1">
         <v>0.25</v>
       </c>
-      <c r="I103" t="str">
-        <v/>
+      <c r="I103" s="1">
+        <v>0.17</v>
       </c>
       <c r="J103" t="str">
         <v>Yes</v>
@@ -5245,10 +5245,10 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C104" t="str">
         <v>Route 118</v>
@@ -5263,7 +5263,7 @@
         <v>38-41</v>
       </c>
       <c r="G104" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H104" s="1">
         <v>0.2</v>
@@ -5281,10 +5281,10 @@
         <v>Yes</v>
       </c>
       <c r="M104" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N104" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Manectric","count":1},{"species":"Kecleon","count":1}]}</v>
       </c>
       <c r="O104" t="str">
         <v/>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C105" t="str">
         <v>Route 118</v>
@@ -5310,7 +5310,7 @@
         <v>38-41</v>
       </c>
       <c r="G105" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H105" s="1">
         <v>0.2</v>
@@ -5328,10 +5328,10 @@
         <v>Yes</v>
       </c>
       <c r="M105" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N105" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Manectric","count":1},{"species":"Kecleon","count":1}]}</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -5339,10 +5339,10 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C106" t="str">
         <v>Route 118</v>
@@ -5357,7 +5357,7 @@
         <v>38-41</v>
       </c>
       <c r="G106" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H106" s="1">
         <v>0.15</v>
@@ -5375,10 +5375,10 @@
         <v>Yes</v>
       </c>
       <c r="M106" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N106" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Manectric","count":1},{"species":"Kecleon","count":1}]}</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -5386,10 +5386,10 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C107" t="str">
         <v>Route 118</v>
@@ -5404,13 +5404,13 @@
         <v>38-41</v>
       </c>
       <c r="G107" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H107" s="1">
         <v>0.1</v>
       </c>
-      <c r="I107" t="str">
-        <v/>
+      <c r="I107" s="1">
+        <v>0.17</v>
       </c>
       <c r="J107" t="str">
         <v>Legacy</v>
@@ -5422,10 +5422,10 @@
         <v>Yes</v>
       </c>
       <c r="M107" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N107" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Manectric","count":1},{"species":"Kecleon","count":1}]}</v>
       </c>
       <c r="O107" t="str">
         <v/>
@@ -5433,10 +5433,10 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v/>
+        <v>Challenge 23</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="C108" t="str">
         <v>Route 118</v>
@@ -5451,7 +5451,7 @@
         <v>38-41</v>
       </c>
       <c r="G108" t="str">
-        <v>31-34</v>
+        <v>33-36</v>
       </c>
       <c r="H108" s="1">
         <v>0.1</v>
@@ -5469,10 +5469,10 @@
         <v>Yes</v>
       </c>
       <c r="M108" t="str">
-        <v/>
+        <v>Small Fishing Spot</v>
       </c>
       <c r="N108" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Manectric","count":1},{"species":"Kecleon","count":1}]}</v>
       </c>
       <c r="O108" t="str">
         <v/>
@@ -5498,13 +5498,13 @@
         <v>40-43</v>
       </c>
       <c r="G109" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H109" s="1">
         <v>0.09</v>
       </c>
-      <c r="I109" t="str">
-        <v/>
+      <c r="I109" s="1">
+        <v>0.14</v>
       </c>
       <c r="J109" t="str">
         <v/>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C110" t="str">
         <v>Small Fishing Spot</v>
@@ -5545,7 +5545,7 @@
         <v>40-43</v>
       </c>
       <c r="G110" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H110" s="1">
         <v>0.18</v>
@@ -5563,10 +5563,10 @@
         <v>Yes</v>
       </c>
       <c r="M110" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N110" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -5574,10 +5574,10 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C111" t="str">
         <v>Small Fishing Spot</v>
@@ -5592,7 +5592,7 @@
         <v>40-43</v>
       </c>
       <c r="G111" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H111" s="1">
         <v>0.18</v>
@@ -5610,10 +5610,10 @@
         <v>Yes</v>
       </c>
       <c r="M111" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N111" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C112" t="str">
         <v>Small Fishing Spot</v>
@@ -5639,13 +5639,13 @@
         <v>40-43</v>
       </c>
       <c r="G112" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H112" s="1">
         <v>0.09</v>
       </c>
-      <c r="I112" t="str">
-        <v/>
+      <c r="I112" s="1">
+        <v>0.14</v>
       </c>
       <c r="J112" t="str">
         <v/>
@@ -5657,10 +5657,10 @@
         <v>Yes</v>
       </c>
       <c r="M112" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N112" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O112" t="str">
         <v/>
@@ -5668,10 +5668,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B113" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C113" t="str">
         <v>Small Fishing Spot</v>
@@ -5686,7 +5686,7 @@
         <v>40-43</v>
       </c>
       <c r="G113" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H113" s="1">
         <v>0.18</v>
@@ -5704,10 +5704,10 @@
         <v>Yes</v>
       </c>
       <c r="M113" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N113" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O113" t="str">
         <v/>
@@ -5715,10 +5715,10 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C114" t="str">
         <v>Small Fishing Spot</v>
@@ -5733,7 +5733,7 @@
         <v>40-43</v>
       </c>
       <c r="G114" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H114" s="1">
         <v>0.18</v>
@@ -5751,10 +5751,10 @@
         <v>Yes</v>
       </c>
       <c r="M114" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N114" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O114" t="str">
         <v/>
@@ -5762,10 +5762,10 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v/>
+        <v>Challenge 24</v>
       </c>
       <c r="B115" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="C115" t="str">
         <v>Small Fishing Spot</v>
@@ -5780,13 +5780,13 @@
         <v>40-43</v>
       </c>
       <c r="G115" t="str">
-        <v>33-36</v>
+        <v>35-38</v>
       </c>
       <c r="H115" s="1">
         <v>0.1</v>
       </c>
-      <c r="I115" t="str">
-        <v/>
+      <c r="I115" s="1">
+        <v>0.16</v>
       </c>
       <c r="J115" t="str">
         <v/>
@@ -5798,10 +5798,10 @@
         <v>Yes</v>
       </c>
       <c r="M115" t="str">
-        <v/>
+        <v>Route 119</v>
       </c>
       <c r="N115" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Carvanha","count":1},{"species":"Barboach","count":1}]}</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -5827,13 +5827,13 @@
         <v>41-45</v>
       </c>
       <c r="G116" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H116" s="1">
         <v>0.3</v>
       </c>
       <c r="I116" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J116" t="str">
         <v>Yes</v>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B117" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C117" t="str">
         <v>Route 119</v>
@@ -5874,13 +5874,13 @@
         <v>41-45</v>
       </c>
       <c r="G117" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H117" s="1">
         <v>0.3</v>
       </c>
       <c r="I117" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.17</v>
       </c>
       <c r="J117" t="str">
         <v>Yes</v>
@@ -5892,10 +5892,10 @@
         <v>Yes</v>
       </c>
       <c r="M117" t="str">
-        <v/>
+        <v>Route 120</v>
       </c>
       <c r="N117" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":2}]}</v>
       </c>
       <c r="O117" t="str">
         <v/>
@@ -5903,10 +5903,10 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B118" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C118" t="str">
         <v>Route 119</v>
@@ -5921,7 +5921,7 @@
         <v>41-45</v>
       </c>
       <c r="G118" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H118" s="1">
         <v>0.15</v>
@@ -5939,10 +5939,10 @@
         <v>Yes</v>
       </c>
       <c r="M118" t="str">
-        <v/>
+        <v>Route 120</v>
       </c>
       <c r="N118" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":2}]}</v>
       </c>
       <c r="O118" t="str">
         <v/>
@@ -5950,10 +5950,10 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B119" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C119" t="str">
         <v>Route 119</v>
@@ -5968,13 +5968,13 @@
         <v>41-45</v>
       </c>
       <c r="G119" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H119" s="1">
         <v>0.1</v>
       </c>
-      <c r="I119" t="str">
-        <v/>
+      <c r="I119" s="1">
+        <v>0.17</v>
       </c>
       <c r="J119" t="str">
         <v>Yes</v>
@@ -5986,10 +5986,10 @@
         <v>Yes</v>
       </c>
       <c r="M119" t="str">
-        <v/>
+        <v>Route 120</v>
       </c>
       <c r="N119" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":2}]}</v>
       </c>
       <c r="O119" t="str">
         <v/>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B120" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C120" t="str">
         <v>Route 119</v>
@@ -6015,13 +6015,13 @@
         <v>41-45</v>
       </c>
       <c r="G120" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H120" s="1">
         <v>0.1</v>
       </c>
-      <c r="I120" t="str">
-        <v/>
+      <c r="I120" s="1">
+        <v>0.17</v>
       </c>
       <c r="J120" t="str">
         <v>Yes</v>
@@ -6033,10 +6033,10 @@
         <v>Yes</v>
       </c>
       <c r="M120" t="str">
-        <v/>
+        <v>Route 120</v>
       </c>
       <c r="N120" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":2}]}</v>
       </c>
       <c r="O120" t="str">
         <v/>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v/>
+        <v>Challenge 25</v>
       </c>
       <c r="B121" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="C121" t="str">
         <v>Route 119</v>
@@ -6062,13 +6062,13 @@
         <v>41-45</v>
       </c>
       <c r="G121" t="str">
-        <v>35-38</v>
+        <v>37-40</v>
       </c>
       <c r="H121" s="1">
         <v>0.05</v>
       </c>
       <c r="I121" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.15</v>
       </c>
       <c r="J121" t="str">
         <v>Yes</v>
@@ -6080,10 +6080,10 @@
         <v>Yes</v>
       </c>
       <c r="M121" t="str">
-        <v/>
+        <v>Route 120</v>
       </c>
       <c r="N121" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tropius","count":2}]}</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -6109,13 +6109,13 @@
         <v>43-46</v>
       </c>
       <c r="G122" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H122" s="1">
         <v>0.2375</v>
       </c>
       <c r="I122" s="1">
-        <v>0.125</v>
+        <v>0.13</v>
       </c>
       <c r="J122" t="str">
         <v>Yes</v>
@@ -6138,10 +6138,10 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B123" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C123" t="str">
         <v>Route 120</v>
@@ -6156,13 +6156,13 @@
         <v>43-46</v>
       </c>
       <c r="G123" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H123" s="1">
         <v>0.19</v>
       </c>
-      <c r="I123" t="str">
-        <v/>
+      <c r="I123" s="1">
+        <v>0.13</v>
       </c>
       <c r="J123" t="str">
         <v>Legacy</v>
@@ -6174,10 +6174,10 @@
         <v>Yes</v>
       </c>
       <c r="M123" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N123" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O123" t="str">
         <v/>
@@ -6185,10 +6185,10 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B124" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C124" t="str">
         <v>Route 120</v>
@@ -6203,7 +6203,7 @@
         <v>43-46</v>
       </c>
       <c r="G124" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H124" s="1">
         <v>0.1425</v>
@@ -6221,10 +6221,10 @@
         <v>Yes</v>
       </c>
       <c r="M124" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N124" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O124" t="str">
         <v/>
@@ -6232,10 +6232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B125" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C125" t="str">
         <v>Route 120</v>
@@ -6250,7 +6250,7 @@
         <v>43-46</v>
       </c>
       <c r="G125" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H125" s="1">
         <v>0.1425</v>
@@ -6268,10 +6268,10 @@
         <v>Yes</v>
       </c>
       <c r="M125" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N125" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O125" t="str">
         <v/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C126" t="str">
         <v>Route 120</v>
@@ -6297,7 +6297,7 @@
         <v>43-46</v>
       </c>
       <c r="G126" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H126" s="1">
         <v>0.095</v>
@@ -6315,10 +6315,10 @@
         <v>Yes</v>
       </c>
       <c r="M126" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N126" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O126" t="str">
         <v/>
@@ -6326,10 +6326,10 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B127" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C127" t="str">
         <v>Route 120</v>
@@ -6344,7 +6344,7 @@
         <v>43-46</v>
       </c>
       <c r="G127" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H127" s="1">
         <v>0.095</v>
@@ -6362,10 +6362,10 @@
         <v>Yes</v>
       </c>
       <c r="M127" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N127" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O127" t="str">
         <v/>
@@ -6373,10 +6373,10 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B128" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C128" t="str">
         <v>Route 120</v>
@@ -6391,13 +6391,13 @@
         <v>43-46</v>
       </c>
       <c r="G128" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H128" s="1">
         <v>0.0475</v>
       </c>
-      <c r="I128" t="str">
-        <v/>
+      <c r="I128" s="1">
+        <v>0.13</v>
       </c>
       <c r="J128" t="str">
         <v>Yes</v>
@@ -6409,10 +6409,10 @@
         <v>Yes</v>
       </c>
       <c r="M128" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N128" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O128" t="str">
         <v/>
@@ -6420,10 +6420,10 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v/>
+        <v>Challenge 26</v>
       </c>
       <c r="B129" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="C129" t="str">
         <v>Route 120</v>
@@ -6438,7 +6438,7 @@
         <v>43-46</v>
       </c>
       <c r="G129" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H129" s="1">
         <v>0.05</v>
@@ -6456,10 +6456,10 @@
         <v>Yes</v>
       </c>
       <c r="M129" t="str">
-        <v/>
+        <v>Route 121</v>
       </c>
       <c r="N129" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Absol","count":1}]}</v>
       </c>
       <c r="O129" t="str">
         <v/>
@@ -6485,7 +6485,7 @@
         <v>44-48</v>
       </c>
       <c r="G130" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H130" s="1">
         <v>0.2</v>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B131" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C131" t="str">
         <v>Route 121</v>
@@ -6532,13 +6532,13 @@
         <v>44-48</v>
       </c>
       <c r="G131" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H131" s="1">
         <v>0.25</v>
       </c>
-      <c r="I131" t="str">
-        <v/>
+      <c r="I131" s="1">
+        <v>0.17</v>
       </c>
       <c r="J131" t="str">
         <v>Yes</v>
@@ -6550,10 +6550,10 @@
         <v>Yes</v>
       </c>
       <c r="M131" t="str">
-        <v/>
+        <v>Safari Zone East, Safari Zone West, Safari Zone North</v>
       </c>
       <c r="N131" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shuppet","count":2},{"species":"Duskull","count":2}]}</v>
       </c>
       <c r="O131" t="str">
         <v/>
@@ -6561,10 +6561,10 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C132" t="str">
         <v>Route 121</v>
@@ -6579,7 +6579,7 @@
         <v>44-48</v>
       </c>
       <c r="G132" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H132" s="1">
         <v>0.2</v>
@@ -6597,10 +6597,10 @@
         <v>Yes</v>
       </c>
       <c r="M132" t="str">
-        <v/>
+        <v>Safari Zone East, Safari Zone West, Safari Zone North</v>
       </c>
       <c r="N132" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shuppet","count":2},{"species":"Duskull","count":2}]}</v>
       </c>
       <c r="O132" t="str">
         <v/>
@@ -6608,10 +6608,10 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B133" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C133" t="str">
         <v>Route 121</v>
@@ -6626,7 +6626,7 @@
         <v>44-48</v>
       </c>
       <c r="G133" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H133" s="1">
         <v>0.15</v>
@@ -6644,10 +6644,10 @@
         <v>Yes</v>
       </c>
       <c r="M133" t="str">
-        <v/>
+        <v>Safari Zone East, Safari Zone West, Safari Zone North</v>
       </c>
       <c r="N133" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shuppet","count":2},{"species":"Duskull","count":2}]}</v>
       </c>
       <c r="O133" t="str">
         <v/>
@@ -6655,10 +6655,10 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B134" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C134" t="str">
         <v>Route 121</v>
@@ -6673,13 +6673,13 @@
         <v>44-48</v>
       </c>
       <c r="G134" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H134" s="1">
         <v>0.1</v>
       </c>
-      <c r="I134" t="str">
-        <v/>
+      <c r="I134" s="1">
+        <v>0.17</v>
       </c>
       <c r="J134" t="str">
         <v>Legacy</v>
@@ -6691,10 +6691,10 @@
         <v>Yes</v>
       </c>
       <c r="M134" t="str">
-        <v/>
+        <v>Safari Zone East, Safari Zone West, Safari Zone North</v>
       </c>
       <c r="N134" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shuppet","count":2},{"species":"Duskull","count":2}]}</v>
       </c>
       <c r="O134" t="str">
         <v/>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v/>
+        <v>Challenge 27</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="C135" t="str">
         <v>Route 121</v>
@@ -6720,7 +6720,7 @@
         <v>44-48</v>
       </c>
       <c r="G135" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H135" s="1">
         <v>0.1</v>
@@ -6738,10 +6738,10 @@
         <v>Yes</v>
       </c>
       <c r="M135" t="str">
-        <v/>
+        <v>Safari Zone East, Safari Zone West, Safari Zone North</v>
       </c>
       <c r="N135" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Shuppet","count":2},{"species":"Duskull","count":2}]}</v>
       </c>
       <c r="O135" t="str">
         <v/>
@@ -6767,7 +6767,7 @@
         <v>46-50</v>
       </c>
       <c r="G136" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H136" s="1">
         <v>0.15</v>
@@ -6796,10 +6796,10 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B137" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C137" t="str">
         <v>Safari Zone East</v>
@@ -6814,7 +6814,7 @@
         <v>46-50</v>
       </c>
       <c r="G137" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H137" s="1">
         <v>0.15</v>
@@ -6832,10 +6832,10 @@
         <v>Yes</v>
       </c>
       <c r="M137" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N137" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O137" t="str">
         <v/>
@@ -6843,10 +6843,10 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B138" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C138" t="str">
         <v>Safari Zone East</v>
@@ -6861,7 +6861,7 @@
         <v>51-55</v>
       </c>
       <c r="G138" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H138" s="1">
         <v>0.08</v>
@@ -6879,10 +6879,10 @@
         <v>Yes</v>
       </c>
       <c r="M138" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N138" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O138" t="str">
         <v/>
@@ -6890,10 +6890,10 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B139" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C139" t="str">
         <v>Safari Zone East</v>
@@ -6908,7 +6908,7 @@
         <v>46-50</v>
       </c>
       <c r="G139" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H139" s="1">
         <v>0.07</v>
@@ -6926,10 +6926,10 @@
         <v>Yes</v>
       </c>
       <c r="M139" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N139" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O139" t="str">
         <v/>
@@ -6937,10 +6937,10 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B140" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C140" t="str">
         <v>Safari Zone East</v>
@@ -6955,7 +6955,7 @@
         <v>46-50</v>
       </c>
       <c r="G140" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H140" s="1">
         <v>0.11</v>
@@ -6973,10 +6973,10 @@
         <v>Yes</v>
       </c>
       <c r="M140" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N140" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O140" t="str">
         <v/>
@@ -6984,10 +6984,10 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C141" t="str">
         <v>Safari Zone East</v>
@@ -7002,7 +7002,7 @@
         <v>46-50</v>
       </c>
       <c r="G141" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H141" s="1">
         <v>0.1</v>
@@ -7020,10 +7020,10 @@
         <v>Yes</v>
       </c>
       <c r="M141" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N141" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O141" t="str">
         <v/>
@@ -7031,10 +7031,10 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B142" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C142" t="str">
         <v>Safari Zone East</v>
@@ -7049,7 +7049,7 @@
         <v>46-50</v>
       </c>
       <c r="G142" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H142" s="1">
         <v>0.09</v>
@@ -7067,10 +7067,10 @@
         <v>Yes</v>
       </c>
       <c r="M142" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N142" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O142" t="str">
         <v/>
@@ -7078,10 +7078,10 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C143" t="str">
         <v>Safari Zone East</v>
@@ -7096,7 +7096,7 @@
         <v>44-48</v>
       </c>
       <c r="G143" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H143" s="1">
         <v>0.15</v>
@@ -7114,10 +7114,10 @@
         <v>Yes</v>
       </c>
       <c r="M143" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N143" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O143" t="str">
         <v/>
@@ -7125,10 +7125,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B144" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="C144" t="str">
         <v>Safari Zone East</v>
@@ -7143,7 +7143,7 @@
         <v>51-55</v>
       </c>
       <c r="G144" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H144" s="1">
         <v>0.1</v>
@@ -7161,10 +7161,10 @@
         <v>Yes</v>
       </c>
       <c r="M144" t="str">
-        <v/>
+        <v>Mount Pyre</v>
       </c>
       <c r="N144" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Safari Zone East","count":150}}</v>
       </c>
       <c r="O144" t="str">
         <v/>
@@ -7190,7 +7190,7 @@
         <v>46-50</v>
       </c>
       <c r="G145" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H145" s="1">
         <v>0.12</v>
@@ -7219,7 +7219,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -7237,7 +7237,7 @@
         <v>46-50</v>
       </c>
       <c r="G146" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H146" s="1">
         <v>0.08</v>
@@ -7266,7 +7266,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -7284,7 +7284,7 @@
         <v>50-54</v>
       </c>
       <c r="G147" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H147" s="1">
         <v>0.08</v>
@@ -7313,7 +7313,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -7331,7 +7331,7 @@
         <v>46-50</v>
       </c>
       <c r="G148" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H148" s="1">
         <v>0.12</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B149" t="str">
         <v/>
@@ -7378,7 +7378,7 @@
         <v>50-54</v>
       </c>
       <c r="G149" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H149" s="1">
         <v>0.12</v>
@@ -7407,7 +7407,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -7425,7 +7425,7 @@
         <v>46-50</v>
       </c>
       <c r="G150" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H150" s="1">
         <v>0.08</v>
@@ -7454,7 +7454,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -7472,7 +7472,7 @@
         <v>50-54</v>
       </c>
       <c r="G151" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H151" s="1">
         <v>0.1</v>
@@ -7501,7 +7501,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -7519,7 +7519,7 @@
         <v>44-48</v>
       </c>
       <c r="G152" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H152" s="1">
         <v>0.1</v>
@@ -7548,7 +7548,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -7566,7 +7566,7 @@
         <v>44-48</v>
       </c>
       <c r="G153" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H153" s="1">
         <v>0.11</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -7613,7 +7613,7 @@
         <v>48-52</v>
       </c>
       <c r="G154" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H154" s="1">
         <v>0.09</v>
@@ -7660,7 +7660,7 @@
         <v>51-55</v>
       </c>
       <c r="G155" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H155" s="1">
         <v>0.16</v>
@@ -7689,7 +7689,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B156" t="str">
         <v/>
@@ -7707,7 +7707,7 @@
         <v>48-52</v>
       </c>
       <c r="G156" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H156" s="1">
         <v>0.16</v>
@@ -7736,7 +7736,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -7754,7 +7754,7 @@
         <v>51-55</v>
       </c>
       <c r="G157" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H157" s="1">
         <v>0.12</v>
@@ -7783,7 +7783,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -7801,7 +7801,7 @@
         <v>44-48</v>
       </c>
       <c r="G158" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H158" s="1">
         <v>0.12</v>
@@ -7830,7 +7830,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -7848,7 +7848,7 @@
         <v>48-52</v>
       </c>
       <c r="G159" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H159" s="1">
         <v>0.13</v>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B160" t="str">
         <v/>
@@ -7895,7 +7895,7 @@
         <v>44-48</v>
       </c>
       <c r="G160" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H160" s="1">
         <v>0.09</v>
@@ -7924,7 +7924,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -7942,7 +7942,7 @@
         <v>48-52</v>
       </c>
       <c r="G161" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H161" s="1">
         <v>0.13</v>
@@ -7971,7 +7971,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v/>
+        <v>Challenge 28</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -7989,7 +7989,7 @@
         <v>44-48</v>
       </c>
       <c r="G162" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H162" s="1">
         <v>0.09</v>
@@ -8036,7 +8036,7 @@
         <v>48-51</v>
       </c>
       <c r="G163" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H163" s="1">
         <v>0.3</v>
@@ -8065,10 +8065,10 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B164" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C164" t="str">
         <v>Mount Pyre</v>
@@ -8083,7 +8083,7 @@
         <v>48-51</v>
       </c>
       <c r="G164" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H164" s="1">
         <v>0.25</v>
@@ -8101,10 +8101,10 @@
         <v>Yes</v>
       </c>
       <c r="M164" t="str">
-        <v/>
+        <v>Route 123</v>
       </c>
       <c r="N164" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chimecho","count":1}]}</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -8112,10 +8112,10 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B165" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C165" t="str">
         <v>Mount Pyre</v>
@@ -8130,7 +8130,7 @@
         <v>48-51</v>
       </c>
       <c r="G165" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H165" s="1">
         <v>0.2</v>
@@ -8148,10 +8148,10 @@
         <v>Yes</v>
       </c>
       <c r="M165" t="str">
-        <v/>
+        <v>Route 123</v>
       </c>
       <c r="N165" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chimecho","count":1}]}</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C166" t="str">
         <v>Mount Pyre</v>
@@ -8177,13 +8177,13 @@
         <v>48-51</v>
       </c>
       <c r="G166" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H166" s="1">
         <v>0.15</v>
       </c>
-      <c r="I166" t="str">
-        <v/>
+      <c r="I166" s="1">
+        <v>0.2</v>
       </c>
       <c r="J166" t="str">
         <v>Yes</v>
@@ -8195,10 +8195,10 @@
         <v>Yes</v>
       </c>
       <c r="M166" t="str">
-        <v/>
+        <v>Route 123</v>
       </c>
       <c r="N166" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chimecho","count":1}]}</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v/>
+        <v>Challenge 29</v>
       </c>
       <c r="B167" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="C167" t="str">
         <v>Mount Pyre</v>
@@ -8224,7 +8224,7 @@
         <v>48-51</v>
       </c>
       <c r="G167" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H167" s="1">
         <v>0.1</v>
@@ -8242,10 +8242,10 @@
         <v>Yes</v>
       </c>
       <c r="M167" t="str">
-        <v/>
+        <v>Route 123</v>
       </c>
       <c r="N167" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Chimecho","count":1}]}</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -8271,7 +8271,7 @@
         <v>49-53</v>
       </c>
       <c r="G168" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H168" s="1">
         <v>0.3</v>
@@ -8300,10 +8300,10 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B169" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C169" t="str">
         <v>Route 123</v>
@@ -8318,7 +8318,7 @@
         <v>49-53</v>
       </c>
       <c r="G169" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H169" s="1">
         <v>0.25</v>
@@ -8336,10 +8336,10 @@
         <v>Yes</v>
       </c>
       <c r="M169" t="str">
-        <v/>
+        <v>Fortree Gym</v>
       </c>
       <c r="N169" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 123","count":150}}</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C170" t="str">
         <v>Route 123</v>
@@ -8365,7 +8365,7 @@
         <v>49-53</v>
       </c>
       <c r="G170" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H170" s="1">
         <v>0.2</v>
@@ -8383,10 +8383,10 @@
         <v>Yes</v>
       </c>
       <c r="M170" t="str">
-        <v/>
+        <v>Fortree Gym</v>
       </c>
       <c r="N170" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 123","count":150}}</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -8394,10 +8394,10 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B171" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C171" t="str">
         <v>Route 123</v>
@@ -8412,13 +8412,13 @@
         <v>49-53</v>
       </c>
       <c r="G171" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H171" s="1">
         <v>0.15</v>
       </c>
-      <c r="I171" t="str">
-        <v/>
+      <c r="I171" s="1">
+        <v>0.2</v>
       </c>
       <c r="J171" t="str">
         <v>Yes</v>
@@ -8430,10 +8430,10 @@
         <v>Yes</v>
       </c>
       <c r="M171" t="str">
-        <v/>
+        <v>Fortree Gym</v>
       </c>
       <c r="N171" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 123","count":150}}</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -8441,10 +8441,10 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v/>
+        <v>Challenge 30</v>
       </c>
       <c r="B172" t="str">
-        <v/>
+        <v>Challenge 31</v>
       </c>
       <c r="C172" t="str">
         <v>Route 123</v>
@@ -8459,7 +8459,7 @@
         <v>49-53</v>
       </c>
       <c r="G172" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H172" s="1">
         <v>0.1</v>
@@ -8477,10 +8477,10 @@
         <v>Yes</v>
       </c>
       <c r="M172" t="str">
-        <v/>
+        <v>Fortree Gym</v>
       </c>
       <c r="N172" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Route 123","count":150}}</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -8506,13 +8506,13 @@
         <v>54-58</v>
       </c>
       <c r="G173" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H173" s="1">
         <v>0.198</v>
       </c>
-      <c r="I173" t="str">
-        <v/>
+      <c r="I173" s="1">
+        <v>0.13</v>
       </c>
       <c r="J173" t="str">
         <v/>
@@ -8535,10 +8535,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B174" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C174" t="str">
         <v>Big Fishing Spot</v>
@@ -8553,13 +8553,13 @@
         <v>54-58</v>
       </c>
       <c r="G174" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H174" s="1">
         <v>0.198</v>
       </c>
-      <c r="I174" t="str">
-        <v/>
+      <c r="I174" s="1">
+        <v>0.13</v>
       </c>
       <c r="J174" t="str">
         <v/>
@@ -8571,10 +8571,10 @@
         <v>Yes</v>
       </c>
       <c r="M174" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N174" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O174" t="str">
         <v/>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B175" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C175" t="str">
         <v>Big Fishing Spot</v>
@@ -8600,7 +8600,7 @@
         <v>54-58</v>
       </c>
       <c r="G175" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H175" s="1">
         <v>0.135</v>
@@ -8618,10 +8618,10 @@
         <v>Yes</v>
       </c>
       <c r="M175" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N175" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -8629,10 +8629,10 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B176" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C176" t="str">
         <v>Big Fishing Spot</v>
@@ -8647,7 +8647,7 @@
         <v>54-58</v>
       </c>
       <c r="G176" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H176" s="1">
         <v>0.135</v>
@@ -8665,10 +8665,10 @@
         <v>Yes</v>
       </c>
       <c r="M176" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N176" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O176" t="str">
         <v/>
@@ -8676,10 +8676,10 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B177" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C177" t="str">
         <v>Big Fishing Spot</v>
@@ -8694,7 +8694,7 @@
         <v>54-58</v>
       </c>
       <c r="G177" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H177" s="1">
         <v>0.09</v>
@@ -8712,10 +8712,10 @@
         <v>Yes</v>
       </c>
       <c r="M177" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N177" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -8723,10 +8723,10 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B178" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C178" t="str">
         <v>Big Fishing Spot</v>
@@ -8741,13 +8741,13 @@
         <v>54-58</v>
       </c>
       <c r="G178" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H178" s="1">
         <v>0.072</v>
       </c>
-      <c r="I178" t="str">
-        <v/>
+      <c r="I178" s="1">
+        <v>0.13</v>
       </c>
       <c r="J178" t="str">
         <v/>
@@ -8759,10 +8759,10 @@
         <v>Yes</v>
       </c>
       <c r="M178" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N178" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -8770,10 +8770,10 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B179" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C179" t="str">
         <v>Big Fishing Spot</v>
@@ -8788,13 +8788,13 @@
         <v>54-58</v>
       </c>
       <c r="G179" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H179" s="1">
         <v>0.072</v>
       </c>
-      <c r="I179" t="str">
-        <v/>
+      <c r="I179" s="1">
+        <v>0.13</v>
       </c>
       <c r="J179" t="str">
         <v/>
@@ -8806,10 +8806,10 @@
         <v>Yes</v>
       </c>
       <c r="M179" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N179" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -8817,10 +8817,10 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v/>
+        <v>Challenge 33</v>
       </c>
       <c r="B180" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="C180" t="str">
         <v>Big Fishing Spot</v>
@@ -8835,7 +8835,7 @@
         <v>54-58</v>
       </c>
       <c r="G180" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H180" s="1">
         <v>0.1</v>
@@ -8853,10 +8853,10 @@
         <v>Yes</v>
       </c>
       <c r="M180" t="str">
-        <v/>
+        <v>Underwater Fishing Spot</v>
       </c>
       <c r="N180" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Feebas","count":1},{"species":"Wailmer","count":2}]}</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -8882,7 +8882,7 @@
         <v>56-60</v>
       </c>
       <c r="G181" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H181" s="1">
         <v>0.585</v>
@@ -8911,10 +8911,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B182" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C182" t="str">
         <v>Underwater Fishing Spot</v>
@@ -8929,7 +8929,7 @@
         <v>56-60</v>
       </c>
       <c r="G182" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H182" s="1">
         <v>0.225</v>
@@ -8947,10 +8947,10 @@
         <v>Yes</v>
       </c>
       <c r="M182" t="str">
-        <v/>
+        <v>Sootopolis Gym</v>
       </c>
       <c r="N182" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Relicanth","count":1},{"species":"Clamperl","count":2}]}</v>
       </c>
       <c r="O182" t="str">
         <v/>
@@ -8958,10 +8958,10 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B183" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C183" t="str">
         <v>Underwater Fishing Spot</v>
@@ -8976,7 +8976,7 @@
         <v>56-60</v>
       </c>
       <c r="G183" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H183" s="1">
         <v>0.09</v>
@@ -8994,10 +8994,10 @@
         <v>Yes</v>
       </c>
       <c r="M183" t="str">
-        <v/>
+        <v>Sootopolis Gym</v>
       </c>
       <c r="N183" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Relicanth","count":1},{"species":"Clamperl","count":2}]}</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -9005,10 +9005,10 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v/>
+        <v>Challenge 34</v>
       </c>
       <c r="B184" t="str">
-        <v/>
+        <v>Challenge 35</v>
       </c>
       <c r="C184" t="str">
         <v>Underwater Fishing Spot</v>
@@ -9023,7 +9023,7 @@
         <v>56-60</v>
       </c>
       <c r="G184" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H184" s="1">
         <v>0.1</v>
@@ -9041,10 +9041,10 @@
         <v>Yes</v>
       </c>
       <c r="M184" t="str">
-        <v/>
+        <v>Sootopolis Gym</v>
       </c>
       <c r="N184" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Relicanth","count":1},{"species":"Clamperl","count":2}]}</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -9070,7 +9070,7 @@
         <v>59-63</v>
       </c>
       <c r="G185" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H185" s="1">
         <v>0.405</v>
@@ -9099,10 +9099,10 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B186" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C186" t="str">
         <v>Shoal Cave</v>
@@ -9117,13 +9117,13 @@
         <v>59-63</v>
       </c>
       <c r="G186" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H186" s="1">
         <v>0.27</v>
       </c>
-      <c r="I186" t="str">
-        <v/>
+      <c r="I186" s="1">
+        <v>0.2</v>
       </c>
       <c r="J186" t="str">
         <v>Legacy</v>
@@ -9135,10 +9135,10 @@
         <v>Yes</v>
       </c>
       <c r="M186" t="str">
-        <v/>
+        <v>Mirage Island</v>
       </c>
       <c r="N186" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":2},{"species":"Snorunt","count":1}]}</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B187" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C187" t="str">
         <v>Shoal Cave</v>
@@ -9164,13 +9164,13 @@
         <v>59-63</v>
       </c>
       <c r="G187" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H187" s="1">
         <v>0.135</v>
       </c>
-      <c r="I187" t="str">
-        <v/>
+      <c r="I187" s="1">
+        <v>0.2</v>
       </c>
       <c r="J187" t="str">
         <v>Legacy</v>
@@ -9182,10 +9182,10 @@
         <v>Yes</v>
       </c>
       <c r="M187" t="str">
-        <v/>
+        <v>Mirage Island</v>
       </c>
       <c r="N187" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":2},{"species":"Snorunt","count":1}]}</v>
       </c>
       <c r="O187" t="str">
         <v/>
@@ -9193,10 +9193,10 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B188" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C188" t="str">
         <v>Shoal Cave</v>
@@ -9211,7 +9211,7 @@
         <v>59-63</v>
       </c>
       <c r="G188" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H188" s="1">
         <v>0.09</v>
@@ -9229,10 +9229,10 @@
         <v>Yes</v>
       </c>
       <c r="M188" t="str">
-        <v/>
+        <v>Mirage Island</v>
       </c>
       <c r="N188" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":2},{"species":"Snorunt","count":1}]}</v>
       </c>
       <c r="O188" t="str">
         <v/>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v/>
+        <v>Challenge 36</v>
       </c>
       <c r="B189" t="str">
-        <v/>
+        <v>Challenge 37</v>
       </c>
       <c r="C189" t="str">
         <v>Shoal Cave</v>
@@ -9258,7 +9258,7 @@
         <v>59-63</v>
       </c>
       <c r="G189" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H189" s="1">
         <v>0.1</v>
@@ -9276,10 +9276,10 @@
         <v>Yes</v>
       </c>
       <c r="M189" t="str">
-        <v/>
+        <v>Mirage Island</v>
       </c>
       <c r="N189" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Spheal","count":2},{"species":"Snorunt","count":1}]}</v>
       </c>
       <c r="O189" t="str">
         <v/>
@@ -9305,7 +9305,7 @@
         <v>61-65</v>
       </c>
       <c r="G190" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H190" s="1">
         <v>1</v>
@@ -9352,13 +9352,13 @@
         <v>64-68</v>
       </c>
       <c r="G191" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H191" s="1">
         <v>0.2375</v>
       </c>
       <c r="I191" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J191" t="str">
         <v>Legacy</v>
@@ -9381,10 +9381,10 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B192" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C192" t="str">
         <v>Victory Road</v>
@@ -9399,13 +9399,13 @@
         <v>64-68</v>
       </c>
       <c r="G192" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H192" s="1">
         <v>0.2375</v>
       </c>
       <c r="I192" s="1">
-        <v>0.14285714285714285</v>
+        <v>0.14</v>
       </c>
       <c r="J192" t="str">
         <v>Legacy</v>
@@ -9417,10 +9417,10 @@
         <v>Yes</v>
       </c>
       <c r="M192" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N192" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O192" t="str">
         <v/>
@@ -9428,10 +9428,10 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B193" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C193" t="str">
         <v>Victory Road</v>
@@ -9446,7 +9446,7 @@
         <v>64-68</v>
       </c>
       <c r="G193" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H193" s="1">
         <v>0.152</v>
@@ -9464,10 +9464,10 @@
         <v>Yes</v>
       </c>
       <c r="M193" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N193" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O193" t="str">
         <v/>
@@ -9475,10 +9475,10 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B194" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C194" t="str">
         <v>Victory Road</v>
@@ -9493,7 +9493,7 @@
         <v>64-68</v>
       </c>
       <c r="G194" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H194" s="1">
         <v>0.152</v>
@@ -9511,10 +9511,10 @@
         <v>Yes</v>
       </c>
       <c r="M194" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N194" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O194" t="str">
         <v/>
@@ -9522,10 +9522,10 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B195" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C195" t="str">
         <v>Victory Road</v>
@@ -9540,7 +9540,7 @@
         <v>64-68</v>
       </c>
       <c r="G195" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H195" s="1">
         <v>0.114</v>
@@ -9558,10 +9558,10 @@
         <v>Yes</v>
       </c>
       <c r="M195" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N195" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O195" t="str">
         <v/>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C196" t="str">
         <v>Victory Road</v>
@@ -9587,13 +9587,13 @@
         <v>64-68</v>
       </c>
       <c r="G196" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H196" s="1">
         <v>0.057</v>
       </c>
-      <c r="I196" t="str">
-        <v/>
+      <c r="I196" s="1">
+        <v>0.14</v>
       </c>
       <c r="J196" t="str">
         <v>Legacy</v>
@@ -9605,10 +9605,10 @@
         <v>Yes</v>
       </c>
       <c r="M196" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N196" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O196" t="str">
         <v/>
@@ -9616,10 +9616,10 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="B197" t="str">
-        <v/>
+        <v>Challenge 43</v>
       </c>
       <c r="C197" t="str">
         <v>Victory Road</v>
@@ -9634,13 +9634,13 @@
         <v>64-68</v>
       </c>
       <c r="G197" t="str">
-        <v>53-58</v>
+        <v>56-61</v>
       </c>
       <c r="H197" s="1">
         <v>0.05</v>
       </c>
-      <c r="I197" t="str">
-        <v/>
+      <c r="I197" s="1">
+        <v>0.16</v>
       </c>
       <c r="J197" t="str">
         <v>Yes</v>
@@ -9652,10 +9652,10 @@
         <v>Yes</v>
       </c>
       <c r="M197" t="str">
-        <v/>
+        <v>Hoenn Pokemon League</v>
       </c>
       <c r="N197" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Victory Road","count":200}}</v>
       </c>
       <c r="O197" t="str">
         <v/>
@@ -9681,7 +9681,7 @@
         <v>62-66</v>
       </c>
       <c r="G198" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="H198" s="1">
         <v>0.3</v>
@@ -9710,10 +9710,10 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B199" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C199" t="str">
         <v>Sky Pillar</v>
@@ -9728,7 +9728,7 @@
         <v>62-66</v>
       </c>
       <c r="G199" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="H199" s="1">
         <v>0.25</v>
@@ -9746,10 +9746,10 @@
         <v>Yes</v>
       </c>
       <c r="M199" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N199" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Altaria","count":1},{"species":"Claydol","count":1}]}</v>
       </c>
       <c r="O199" t="str">
         <v/>
@@ -9757,10 +9757,10 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B200" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C200" t="str">
         <v>Sky Pillar</v>
@@ -9775,7 +9775,7 @@
         <v>62-66</v>
       </c>
       <c r="G200" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="H200" s="1">
         <v>0.2</v>
@@ -9793,10 +9793,10 @@
         <v>Yes</v>
       </c>
       <c r="M200" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N200" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Altaria","count":1},{"species":"Claydol","count":1}]}</v>
       </c>
       <c r="O200" t="str">
         <v/>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B201" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C201" t="str">
         <v>Sky Pillar</v>
@@ -9822,13 +9822,13 @@
         <v>62-66</v>
       </c>
       <c r="G201" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="H201" s="1">
         <v>0.15</v>
       </c>
-      <c r="I201" t="str">
-        <v/>
+      <c r="I201" s="1">
+        <v>0.2</v>
       </c>
       <c r="J201" t="str">
         <v>Legacy</v>
@@ -9840,10 +9840,10 @@
         <v>Yes</v>
       </c>
       <c r="M201" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N201" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Altaria","count":1},{"species":"Claydol","count":1}]}</v>
       </c>
       <c r="O201" t="str">
         <v/>
@@ -9851,10 +9851,10 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v/>
+        <v>Challenge 41</v>
       </c>
       <c r="B202" t="str">
-        <v/>
+        <v>Challenge 42</v>
       </c>
       <c r="C202" t="str">
         <v>Sky Pillar</v>
@@ -9869,7 +9869,7 @@
         <v>62-66</v>
       </c>
       <c r="G202" t="str">
-        <v>55-60</v>
+        <v>58-63</v>
       </c>
       <c r="H202" s="1">
         <v>0.1</v>
@@ -9887,10 +9887,10 @@
         <v>Yes</v>
       </c>
       <c r="M202" t="str">
-        <v/>
+        <v>Victory Road</v>
       </c>
       <c r="N202" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Altaria","count":1},{"species":"Claydol","count":1}]}</v>
       </c>
       <c r="O202" t="str">
         <v/>
@@ -9945,10 +9945,10 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B204" t="str">
-        <v/>
+        <v>Nebula Fissure Challenge</v>
       </c>
       <c r="C204" t="str">
         <v>Nebula Fissure</v>
@@ -9984,7 +9984,7 @@
         <v/>
       </c>
       <c r="N204" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deoxys","count":1},{"species":"Jirachi","count":1}]}</v>
       </c>
       <c r="O204" t="str">
         <v/>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B205" t="str">
-        <v/>
+        <v>Nebula Fissure Challenge</v>
       </c>
       <c r="C205" t="str">
         <v>Nebula Fissure</v>
@@ -10031,7 +10031,7 @@
         <v/>
       </c>
       <c r="N205" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deoxys","count":1},{"species":"Jirachi","count":1}]}</v>
       </c>
       <c r="O205" t="str">
         <v/>
@@ -10039,10 +10039,10 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="B206" t="str">
-        <v/>
+        <v>Nebula Fissure Challenge</v>
       </c>
       <c r="C206" t="str">
         <v>Nebula Fissure</v>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="N206" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Deoxys","count":1},{"species":"Jirachi","count":1}]}</v>
       </c>
       <c r="O206" t="str">
         <v/>
@@ -10133,10 +10133,10 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B208" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C208" t="str">
         <v>Trick House</v>
@@ -10169,10 +10169,10 @@
         <v>No</v>
       </c>
       <c r="M208" t="str">
-        <v/>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="N208" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Trick House","count":20}}</v>
       </c>
       <c r="O208" t="str">
         <v/>
@@ -10180,10 +10180,10 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B209" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C209" t="str">
         <v>Trick House</v>
@@ -10216,10 +10216,10 @@
         <v>No</v>
       </c>
       <c r="M209" t="str">
-        <v/>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="N209" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Trick House","count":20}}</v>
       </c>
       <c r="O209" t="str">
         <v/>
@@ -10227,10 +10227,10 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="C210" t="str">
         <v>Trick House</v>
@@ -10263,10 +10263,10 @@
         <v>No</v>
       </c>
       <c r="M210" t="str">
-        <v/>
+        <v>Rustboro Fossil Lab</v>
       </c>
       <c r="N210" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Trick House","count":20}}</v>
       </c>
       <c r="O210" t="str">
         <v/>
@@ -10321,10 +10321,10 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B212" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C212" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -10357,10 +10357,10 @@
         <v>No</v>
       </c>
       <c r="M212" t="str">
-        <v/>
+        <v>Abandoned Ship</v>
       </c>
       <c r="N212" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lileep","count":1},{"species":"Anorith","count":1}]}</v>
       </c>
       <c r="O212" t="str">
         <v/>
@@ -10368,10 +10368,10 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B213" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C213" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -10404,10 +10404,10 @@
         <v>No</v>
       </c>
       <c r="M213" t="str">
-        <v/>
+        <v>Abandoned Ship</v>
       </c>
       <c r="N213" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lileep","count":1},{"species":"Anorith","count":1}]}</v>
       </c>
       <c r="O213" t="str">
         <v/>
@@ -10415,10 +10415,10 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v/>
+        <v>Extra Challenge B 1</v>
       </c>
       <c r="B214" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="C214" t="str">
         <v>Rustboro Fossil Lab</v>
@@ -10451,10 +10451,10 @@
         <v>No</v>
       </c>
       <c r="M214" t="str">
-        <v/>
+        <v>Abandoned Ship</v>
       </c>
       <c r="N214" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Lileep","count":1},{"species":"Anorith","count":1}]}</v>
       </c>
       <c r="O214" t="str">
         <v/>
@@ -10509,10 +10509,10 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C216" t="str">
         <v>Abandoned Ship</v>
@@ -10545,10 +10545,10 @@
         <v>No</v>
       </c>
       <c r="M216" t="str">
-        <v/>
+        <v>Enemy Hideout</v>
       </c>
       <c r="N216" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tentacruel","count":1}]}</v>
       </c>
       <c r="O216" t="str">
         <v/>
@@ -10556,10 +10556,10 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B217" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C217" t="str">
         <v>Abandoned Ship</v>
@@ -10592,10 +10592,10 @@
         <v>No</v>
       </c>
       <c r="M217" t="str">
-        <v/>
+        <v>Enemy Hideout</v>
       </c>
       <c r="N217" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tentacruel","count":1}]}</v>
       </c>
       <c r="O217" t="str">
         <v/>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B218" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C218" t="str">
         <v>Abandoned Ship</v>
@@ -10626,8 +10626,8 @@
       <c r="H218" s="1">
         <v>0.1425</v>
       </c>
-      <c r="I218" t="str">
-        <v/>
+      <c r="I218" s="1">
+        <v>0.2</v>
       </c>
       <c r="J218" t="str">
         <v>Yes</v>
@@ -10639,10 +10639,10 @@
         <v>No</v>
       </c>
       <c r="M218" t="str">
-        <v/>
+        <v>Enemy Hideout</v>
       </c>
       <c r="N218" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tentacruel","count":1}]}</v>
       </c>
       <c r="O218" t="str">
         <v/>
@@ -10650,10 +10650,10 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v/>
+        <v>Extra Challenge B 2</v>
       </c>
       <c r="B219" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="C219" t="str">
         <v>Abandoned Ship</v>
@@ -10686,10 +10686,10 @@
         <v>No</v>
       </c>
       <c r="M219" t="str">
-        <v/>
+        <v>Enemy Hideout</v>
       </c>
       <c r="N219" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Tentacruel","count":1}]}</v>
       </c>
       <c r="O219" t="str">
         <v/>
@@ -10744,10 +10744,10 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B221" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C221" t="str">
         <v>Enemy Hideout</v>
@@ -10780,10 +10780,10 @@
         <v>No</v>
       </c>
       <c r="M221" t="str">
-        <v/>
+        <v>Sealed Chamber</v>
       </c>
       <c r="N221" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Weezing","count":1}],"defeatCountRoute":{"route":"Enemy Hideout","count":25}}</v>
       </c>
       <c r="O221" t="str">
         <v/>
@@ -10791,10 +10791,10 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B222" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C222" t="str">
         <v>Enemy Hideout</v>
@@ -10827,10 +10827,10 @@
         <v>No</v>
       </c>
       <c r="M222" t="str">
-        <v/>
+        <v>Sealed Chamber</v>
       </c>
       <c r="N222" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Weezing","count":1}],"defeatCountRoute":{"route":"Enemy Hideout","count":25}}</v>
       </c>
       <c r="O222" t="str">
         <v/>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v/>
+        <v>Extra Challenge B 3</v>
       </c>
       <c r="B223" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="C223" t="str">
         <v>Enemy Hideout</v>
@@ -10874,10 +10874,10 @@
         <v>No</v>
       </c>
       <c r="M223" t="str">
-        <v/>
+        <v>Sealed Chamber</v>
       </c>
       <c r="N223" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Weezing","count":1}],"defeatCountRoute":{"route":"Enemy Hideout","count":25}}</v>
       </c>
       <c r="O223" t="str">
         <v/>
@@ -10932,10 +10932,10 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B225" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="C225" t="str">
         <v>Sealed Chamber</v>
@@ -10955,8 +10955,8 @@
       <c r="H225" s="1">
         <v>0.3325</v>
       </c>
-      <c r="I225" t="str">
-        <v/>
+      <c r="I225" s="1">
+        <v>0.25</v>
       </c>
       <c r="J225" t="str">
         <v>Yes</v>
@@ -10968,10 +10968,10 @@
         <v>No</v>
       </c>
       <c r="M225" t="str">
-        <v/>
+        <v>Ancient Ruins</v>
       </c>
       <c r="N225" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Relicanth","count":1}}</v>
       </c>
       <c r="O225" t="str">
         <v/>
@@ -10979,10 +10979,10 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B226" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="C226" t="str">
         <v>Sealed Chamber</v>
@@ -11015,10 +11015,10 @@
         <v>No</v>
       </c>
       <c r="M226" t="str">
-        <v/>
+        <v>Ancient Ruins</v>
       </c>
       <c r="N226" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Relicanth","count":1}}</v>
       </c>
       <c r="O226" t="str">
         <v/>
@@ -11026,10 +11026,10 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v/>
+        <v>Extra Challenge B 4</v>
       </c>
       <c r="B227" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="C227" t="str">
         <v>Sealed Chamber</v>
@@ -11062,10 +11062,10 @@
         <v>No</v>
       </c>
       <c r="M227" t="str">
-        <v/>
+        <v>Ancient Ruins</v>
       </c>
       <c r="N227" t="str">
-        <v/>
+        <v>{"defeatSpecific":{"name":"Relicanth","count":1}}</v>
       </c>
       <c r="O227" t="str">
         <v/>
@@ -11096,8 +11096,8 @@
       <c r="H228" s="1">
         <v>0.33</v>
       </c>
-      <c r="I228" t="str">
-        <v/>
+      <c r="I228" s="1">
+        <v>0.33</v>
       </c>
       <c r="J228" t="str">
         <v>Yes</v>
@@ -11120,10 +11120,10 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>Extra Challenge B 6</v>
       </c>
       <c r="C229" t="str">
         <v>Ancient Ruins</v>
@@ -11143,8 +11143,8 @@
       <c r="H229" s="1">
         <v>0.33</v>
       </c>
-      <c r="I229" t="str">
-        <v/>
+      <c r="I229" s="1">
+        <v>0.33</v>
       </c>
       <c r="J229" t="str">
         <v>Yes</v>
@@ -11156,10 +11156,10 @@
         <v>No</v>
       </c>
       <c r="M229" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="N229" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Regirock","count":1},{"species":"Regice","count":1},{"species":"Registeel","count":1}]}</v>
       </c>
       <c r="O229" t="str">
         <v/>
@@ -11167,10 +11167,10 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v/>
+        <v>Extra Challenge B 5</v>
       </c>
       <c r="B230" t="str">
-        <v/>
+        <v>Extra Challenge B 6</v>
       </c>
       <c r="C230" t="str">
         <v>Ancient Ruins</v>
@@ -11190,8 +11190,8 @@
       <c r="H230" s="1">
         <v>0.33</v>
       </c>
-      <c r="I230" t="str">
-        <v/>
+      <c r="I230" s="1">
+        <v>0.34</v>
       </c>
       <c r="J230" t="str">
         <v>Yes</v>
@@ -11203,10 +11203,10 @@
         <v>No</v>
       </c>
       <c r="M230" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="N230" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Regirock","count":1},{"species":"Regice","count":1},{"species":"Registeel","count":1}]}</v>
       </c>
       <c r="O230" t="str">
         <v/>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B232" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C232" t="str">
         <v>Mauville Game Corner</v>
@@ -11297,10 +11297,10 @@
         <v>No</v>
       </c>
       <c r="M232" t="str">
-        <v/>
+        <v>Starter Sanctuary</v>
       </c>
       <c r="N232" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Slakoth","Abra"],"quality":"Common","count":8}]}</v>
       </c>
       <c r="O232" t="str">
         <v/>
@@ -11308,10 +11308,10 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B233" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C233" t="str">
         <v>Mauville Game Corner</v>
@@ -11344,10 +11344,10 @@
         <v>No</v>
       </c>
       <c r="M233" t="str">
-        <v/>
+        <v>Starter Sanctuary</v>
       </c>
       <c r="N233" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Slakoth","Abra"],"quality":"Common","count":8}]}</v>
       </c>
       <c r="O233" t="str">
         <v/>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B234" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="C234" t="str">
         <v>Mauville Game Corner</v>
@@ -11391,10 +11391,10 @@
         <v>No</v>
       </c>
       <c r="M234" t="str">
-        <v/>
+        <v>Starter Sanctuary</v>
       </c>
       <c r="N234" t="str">
-        <v/>
+        <v>{"catchSpeciesAnyOfByQuality":[{"species":["Slakoth","Abra"],"quality":"Common","count":8}]}</v>
       </c>
       <c r="O234" t="str">
         <v/>
@@ -11449,10 +11449,10 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B236" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C236" t="str">
         <v>Starter Sanctuary</v>
@@ -11485,10 +11485,10 @@
         <v>No</v>
       </c>
       <c r="M236" t="str">
-        <v/>
+        <v>Advanced Starter Sanctuary</v>
       </c>
       <c r="N236" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Treecko","count":1},{"species":"Torchic","count":1},{"species":"Mudkip","count":1}]}</v>
       </c>
       <c r="O236" t="str">
         <v/>
@@ -11496,10 +11496,10 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v/>
+        <v>Extra Challenge A 1</v>
       </c>
       <c r="B237" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="C237" t="str">
         <v>Starter Sanctuary</v>
@@ -11532,10 +11532,10 @@
         <v>No</v>
       </c>
       <c r="M237" t="str">
-        <v/>
+        <v>Advanced Starter Sanctuary</v>
       </c>
       <c r="N237" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Treecko","count":1},{"species":"Torchic","count":1},{"species":"Mudkip","count":1}]}</v>
       </c>
       <c r="O237" t="str">
         <v/>
@@ -11590,10 +11590,10 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B239" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C239" t="str">
         <v>Daycare Special Spot</v>
@@ -11626,10 +11626,10 @@
         <v>No</v>
       </c>
       <c r="M239" t="str">
-        <v/>
+        <v>Battle Frontier Facility</v>
       </c>
       <c r="N239" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wynaut","count":1},{"species":"Azurill","count":1}]}</v>
       </c>
       <c r="O239" t="str">
         <v/>
@@ -11637,10 +11637,10 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B240" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C240" t="str">
         <v>Daycare Special Spot</v>
@@ -11673,10 +11673,10 @@
         <v>No</v>
       </c>
       <c r="M240" t="str">
-        <v/>
+        <v>Battle Frontier Facility</v>
       </c>
       <c r="N240" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wynaut","count":1},{"species":"Azurill","count":1}]}</v>
       </c>
       <c r="O240" t="str">
         <v/>
@@ -11684,10 +11684,10 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="B241" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="C241" t="str">
         <v>Daycare Special Spot</v>
@@ -11720,10 +11720,10 @@
         <v>No</v>
       </c>
       <c r="M241" t="str">
-        <v/>
+        <v>Battle Frontier Facility</v>
       </c>
       <c r="N241" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Wynaut","count":1},{"species":"Azurill","count":1}]}</v>
       </c>
       <c r="O241" t="str">
         <v/>
@@ -11778,10 +11778,10 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B243" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C243" t="str">
         <v>Battle Frontier Facility</v>
@@ -11814,10 +11814,10 @@
         <v>No</v>
       </c>
       <c r="M243" t="str">
-        <v/>
+        <v>Weather Climax Cave</v>
       </c>
       <c r="N243" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Battle Frontier Facility","count":50}}</v>
       </c>
       <c r="O243" t="str">
         <v/>
@@ -11825,10 +11825,10 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B244" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C244" t="str">
         <v>Battle Frontier Facility</v>
@@ -11861,10 +11861,10 @@
         <v>No</v>
       </c>
       <c r="M244" t="str">
-        <v/>
+        <v>Weather Climax Cave</v>
       </c>
       <c r="N244" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Battle Frontier Facility","count":50}}</v>
       </c>
       <c r="O244" t="str">
         <v/>
@@ -11872,10 +11872,10 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v/>
+        <v>Extra Challenge A 4</v>
       </c>
       <c r="B245" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="C245" t="str">
         <v>Battle Frontier Facility</v>
@@ -11908,10 +11908,10 @@
         <v>No</v>
       </c>
       <c r="M245" t="str">
-        <v/>
+        <v>Weather Climax Cave</v>
       </c>
       <c r="N245" t="str">
-        <v/>
+        <v>{"defeatCountRoute":{"route":"Battle Frontier Facility","count":50}}</v>
       </c>
       <c r="O245" t="str">
         <v/>
@@ -11942,8 +11942,8 @@
       <c r="H246" s="1">
         <v>0.33</v>
       </c>
-      <c r="I246" t="str">
-        <v/>
+      <c r="I246" s="1">
+        <v>0.33</v>
       </c>
       <c r="J246" t="str">
         <v>Yes</v>
@@ -11966,10 +11966,10 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B247" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C247" t="str">
         <v>Weather Climax Cave</v>
@@ -11989,8 +11989,8 @@
       <c r="H247" s="1">
         <v>0.33</v>
       </c>
-      <c r="I247" t="str">
-        <v/>
+      <c r="I247" s="1">
+        <v>0.33</v>
       </c>
       <c r="J247" t="str">
         <v>Yes</v>
@@ -12002,10 +12002,10 @@
         <v>No</v>
       </c>
       <c r="M247" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="N247" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kyogre","count":1},{"species":"Groudon","count":1},{"species":"Rayquaza","count":1}]}</v>
       </c>
       <c r="O247" t="str">
         <v/>
@@ -12013,10 +12013,10 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v/>
+        <v>Extra Challenge A 5</v>
       </c>
       <c r="B248" t="str">
-        <v/>
+        <v>Extra Challenge A 6</v>
       </c>
       <c r="C248" t="str">
         <v>Weather Climax Cave</v>
@@ -12036,8 +12036,8 @@
       <c r="H248" s="1">
         <v>0.33</v>
       </c>
-      <c r="I248" t="str">
-        <v/>
+      <c r="I248" s="1">
+        <v>0.34</v>
       </c>
       <c r="J248" t="str">
         <v>Yes</v>
@@ -12049,10 +12049,10 @@
         <v>No</v>
       </c>
       <c r="M248" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="N248" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Kyogre","count":1},{"species":"Groudon","count":1},{"species":"Rayquaza","count":1}]}</v>
       </c>
       <c r="O248" t="str">
         <v/>
@@ -12107,10 +12107,10 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v/>
+        <v>Challenge 44</v>
       </c>
       <c r="B250" t="str">
-        <v/>
+        <v>Extra Challenge (Roaming)</v>
       </c>
       <c r="C250" t="str">
         <v>Roaming Hoenn Skies</v>
@@ -12143,10 +12143,10 @@
         <v>No</v>
       </c>
       <c r="M250" t="str">
-        <v/>
+        <v>Key to Nebula Fissure Challenge</v>
       </c>
       <c r="N250" t="str">
-        <v/>
+        <v>{"defeatMultipleSpecific":[{"name":"Latias","count":1},{"name":"Latios","count":1}]}</v>
       </c>
       <c r="O250" t="str">
         <v/>
@@ -12201,10 +12201,10 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B252" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C252" t="str">
         <v>Advanced Starter Sanctuary</v>
@@ -12237,10 +12237,10 @@
         <v>Yes</v>
       </c>
       <c r="M252" t="str">
-        <v/>
+        <v>Daycare Special Spot</v>
       </c>
       <c r="N252" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Grovyle","count":1},{"species":"Combusken","count":1},{"species":"Marshtomp","count":1}]}</v>
       </c>
       <c r="O252" t="str">
         <v/>
@@ -12248,10 +12248,10 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v/>
+        <v>Extra Challenge A 2</v>
       </c>
       <c r="B253" t="str">
-        <v/>
+        <v>Extra Challenge A 3</v>
       </c>
       <c r="C253" t="str">
         <v>Advanced Starter Sanctuary</v>
@@ -12284,25 +12284,495 @@
         <v>Yes</v>
       </c>
       <c r="M253" t="str">
-        <v/>
+        <v>Daycare Special Spot</v>
       </c>
       <c r="N253" t="str">
-        <v/>
+        <v>{"catchSpecies":[{"species":"Grovyle","count":1},{"species":"Combusken","count":1},{"species":"Marshtomp","count":1}]}</v>
       </c>
       <c r="O253" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>Challenge 6</v>
+      </c>
+      <c r="B254" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="C254" t="str">
+        <v>Rustboro Gym</v>
+      </c>
+      <c r="D254" t="str">
+        <v/>
+      </c>
+      <c r="E254" t="str">
+        <v/>
+      </c>
+      <c r="F254" t="str">
+        <v/>
+      </c>
+      <c r="G254" t="str">
+        <v/>
+      </c>
+      <c r="H254" t="str">
+        <v/>
+      </c>
+      <c r="I254" t="str">
+        <v/>
+      </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
+      <c r="K254" t="str">
+        <v/>
+      </c>
+      <c r="L254" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M254" t="str">
+        <v>Granite Cave</v>
+      </c>
+      <c r="N254" t="str">
+        <v>{"earnBadge":{"name":"Stone Badge","leader":"Roxanne","badgeCount":1}}</v>
+      </c>
+      <c r="O254" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>Challenge 9</v>
+      </c>
+      <c r="B255" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="C255" t="str">
+        <v>Dewford Gym</v>
+      </c>
+      <c r="D255" t="str">
+        <v/>
+      </c>
+      <c r="E255" t="str">
+        <v/>
+      </c>
+      <c r="F255" t="str">
+        <v/>
+      </c>
+      <c r="G255" t="str">
+        <v/>
+      </c>
+      <c r="H255" t="str">
+        <v/>
+      </c>
+      <c r="I255" t="str">
+        <v/>
+      </c>
+      <c r="J255" t="str">
+        <v/>
+      </c>
+      <c r="K255" t="str">
+        <v/>
+      </c>
+      <c r="L255" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M255" t="str">
+        <v>Route 107</v>
+      </c>
+      <c r="N255" t="str">
+        <v>{"earnBadge":{"name":"Knuckle Badge","leader":"Brawly","badgeCount":2}}</v>
+      </c>
+      <c r="O255" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>Challenge 11</v>
+      </c>
+      <c r="B256" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="C256" t="str">
+        <v>Mauville Gym</v>
+      </c>
+      <c r="D256" t="str">
+        <v/>
+      </c>
+      <c r="E256" t="str">
+        <v/>
+      </c>
+      <c r="F256" t="str">
+        <v/>
+      </c>
+      <c r="G256" t="str">
+        <v/>
+      </c>
+      <c r="H256" t="str">
+        <v/>
+      </c>
+      <c r="I256" t="str">
+        <v/>
+      </c>
+      <c r="J256" t="str">
+        <v/>
+      </c>
+      <c r="K256" t="str">
+        <v/>
+      </c>
+      <c r="L256" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M256" t="str">
+        <v>Route 110</v>
+      </c>
+      <c r="N256" t="str">
+        <v>{"earnBadge":{"name":"Dynamo Badge","leader":"Wattson","badgeCount":3}}</v>
+      </c>
+      <c r="O256" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>Challenge 15</v>
+      </c>
+      <c r="B257" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="C257" t="str">
+        <v>Lavaridge Gym</v>
+      </c>
+      <c r="D257" t="str">
+        <v/>
+      </c>
+      <c r="E257" t="str">
+        <v/>
+      </c>
+      <c r="F257" t="str">
+        <v/>
+      </c>
+      <c r="G257" t="str">
+        <v/>
+      </c>
+      <c r="H257" t="str">
+        <v/>
+      </c>
+      <c r="I257" t="str">
+        <v/>
+      </c>
+      <c r="J257" t="str">
+        <v/>
+      </c>
+      <c r="K257" t="str">
+        <v/>
+      </c>
+      <c r="L257" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M257" t="str">
+        <v>Fiery Path</v>
+      </c>
+      <c r="N257" t="str">
+        <v>{"earnBadge":{"name":"Heat Badge","leader":"Flannery","badgeCount":4}}</v>
+      </c>
+      <c r="O257" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>Challenge 22</v>
+      </c>
+      <c r="B258" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="C258" t="str">
+        <v>Petalburg Gym</v>
+      </c>
+      <c r="D258" t="str">
+        <v/>
+      </c>
+      <c r="E258" t="str">
+        <v/>
+      </c>
+      <c r="F258" t="str">
+        <v/>
+      </c>
+      <c r="G258" t="str">
+        <v/>
+      </c>
+      <c r="H258" t="str">
+        <v/>
+      </c>
+      <c r="I258" t="str">
+        <v/>
+      </c>
+      <c r="J258" t="str">
+        <v/>
+      </c>
+      <c r="K258" t="str">
+        <v/>
+      </c>
+      <c r="L258" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M258" t="str">
+        <v>Route 118</v>
+      </c>
+      <c r="N258" t="str">
+        <v>{"earnBadge":{"name":"Balance Badge","leader":"Norman","badgeCount":5}}</v>
+      </c>
+      <c r="O258" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>Challenge 31</v>
+      </c>
+      <c r="B259" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="C259" t="str">
+        <v>Fortree Gym</v>
+      </c>
+      <c r="D259" t="str">
+        <v/>
+      </c>
+      <c r="E259" t="str">
+        <v/>
+      </c>
+      <c r="F259" t="str">
+        <v/>
+      </c>
+      <c r="G259" t="str">
+        <v/>
+      </c>
+      <c r="H259" t="str">
+        <v/>
+      </c>
+      <c r="I259" t="str">
+        <v/>
+      </c>
+      <c r="J259" t="str">
+        <v/>
+      </c>
+      <c r="K259" t="str">
+        <v/>
+      </c>
+      <c r="L259" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M259" t="str">
+        <v>Mossdeep Gym</v>
+      </c>
+      <c r="N259" t="str">
+        <v>{"earnBadge":{"name":"Feather Badge","leader":"Winona","badgeCount":6}}</v>
+      </c>
+      <c r="O259" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B260" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="C260" t="str">
+        <v>Mossdeep Gym</v>
+      </c>
+      <c r="D260" t="str">
+        <v/>
+      </c>
+      <c r="E260" t="str">
+        <v/>
+      </c>
+      <c r="F260" t="str">
+        <v/>
+      </c>
+      <c r="G260" t="str">
+        <v/>
+      </c>
+      <c r="H260" t="str">
+        <v/>
+      </c>
+      <c r="I260" t="str">
+        <v/>
+      </c>
+      <c r="J260" t="str">
+        <v/>
+      </c>
+      <c r="K260" t="str">
+        <v/>
+      </c>
+      <c r="L260" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M260" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="N260" t="str">
+        <v>{"earnBadge":{"name":"Mind Badge","leader":"Tate and Liza","badgeCount":7}}</v>
+      </c>
+      <c r="O260" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>Challenge 35</v>
+      </c>
+      <c r="B261" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="C261" t="str">
+        <v>Sootopolis Gym</v>
+      </c>
+      <c r="D261" t="str">
+        <v/>
+      </c>
+      <c r="E261" t="str">
+        <v/>
+      </c>
+      <c r="F261" t="str">
+        <v/>
+      </c>
+      <c r="G261" t="str">
+        <v/>
+      </c>
+      <c r="H261" t="str">
+        <v/>
+      </c>
+      <c r="I261" t="str">
+        <v/>
+      </c>
+      <c r="J261" t="str">
+        <v/>
+      </c>
+      <c r="K261" t="str">
+        <v/>
+      </c>
+      <c r="L261" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M261" t="str">
+        <v>Shoal Cave</v>
+      </c>
+      <c r="N261" t="str">
+        <v>{"earnBadge":{"name":"Rain Badge","leader":"Juan","badgeCount":8}}</v>
+      </c>
+      <c r="O261" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>Challenge 43</v>
+      </c>
+      <c r="B262" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="C262" t="str">
+        <v>Hoenn Pokemon League</v>
+      </c>
+      <c r="D262" t="str">
+        <v/>
+      </c>
+      <c r="E262" t="str">
+        <v/>
+      </c>
+      <c r="F262" t="str">
+        <v/>
+      </c>
+      <c r="G262" t="str">
+        <v/>
+      </c>
+      <c r="H262" t="str">
+        <v/>
+      </c>
+      <c r="I262" t="str">
+        <v/>
+      </c>
+      <c r="J262" t="str">
+        <v/>
+      </c>
+      <c r="K262" t="str">
+        <v/>
+      </c>
+      <c r="L262" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M262" t="str">
+        <v>Roaming Hoenn Skies, Mauville Game Corner, Trick House</v>
+      </c>
+      <c r="N262" t="str">
+        <v>{"defeatHoennChampion":true}</v>
+      </c>
+      <c r="O262" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>Extra Challenge A 6</v>
+      </c>
+      <c r="B263" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="C263" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="D263" t="str">
+        <v/>
+      </c>
+      <c r="E263" t="str">
+        <v/>
+      </c>
+      <c r="F263" t="str">
+        <v/>
+      </c>
+      <c r="G263" t="str">
+        <v/>
+      </c>
+      <c r="H263" t="str">
+        <v/>
+      </c>
+      <c r="I263" t="str">
+        <v/>
+      </c>
+      <c r="J263" t="str">
+        <v/>
+      </c>
+      <c r="K263" t="str">
+        <v/>
+      </c>
+      <c r="L263" t="str">
+        <v>No</v>
+      </c>
+      <c r="M263" t="str">
+        <v>Nebula Fissure</v>
+      </c>
+      <c r="N263" t="str">
+        <v>{"completeChallenges":["Extra Challenge A 6","Extra Challenge B 6","Extra Challenge (Roaming)"]}</v>
+      </c>
+      <c r="O263" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O253"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O263"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -13244,9 +13714,209 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>Challenge 7</v>
+      </c>
+      <c r="B48" t="str">
+        <v>{"earnBadge":{"name":"Stone Badge","leader":"Roxanne","badgeCount":1}}</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Granite Cave</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>Challenge 10</v>
+      </c>
+      <c r="B49" t="str">
+        <v>{"earnBadge":{"name":"Knuckle Badge","leader":"Brawly","badgeCount":2}}</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Route 107</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>Challenge 12</v>
+      </c>
+      <c r="B50" t="str">
+        <v>{"earnBadge":{"name":"Dynamo Badge","leader":"Wattson","badgeCount":3}}</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Route 110</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>Challenge 16</v>
+      </c>
+      <c r="B51" t="str">
+        <v>{"earnBadge":{"name":"Heat Badge","leader":"Flannery","badgeCount":4}}</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Fiery Path</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>Challenge 23</v>
+      </c>
+      <c r="B52" t="str">
+        <v>{"earnBadge":{"name":"Balance Badge","leader":"Norman","badgeCount":5}}</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Route 118</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>Challenge 32</v>
+      </c>
+      <c r="B53" t="str">
+        <v>{"earnBadge":{"name":"Feather Badge","leader":"Winona","badgeCount":6}}</v>
+      </c>
+      <c r="C53" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Mossdeep Gym</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>Challenge 33</v>
+      </c>
+      <c r="B54" t="str">
+        <v>{"earnBadge":{"name":"Mind Badge","leader":"Tate and Liza","badgeCount":7}}</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Big Fishing Spot</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>Challenge 36</v>
+      </c>
+      <c r="B55" t="str">
+        <v>{"earnBadge":{"name":"Rain Badge","leader":"Juan","badgeCount":8}}</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Defeat Gym Leader</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Shoal Cave</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>Challenge 44</v>
+      </c>
+      <c r="B56" t="str">
+        <v>{"defeatHoennChampion":true}</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Win Pokemon League</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Roaming Hoenn Skies, Mauville Game Corner, Trick House</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>Key to Nebula Fissure Challenge</v>
+      </c>
+      <c r="B57" t="str">
+        <v>{"completeChallenges":["Extra Challenge A 6","Extra Challenge B 6","Extra Challenge (Roaming)"]}</v>
+      </c>
+      <c r="C57" t="str">
+        <v>Defeat 250 pokemon</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Nebula Fissure</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F57"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/3_Hoenn_Data.xlsx
+++ b/3_Hoenn_Data.xlsx
@@ -6908,7 +6908,7 @@
         <v>41-45</v>
       </c>
       <c r="G139" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H139" s="1">
         <v>0.3</v>
@@ -6955,7 +6955,7 @@
         <v>41-45</v>
       </c>
       <c r="G140" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H140" s="1">
         <v>0.3</v>
@@ -7002,7 +7002,7 @@
         <v>41-45</v>
       </c>
       <c r="G141" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H141" s="1">
         <v>0.15</v>
@@ -7049,7 +7049,7 @@
         <v>41-45</v>
       </c>
       <c r="G142" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H142" s="1">
         <v>0.1</v>
@@ -7096,7 +7096,7 @@
         <v>41-45</v>
       </c>
       <c r="G143" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H143" s="1">
         <v>0.1</v>
@@ -7143,7 +7143,7 @@
         <v>41-45</v>
       </c>
       <c r="G144" t="str">
-        <v>37-40</v>
+        <v>38-41</v>
       </c>
       <c r="H144" s="1">
         <v>0.05</v>
@@ -7190,7 +7190,7 @@
         <v>43-46</v>
       </c>
       <c r="G145" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H145" s="1">
         <v>0.2375</v>
@@ -7237,7 +7237,7 @@
         <v>43-46</v>
       </c>
       <c r="G146" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H146" s="1">
         <v>0.19</v>
@@ -7284,7 +7284,7 @@
         <v>43-46</v>
       </c>
       <c r="G147" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H147" s="1">
         <v>0.1425</v>
@@ -7331,7 +7331,7 @@
         <v>43-46</v>
       </c>
       <c r="G148" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H148" s="1">
         <v>0.1425</v>
@@ -7378,7 +7378,7 @@
         <v>43-46</v>
       </c>
       <c r="G149" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H149" s="1">
         <v>0.095</v>
@@ -7425,7 +7425,7 @@
         <v>43-46</v>
       </c>
       <c r="G150" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H150" s="1">
         <v>0.095</v>
@@ -7472,7 +7472,7 @@
         <v>43-46</v>
       </c>
       <c r="G151" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H151" s="1">
         <v>0.0475</v>
@@ -7519,7 +7519,7 @@
         <v>43-46</v>
       </c>
       <c r="G152" t="str">
-        <v>38-41</v>
+        <v>40-44</v>
       </c>
       <c r="H152" s="1">
         <v>0.05</v>
@@ -7566,7 +7566,7 @@
         <v>44-48</v>
       </c>
       <c r="G153" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H153" s="1">
         <v>0.2</v>
@@ -7613,7 +7613,7 @@
         <v>44-48</v>
       </c>
       <c r="G154" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H154" s="1">
         <v>0.25</v>
@@ -7660,7 +7660,7 @@
         <v>44-48</v>
       </c>
       <c r="G155" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H155" s="1">
         <v>0.2</v>
@@ -7707,7 +7707,7 @@
         <v>44-48</v>
       </c>
       <c r="G156" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H156" s="1">
         <v>0.15</v>
@@ -7754,7 +7754,7 @@
         <v>44-48</v>
       </c>
       <c r="G157" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H157" s="1">
         <v>0.1</v>
@@ -7801,7 +7801,7 @@
         <v>44-48</v>
       </c>
       <c r="G158" t="str">
-        <v>40-44</v>
+        <v>42-46</v>
       </c>
       <c r="H158" s="1">
         <v>0.1</v>
@@ -7848,7 +7848,7 @@
         <v>46-50</v>
       </c>
       <c r="G159" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H159" s="1">
         <v>0.15</v>
@@ -7895,7 +7895,7 @@
         <v>46-50</v>
       </c>
       <c r="G160" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H160" s="1">
         <v>0.15</v>
@@ -7942,7 +7942,7 @@
         <v>51-55</v>
       </c>
       <c r="G161" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H161" s="1">
         <v>0.08</v>
@@ -7989,7 +7989,7 @@
         <v>46-50</v>
       </c>
       <c r="G162" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H162" s="1">
         <v>0.07</v>
@@ -8036,7 +8036,7 @@
         <v>46-50</v>
       </c>
       <c r="G163" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H163" s="1">
         <v>0.11</v>
@@ -8083,7 +8083,7 @@
         <v>46-50</v>
       </c>
       <c r="G164" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H164" s="1">
         <v>0.1</v>
@@ -8130,7 +8130,7 @@
         <v>46-50</v>
       </c>
       <c r="G165" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H165" s="1">
         <v>0.09</v>
@@ -8177,7 +8177,7 @@
         <v>44-48</v>
       </c>
       <c r="G166" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H166" s="1">
         <v>0.15</v>
@@ -8224,7 +8224,7 @@
         <v>51-55</v>
       </c>
       <c r="G167" t="str">
-        <v>42-46</v>
+        <v>44-48</v>
       </c>
       <c r="H167" s="1">
         <v>0.1</v>
@@ -8271,7 +8271,7 @@
         <v>48-51</v>
       </c>
       <c r="G168" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H168" s="1">
         <v>0.3</v>
@@ -8318,7 +8318,7 @@
         <v>48-51</v>
       </c>
       <c r="G169" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H169" s="1">
         <v>0.25</v>
@@ -8365,7 +8365,7 @@
         <v>48-51</v>
       </c>
       <c r="G170" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H170" s="1">
         <v>0.2</v>
@@ -8412,7 +8412,7 @@
         <v>48-51</v>
       </c>
       <c r="G171" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H171" s="1">
         <v>0.15</v>
@@ -8459,7 +8459,7 @@
         <v>48-51</v>
       </c>
       <c r="G172" t="str">
-        <v>44-48</v>
+        <v>46-50</v>
       </c>
       <c r="H172" s="1">
         <v>0.1</v>
@@ -8506,7 +8506,7 @@
         <v>49-53</v>
       </c>
       <c r="G173" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H173" s="1">
         <v>0.3</v>
@@ -8553,7 +8553,7 @@
         <v>49-53</v>
       </c>
       <c r="G174" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H174" s="1">
         <v>0.25</v>
@@ -8600,7 +8600,7 @@
         <v>49-53</v>
       </c>
       <c r="G175" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H175" s="1">
         <v>0.2</v>
@@ -8647,7 +8647,7 @@
         <v>49-53</v>
       </c>
       <c r="G176" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H176" s="1">
         <v>0.15</v>
@@ -8694,7 +8694,7 @@
         <v>49-53</v>
       </c>
       <c r="G177" t="str">
-        <v>46-50</v>
+        <v>48-52</v>
       </c>
       <c r="H177" s="1">
         <v>0.1</v>
@@ -8835,7 +8835,7 @@
         <v>54-58</v>
       </c>
       <c r="G180" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H180" s="1">
         <v>0.198</v>
@@ -8882,7 +8882,7 @@
         <v>54-58</v>
       </c>
       <c r="G181" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H181" s="1">
         <v>0.198</v>
@@ -8929,7 +8929,7 @@
         <v>54-58</v>
       </c>
       <c r="G182" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H182" s="1">
         <v>0.135</v>
@@ -8976,7 +8976,7 @@
         <v>54-58</v>
       </c>
       <c r="G183" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H183" s="1">
         <v>0.135</v>
@@ -9023,7 +9023,7 @@
         <v>54-58</v>
       </c>
       <c r="G184" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H184" s="1">
         <v>0.09</v>
@@ -9070,7 +9070,7 @@
         <v>54-58</v>
       </c>
       <c r="G185" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H185" s="1">
         <v>0.072</v>
@@ -9117,7 +9117,7 @@
         <v>54-58</v>
       </c>
       <c r="G186" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H186" s="1">
         <v>0.072</v>
@@ -9164,7 +9164,7 @@
         <v>54-58</v>
       </c>
       <c r="G187" t="str">
-        <v>48-52</v>
+        <v>50-55</v>
       </c>
       <c r="H187" s="1">
         <v>0.1</v>
@@ -9211,7 +9211,7 @@
         <v>56-60</v>
       </c>
       <c r="G188" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H188" s="1">
         <v>0.585</v>
@@ -9258,7 +9258,7 @@
         <v>56-60</v>
       </c>
       <c r="G189" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H189" s="1">
         <v>0.225</v>
@@ -9305,7 +9305,7 @@
         <v>56-60</v>
       </c>
       <c r="G190" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H190" s="1">
         <v>0.09</v>
@@ -9352,7 +9352,7 @@
         <v>56-60</v>
       </c>
       <c r="G191" t="str">
-        <v>50-55</v>
+        <v>52-57</v>
       </c>
       <c r="H191" s="1">
         <v>0.1</v>
@@ -9446,7 +9446,7 @@
         <v>59-63</v>
       </c>
       <c r="G193" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H193" s="1">
         <v>0.405</v>
@@ -9493,7 +9493,7 @@
         <v>59-63</v>
       </c>
       <c r="G194" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H194" s="1">
         <v>0.27</v>
@@ -9540,7 +9540,7 @@
         <v>59-63</v>
       </c>
       <c r="G195" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H195" s="1">
         <v>0.135</v>
@@ -9587,7 +9587,7 @@
         <v>59-63</v>
       </c>
       <c r="G196" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H196" s="1">
         <v>0.09</v>
@@ -9634,7 +9634,7 @@
         <v>59-63</v>
       </c>
       <c r="G197" t="str">
-        <v>52-57</v>
+        <v>54-59</v>
       </c>
       <c r="H197" s="1">
         <v>0.1</v>
@@ -9681,7 +9681,7 @@
         <v>61-65</v>
       </c>
       <c r="G198" t="str">
-        <v>54-59</v>
+        <v>56-61</v>
       </c>
       <c r="H198" s="1">
         <v>1</v>
@@ -9728,7 +9728,7 @@
         <v>62-66</v>
       </c>
       <c r="G199" t="str">
-        <v>58-63</v>
+        <v>60-66</v>
       </c>
       <c r="H199" s="1">
         <v>0.3</v>
@@ -9775,7 +9775,7 @@
         <v>62-66</v>
       </c>
       <c r="G200" t="str">
-        <v>58-63</v>
+        <v>60-66</v>
       </c>
       <c r="H200" s="1">
         <v>0.25</v>
@@ -9822,7 +9822,7 @@
         <v>62-66</v>
       </c>
       <c r="G201" t="str">
-        <v>58-63</v>
+        <v>60-66</v>
       </c>
       <c r="H201" s="1">
         <v>0.2</v>
@@ -9869,7 +9869,7 @@
         <v>62-66</v>
       </c>
       <c r="G202" t="str">
-        <v>58-63</v>
+        <v>60-66</v>
       </c>
       <c r="H202" s="1">
         <v>0.15</v>
@@ -9916,7 +9916,7 @@
         <v>62-66</v>
       </c>
       <c r="G203" t="str">
-        <v>58-63</v>
+        <v>60-66</v>
       </c>
       <c r="H203" s="1">
         <v>0.1</v>
@@ -9963,7 +9963,7 @@
         <v>64-68</v>
       </c>
       <c r="G204" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H204" s="1">
         <v>0.2375</v>
@@ -10010,7 +10010,7 @@
         <v>64-68</v>
       </c>
       <c r="G205" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H205" s="1">
         <v>0.2375</v>
@@ -10057,7 +10057,7 @@
         <v>64-68</v>
       </c>
       <c r="G206" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H206" s="1">
         <v>0.152</v>
@@ -10104,7 +10104,7 @@
         <v>64-68</v>
       </c>
       <c r="G207" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H207" s="1">
         <v>0.152</v>
@@ -10151,7 +10151,7 @@
         <v>64-68</v>
       </c>
       <c r="G208" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H208" s="1">
         <v>0.114</v>
@@ -10198,7 +10198,7 @@
         <v>64-68</v>
       </c>
       <c r="G209" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H209" s="1">
         <v>0.057</v>
@@ -10245,7 +10245,7 @@
         <v>64-68</v>
       </c>
       <c r="G210" t="str">
-        <v>56-61</v>
+        <v>58-63</v>
       </c>
       <c r="H210" s="1">
         <v>0.05</v>
@@ -10762,7 +10762,7 @@
         <v>82-87</v>
       </c>
       <c r="G221" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H221" s="1">
         <v>0.3333</v>
@@ -10809,7 +10809,7 @@
         <v>82-87</v>
       </c>
       <c r="G222" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H222" s="1">
         <v>0.3333</v>
@@ -10856,7 +10856,7 @@
         <v>82-87</v>
       </c>
       <c r="G223" t="str">
-        <v>96-104</v>
+        <v>92-100</v>
       </c>
       <c r="H223" s="1">
         <v>0.3334</v>
